--- a/Analisis Retail Bisnis Omni-Channel.xlsx
+++ b/Analisis Retail Bisnis Omni-Channel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aldy\Documents\DATA ANALYST\MICROSOFT EXCEL\PORTOFOLIO\Analisis Retail Bisnis Omni-Channel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FAB447-721E-4F5D-A9D2-874A6AE0E43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EA1C2C-50F4-4DE2-B540-46896F24CC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="5" xr2:uid="{0FABD09F-C599-4D8F-AE1F-66CDC9C9D3DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="2" activeTab="6" xr2:uid="{0FABD09F-C599-4D8F-AE1F-66CDC9C9D3DB}"/>
   </bookViews>
   <sheets>
     <sheet name="penjualan" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="594">
   <si>
     <t>ID_Transaksi</t>
   </si>
@@ -1806,64 +1806,38 @@
     <t>Dasbor visual interaktif untuk portofolio LinkedIn/GitHub</t>
   </si>
   <si>
-    <t>Sum of Laba_Kotor</t>
-  </si>
-  <si>
     <t>Sum of Margin_Keuntungan</t>
   </si>
   <si>
-    <t>Months (Tanggal)</t>
-  </si>
-  <si>
-    <t>Jan</t>
-  </si>
-  <si>
-    <t>Feb</t>
-  </si>
-  <si>
-    <t>Mar</t>
-  </si>
-  <si>
-    <t>Apr</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>Jun</t>
-  </si>
-  <si>
-    <t>Jul</t>
-  </si>
-  <si>
-    <t>Aug</t>
-  </si>
-  <si>
-    <t>Sep</t>
-  </si>
-  <si>
-    <t>Oct</t>
-  </si>
-  <si>
-    <t>Nov</t>
-  </si>
-  <si>
-    <t>Dec</t>
-  </si>
-  <si>
-    <t>Sum of Total_Pendapatan_Bersih</t>
+    <t>ANALISIS BISNIS RETAIL OMNI-CHANNEL</t>
+  </si>
+  <si>
+    <t>TOTAL REVENUE</t>
+  </si>
+  <si>
+    <t>TOTAL NET PROFIT</t>
+  </si>
+  <si>
+    <t>OVERALL PROFIT MARGIN%</t>
+  </si>
+  <si>
+    <t>TOTAL UNITS SOLD</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="&quot;Rp&quot;#,##0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1889,8 +1863,14 @@
       <color theme="1"/>
       <name val="Poppins"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Poppins"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1900,6 +1880,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2028,7 +2014,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2145,7 +2131,33 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2153,404 +2165,11 @@
   </cellStyles>
   <dxfs count="54">
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right/>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF9F"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right/>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -3044,6 +2663,214 @@
         <name val="Poppins"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right/>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="166" formatCode="0.0%"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -3473,6 +3300,191 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right/>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -3965,7 +3977,106 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1225000" maxValue="42675000"/>
     </cacheField>
     <cacheField name="Laba_Kotor" numFmtId="165">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="235000" maxValue="17325000"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="235000" maxValue="17325000" count="98">
+        <n v="4550000"/>
+        <n v="550000"/>
+        <n v="850000"/>
+        <n v="1665000"/>
+        <n v="2710000"/>
+        <n v="3465000"/>
+        <n v="570000"/>
+        <n v="3580000"/>
+        <n v="1870000"/>
+        <n v="705000"/>
+        <n v="3450000"/>
+        <n v="1320000"/>
+        <n v="1330000"/>
+        <n v="980000"/>
+        <n v="1750000"/>
+        <n v="2070000"/>
+        <n v="1450000"/>
+        <n v="1515000"/>
+        <n v="2500000"/>
+        <n v="1660000"/>
+        <n v="6825000"/>
+        <n v="770000"/>
+        <n v="1700000"/>
+        <n v="555000"/>
+        <n v="4065000"/>
+        <n v="6930000"/>
+        <n v="380000"/>
+        <n v="895000"/>
+        <n v="4675000"/>
+        <n v="470000"/>
+        <n v="10350000"/>
+        <n v="990000"/>
+        <n v="665000"/>
+        <n v="490000"/>
+        <n v="7000000"/>
+        <n v="1035000"/>
+        <n v="870000"/>
+        <n v="1010000"/>
+        <n v="6250000"/>
+        <n v="830000"/>
+        <n v="9100000"/>
+        <n v="880000"/>
+        <n v="475000"/>
+        <n v="2685000"/>
+        <n v="940000"/>
+        <n v="6900000"/>
+        <n v="1155000"/>
+        <n v="1995000"/>
+        <n v="245000"/>
+        <n v="3500000"/>
+        <n v="3105000"/>
+        <n v="1160000"/>
+        <n v="505000"/>
+        <n v="7500000"/>
+        <n v="660000"/>
+        <n v="2550000"/>
+        <n v="2220000"/>
+        <n v="1355000"/>
+        <n v="10395000"/>
+        <n v="1790000"/>
+        <n v="2805000"/>
+        <n v="235000"/>
+        <n v="2660000"/>
+        <n v="5250000"/>
+        <n v="2020000"/>
+        <n v="1250000"/>
+        <n v="1245000"/>
+        <n v="2775000"/>
+        <n v="1175000"/>
+        <n v="735000"/>
+        <n v="2030000"/>
+        <n v="5000000"/>
+        <n v="2275000"/>
+        <n v="1110000"/>
+        <n v="5420000"/>
+        <n v="13800000"/>
+        <n v="1225000"/>
+        <n v="3750000"/>
+        <n v="415000"/>
+        <n v="3400000"/>
+        <n v="3740000"/>
+        <n v="8750000"/>
+        <n v="2075000"/>
+        <n v="1470000"/>
+        <n v="13860000"/>
+        <n v="935000"/>
+        <n v="3325000"/>
+        <n v="2525000"/>
+        <n v="1740000"/>
+        <n v="2320000"/>
+        <n v="440000"/>
+        <n v="17325000"/>
+        <n v="760000"/>
+        <n v="825000"/>
+        <n v="6775000"/>
+        <n v="4475000"/>
+        <n v="1410000"/>
+        <n v="4140000"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Margin_Keuntungan" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.10294117647058823" maxValue="0.41666666666666669"/>
@@ -4394,7 +4505,7 @@
     <n v="2400000"/>
     <n v="21600000"/>
     <n v="17050000"/>
-    <n v="4550000"/>
+    <x v="0"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -4414,7 +4525,7 @@
     <n v="1275000"/>
     <n v="2975000"/>
     <n v="2425000"/>
-    <n v="550000"/>
+    <x v="1"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -4434,7 +4545,7 @@
     <n v="0"/>
     <n v="2100000"/>
     <n v="1250000"/>
-    <n v="850000"/>
+    <x v="2"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -4454,7 +4565,7 @@
     <n v="2040000"/>
     <n v="8160000"/>
     <n v="6495000"/>
-    <n v="1665000"/>
+    <x v="3"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -4474,7 +4585,7 @@
     <n v="840000"/>
     <n v="7560000"/>
     <n v="4850000"/>
-    <n v="2710000"/>
+    <x v="4"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -4494,7 +4605,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8535000"/>
-    <n v="3465000"/>
+    <x v="5"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -4514,7 +4625,7 @@
     <n v="1530000"/>
     <n v="3570000"/>
     <n v="3000000"/>
-    <n v="570000"/>
+    <x v="6"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -4534,7 +4645,7 @@
     <n v="3360000"/>
     <n v="13440000"/>
     <n v="9860000"/>
-    <n v="3580000"/>
+    <x v="7"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -4554,7 +4665,7 @@
     <n v="680000"/>
     <n v="6120000"/>
     <n v="4250000"/>
-    <n v="1870000"/>
+    <x v="8"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -4574,7 +4685,7 @@
     <n v="1890000"/>
     <n v="4410000"/>
     <n v="3705000"/>
-    <n v="705000"/>
+    <x v="9"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -4594,7 +4705,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8550000"/>
-    <n v="3450000"/>
+    <x v="10"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -4614,7 +4725,7 @@
     <n v="1360000"/>
     <n v="5440000"/>
     <n v="4120000"/>
-    <n v="1320000"/>
+    <x v="11"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -4634,7 +4745,7 @@
     <n v="420000"/>
     <n v="3780000"/>
     <n v="2450000"/>
-    <n v="1330000"/>
+    <x v="12"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -4654,7 +4765,7 @@
     <n v="4080000"/>
     <n v="9520000"/>
     <n v="8540000"/>
-    <n v="980000"/>
+    <x v="13"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -4674,7 +4785,7 @@
     <n v="0"/>
     <n v="4200000"/>
     <n v="2450000"/>
-    <n v="1750000"/>
+    <x v="14"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -4694,7 +4805,7 @@
     <n v="4800000"/>
     <n v="19200000"/>
     <n v="17130000"/>
-    <n v="2070000"/>
+    <x v="15"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -4714,7 +4825,7 @@
     <n v="425000"/>
     <n v="3825000"/>
     <n v="2375000"/>
-    <n v="1450000"/>
+    <x v="16"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -4734,7 +4845,7 @@
     <n v="3780000"/>
     <n v="8820000"/>
     <n v="7305000"/>
-    <n v="1515000"/>
+    <x v="17"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -4754,7 +4865,7 @@
     <n v="0"/>
     <n v="6800000"/>
     <n v="4300000"/>
-    <n v="2500000"/>
+    <x v="18"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -4774,7 +4885,7 @@
     <n v="1680000"/>
     <n v="6720000"/>
     <n v="5060000"/>
-    <n v="1660000"/>
+    <x v="19"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -4794,7 +4905,7 @@
     <n v="3600000"/>
     <n v="32400000"/>
     <n v="25575000"/>
-    <n v="6825000"/>
+    <x v="20"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -4814,7 +4925,7 @@
     <n v="1785000"/>
     <n v="4165000"/>
     <n v="3395000"/>
-    <n v="770000"/>
+    <x v="21"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -4834,7 +4945,7 @@
     <n v="0"/>
     <n v="4200000"/>
     <n v="2500000"/>
-    <n v="1700000"/>
+    <x v="22"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -4854,7 +4965,7 @@
     <n v="680000"/>
     <n v="2720000"/>
     <n v="2165000"/>
-    <n v="555000"/>
+    <x v="23"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -4874,7 +4985,7 @@
     <n v="1260000"/>
     <n v="11340000"/>
     <n v="7275000"/>
-    <n v="4065000"/>
+    <x v="24"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -4894,7 +5005,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17070000"/>
-    <n v="6930000"/>
+    <x v="25"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -4914,7 +5025,7 @@
     <n v="1020000"/>
     <n v="2380000"/>
     <n v="2000000"/>
-    <n v="380000"/>
+    <x v="26"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -4934,7 +5045,7 @@
     <n v="840000"/>
     <n v="3360000"/>
     <n v="2465000"/>
-    <n v="895000"/>
+    <x v="27"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -4954,7 +5065,7 @@
     <n v="1700000"/>
     <n v="15300000"/>
     <n v="10625000"/>
-    <n v="4675000"/>
+    <x v="28"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -4974,7 +5085,7 @@
     <n v="1260000"/>
     <n v="2940000"/>
     <n v="2470000"/>
-    <n v="470000"/>
+    <x v="29"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -4994,7 +5105,7 @@
     <n v="0"/>
     <n v="36000000"/>
     <n v="25650000"/>
-    <n v="10350000"/>
+    <x v="30"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -5014,7 +5125,7 @@
     <n v="1020000"/>
     <n v="4080000"/>
     <n v="3090000"/>
-    <n v="990000"/>
+    <x v="31"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -5034,7 +5145,7 @@
     <n v="210000"/>
     <n v="1890000"/>
     <n v="1225000"/>
-    <n v="665000"/>
+    <x v="32"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -5054,7 +5165,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="4270000"/>
-    <n v="490000"/>
+    <x v="33"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -5074,7 +5185,7 @@
     <n v="0"/>
     <n v="16800000"/>
     <n v="9800000"/>
-    <n v="7000000"/>
+    <x v="34"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -5094,7 +5205,7 @@
     <n v="2400000"/>
     <n v="9600000"/>
     <n v="8565000"/>
-    <n v="1035000"/>
+    <x v="35"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -5114,7 +5225,7 @@
     <n v="255000"/>
     <n v="2295000"/>
     <n v="1425000"/>
-    <n v="870000"/>
+    <x v="36"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -5134,7 +5245,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4870000"/>
-    <n v="1010000"/>
+    <x v="37"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -5154,7 +5265,7 @@
     <n v="0"/>
     <n v="17000000"/>
     <n v="10750000"/>
-    <n v="6250000"/>
+    <x v="38"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -5174,7 +5285,7 @@
     <n v="840000"/>
     <n v="3360000"/>
     <n v="2530000"/>
-    <n v="830000"/>
+    <x v="39"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -5194,7 +5305,7 @@
     <n v="4800000"/>
     <n v="43200000"/>
     <n v="34100000"/>
-    <n v="9100000"/>
+    <x v="40"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -5214,7 +5325,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="3880000"/>
-    <n v="880000"/>
+    <x v="41"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -5234,7 +5345,7 @@
     <n v="0"/>
     <n v="2100000"/>
     <n v="1250000"/>
-    <n v="850000"/>
+    <x v="2"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -5254,7 +5365,7 @@
     <n v="2040000"/>
     <n v="8160000"/>
     <n v="6495000"/>
-    <n v="1665000"/>
+    <x v="3"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -5274,7 +5385,7 @@
     <n v="840000"/>
     <n v="7560000"/>
     <n v="4850000"/>
-    <n v="2710000"/>
+    <x v="4"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -5294,7 +5405,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8535000"/>
-    <n v="3465000"/>
+    <x v="5"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -5314,7 +5425,7 @@
     <n v="1275000"/>
     <n v="2975000"/>
     <n v="2500000"/>
-    <n v="475000"/>
+    <x v="42"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -5334,7 +5445,7 @@
     <n v="2520000"/>
     <n v="10080000"/>
     <n v="7395000"/>
-    <n v="2685000"/>
+    <x v="43"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -5354,7 +5465,7 @@
     <n v="680000"/>
     <n v="6120000"/>
     <n v="4250000"/>
-    <n v="1870000"/>
+    <x v="8"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -5374,7 +5485,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4940000"/>
-    <n v="940000"/>
+    <x v="44"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -5394,7 +5505,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17100000"/>
-    <n v="6900000"/>
+    <x v="45"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -5414,7 +5525,7 @@
     <n v="1190000"/>
     <n v="4760000"/>
     <n v="3605000"/>
-    <n v="1155000"/>
+    <x v="46"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -5434,7 +5545,7 @@
     <n v="630000"/>
     <n v="5670000"/>
     <n v="3675000"/>
-    <n v="1995000"/>
+    <x v="47"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -5454,7 +5565,7 @@
     <n v="1020000"/>
     <n v="2380000"/>
     <n v="2135000"/>
-    <n v="245000"/>
+    <x v="48"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -5474,7 +5585,7 @@
     <n v="0"/>
     <n v="8400000"/>
     <n v="4900000"/>
-    <n v="3500000"/>
+    <x v="49"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -5494,7 +5605,7 @@
     <n v="7200000"/>
     <n v="28800000"/>
     <n v="25695000"/>
-    <n v="3105000"/>
+    <x v="50"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -5514,7 +5625,7 @@
     <n v="340000"/>
     <n v="3060000"/>
     <n v="1900000"/>
-    <n v="1160000"/>
+    <x v="51"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -5534,7 +5645,7 @@
     <n v="1260000"/>
     <n v="2940000"/>
     <n v="2435000"/>
-    <n v="505000"/>
+    <x v="52"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -5554,7 +5665,7 @@
     <n v="0"/>
     <n v="20400000"/>
     <n v="12900000"/>
-    <n v="7500000"/>
+    <x v="53"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -5574,7 +5685,7 @@
     <n v="840000"/>
     <n v="3360000"/>
     <n v="2530000"/>
-    <n v="830000"/>
+    <x v="39"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -5594,7 +5705,7 @@
     <n v="2400000"/>
     <n v="21600000"/>
     <n v="17050000"/>
-    <n v="4550000"/>
+    <x v="0"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -5614,7 +5725,7 @@
     <n v="1530000"/>
     <n v="3570000"/>
     <n v="2910000"/>
-    <n v="660000"/>
+    <x v="54"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -5634,7 +5745,7 @@
     <n v="0"/>
     <n v="6300000"/>
     <n v="3750000"/>
-    <n v="2550000"/>
+    <x v="55"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -5654,7 +5765,7 @@
     <n v="2720000"/>
     <n v="10880000"/>
     <n v="8660000"/>
-    <n v="2220000"/>
+    <x v="56"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -5674,7 +5785,7 @@
     <n v="420000"/>
     <n v="3780000"/>
     <n v="2425000"/>
-    <n v="1355000"/>
+    <x v="57"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -5694,7 +5805,7 @@
     <n v="0"/>
     <n v="36000000"/>
     <n v="25605000"/>
-    <n v="10395000"/>
+    <x v="58"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -5714,7 +5825,7 @@
     <n v="1275000"/>
     <n v="2975000"/>
     <n v="2500000"/>
-    <n v="475000"/>
+    <x v="42"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -5734,7 +5845,7 @@
     <n v="1680000"/>
     <n v="6720000"/>
     <n v="4930000"/>
-    <n v="1790000"/>
+    <x v="59"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -5754,7 +5865,7 @@
     <n v="1020000"/>
     <n v="9180000"/>
     <n v="6375000"/>
-    <n v="2805000"/>
+    <x v="60"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -5774,7 +5885,7 @@
     <n v="630000"/>
     <n v="1470000"/>
     <n v="1235000"/>
-    <n v="235000"/>
+    <x v="61"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -5794,7 +5905,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17100000"/>
-    <n v="6900000"/>
+    <x v="45"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -5814,7 +5925,7 @@
     <n v="1190000"/>
     <n v="4760000"/>
     <n v="3605000"/>
-    <n v="1155000"/>
+    <x v="46"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -5834,7 +5945,7 @@
     <n v="840000"/>
     <n v="7560000"/>
     <n v="4900000"/>
-    <n v="2660000"/>
+    <x v="62"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -5854,7 +5965,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="4270000"/>
-    <n v="490000"/>
+    <x v="33"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -5874,7 +5985,7 @@
     <n v="0"/>
     <n v="12600000"/>
     <n v="7350000"/>
-    <n v="5250000"/>
+    <x v="63"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -5894,7 +6005,7 @@
     <n v="2400000"/>
     <n v="9600000"/>
     <n v="8565000"/>
-    <n v="1035000"/>
+    <x v="35"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -5914,7 +6025,7 @@
     <n v="425000"/>
     <n v="3825000"/>
     <n v="2375000"/>
-    <n v="1450000"/>
+    <x v="16"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -5934,7 +6045,7 @@
     <n v="5040000"/>
     <n v="11760000"/>
     <n v="9740000"/>
-    <n v="2020000"/>
+    <x v="64"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -5954,7 +6065,7 @@
     <n v="0"/>
     <n v="3400000"/>
     <n v="2150000"/>
-    <n v="1250000"/>
+    <x v="65"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -5974,7 +6085,7 @@
     <n v="1260000"/>
     <n v="5040000"/>
     <n v="3795000"/>
-    <n v="1245000"/>
+    <x v="66"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -5994,7 +6105,7 @@
     <n v="2400000"/>
     <n v="21600000"/>
     <n v="17050000"/>
-    <n v="4550000"/>
+    <x v="0"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -6014,7 +6125,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="3880000"/>
-    <n v="880000"/>
+    <x v="41"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -6034,7 +6145,7 @@
     <n v="0"/>
     <n v="4200000"/>
     <n v="2500000"/>
-    <n v="1700000"/>
+    <x v="22"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -6054,7 +6165,7 @@
     <n v="3400000"/>
     <n v="13600000"/>
     <n v="10825000"/>
-    <n v="2775000"/>
+    <x v="67"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -6074,7 +6185,7 @@
     <n v="840000"/>
     <n v="7560000"/>
     <n v="4850000"/>
-    <n v="2710000"/>
+    <x v="4"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -6094,7 +6205,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8535000"/>
-    <n v="3465000"/>
+    <x v="5"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -6114,7 +6225,7 @@
     <n v="1020000"/>
     <n v="2380000"/>
     <n v="2000000"/>
-    <n v="380000"/>
+    <x v="26"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -6134,7 +6245,7 @@
     <n v="2520000"/>
     <n v="10080000"/>
     <n v="7395000"/>
-    <n v="2685000"/>
+    <x v="43"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -6154,7 +6265,7 @@
     <n v="680000"/>
     <n v="6120000"/>
     <n v="4250000"/>
-    <n v="1870000"/>
+    <x v="8"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -6174,7 +6285,7 @@
     <n v="3150000"/>
     <n v="7350000"/>
     <n v="6175000"/>
-    <n v="1175000"/>
+    <x v="68"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -6194,7 +6305,7 @@
     <n v="0"/>
     <n v="36000000"/>
     <n v="25650000"/>
-    <n v="10350000"/>
+    <x v="30"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -6214,7 +6325,7 @@
     <n v="1020000"/>
     <n v="4080000"/>
     <n v="3090000"/>
-    <n v="990000"/>
+    <x v="31"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -6234,7 +6345,7 @@
     <n v="210000"/>
     <n v="1890000"/>
     <n v="1225000"/>
-    <n v="665000"/>
+    <x v="32"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -6254,7 +6365,7 @@
     <n v="3060000"/>
     <n v="7140000"/>
     <n v="6405000"/>
-    <n v="735000"/>
+    <x v="69"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -6274,7 +6385,7 @@
     <n v="0"/>
     <n v="8400000"/>
     <n v="4900000"/>
-    <n v="3500000"/>
+    <x v="49"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -6294,7 +6405,7 @@
     <n v="4800000"/>
     <n v="19200000"/>
     <n v="17130000"/>
-    <n v="2070000"/>
+    <x v="15"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -6314,7 +6425,7 @@
     <n v="595000"/>
     <n v="5355000"/>
     <n v="3325000"/>
-    <n v="2030000"/>
+    <x v="70"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -6334,7 +6445,7 @@
     <n v="1260000"/>
     <n v="2940000"/>
     <n v="2435000"/>
-    <n v="505000"/>
+    <x v="52"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -6354,7 +6465,7 @@
     <n v="0"/>
     <n v="13600000"/>
     <n v="8600000"/>
-    <n v="5000000"/>
+    <x v="71"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -6374,7 +6485,7 @@
     <n v="840000"/>
     <n v="3360000"/>
     <n v="2530000"/>
-    <n v="830000"/>
+    <x v="39"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -6394,7 +6505,7 @@
     <n v="1200000"/>
     <n v="10800000"/>
     <n v="8525000"/>
-    <n v="2275000"/>
+    <x v="72"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -6414,7 +6525,7 @@
     <n v="1275000"/>
     <n v="2975000"/>
     <n v="2425000"/>
-    <n v="550000"/>
+    <x v="1"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -6434,7 +6545,7 @@
     <n v="0"/>
     <n v="6300000"/>
     <n v="3750000"/>
-    <n v="2550000"/>
+    <x v="55"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -6454,7 +6565,7 @@
     <n v="1360000"/>
     <n v="5440000"/>
     <n v="4330000"/>
-    <n v="1110000"/>
+    <x v="73"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -6474,7 +6585,7 @@
     <n v="1680000"/>
     <n v="15120000"/>
     <n v="9700000"/>
-    <n v="5420000"/>
+    <x v="74"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -6494,7 +6605,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17070000"/>
-    <n v="6930000"/>
+    <x v="25"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -6514,7 +6625,7 @@
     <n v="1530000"/>
     <n v="3570000"/>
     <n v="3000000"/>
-    <n v="570000"/>
+    <x v="6"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -6534,7 +6645,7 @@
     <n v="840000"/>
     <n v="3360000"/>
     <n v="2465000"/>
-    <n v="895000"/>
+    <x v="27"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -6554,7 +6665,7 @@
     <n v="1020000"/>
     <n v="9180000"/>
     <n v="6375000"/>
-    <n v="2805000"/>
+    <x v="60"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -6574,7 +6685,7 @@
     <n v="1260000"/>
     <n v="2940000"/>
     <n v="2470000"/>
-    <n v="470000"/>
+    <x v="29"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -6594,7 +6705,7 @@
     <n v="0"/>
     <n v="48000000"/>
     <n v="34200000"/>
-    <n v="13800000"/>
+    <x v="75"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -6614,7 +6725,7 @@
     <n v="1360000"/>
     <n v="5440000"/>
     <n v="4120000"/>
-    <n v="1320000"/>
+    <x v="11"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -6634,7 +6745,7 @@
     <n v="420000"/>
     <n v="3780000"/>
     <n v="2450000"/>
-    <n v="1330000"/>
+    <x v="12"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -6654,7 +6765,7 @@
     <n v="5100000"/>
     <n v="11900000"/>
     <n v="10675000"/>
-    <n v="1225000"/>
+    <x v="76"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -6674,7 +6785,7 @@
     <n v="0"/>
     <n v="4200000"/>
     <n v="2450000"/>
-    <n v="1750000"/>
+    <x v="14"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -6694,7 +6805,7 @@
     <n v="7200000"/>
     <n v="28800000"/>
     <n v="25695000"/>
-    <n v="3105000"/>
+    <x v="50"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -6714,7 +6825,7 @@
     <n v="340000"/>
     <n v="3060000"/>
     <n v="1900000"/>
-    <n v="1160000"/>
+    <x v="51"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -6734,7 +6845,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4870000"/>
-    <n v="1010000"/>
+    <x v="37"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -6754,7 +6865,7 @@
     <n v="0"/>
     <n v="10200000"/>
     <n v="6450000"/>
-    <n v="3750000"/>
+    <x v="77"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -6774,7 +6885,7 @@
     <n v="420000"/>
     <n v="1680000"/>
     <n v="1265000"/>
-    <n v="415000"/>
+    <x v="78"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -6794,7 +6905,7 @@
     <n v="2400000"/>
     <n v="21600000"/>
     <n v="17050000"/>
-    <n v="4550000"/>
+    <x v="0"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -6814,7 +6925,7 @@
     <n v="1785000"/>
     <n v="4165000"/>
     <n v="3395000"/>
-    <n v="770000"/>
+    <x v="21"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -6834,7 +6945,7 @@
     <n v="0"/>
     <n v="8400000"/>
     <n v="5000000"/>
-    <n v="3400000"/>
+    <x v="79"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -6854,7 +6965,7 @@
     <n v="1360000"/>
     <n v="5440000"/>
     <n v="4330000"/>
-    <n v="1110000"/>
+    <x v="73"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -6874,7 +6985,7 @@
     <n v="1260000"/>
     <n v="11340000"/>
     <n v="7275000"/>
-    <n v="4065000"/>
+    <x v="24"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -6894,7 +7005,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8535000"/>
-    <n v="3465000"/>
+    <x v="5"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -6914,7 +7025,7 @@
     <n v="1275000"/>
     <n v="2975000"/>
     <n v="2500000"/>
-    <n v="475000"/>
+    <x v="42"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -6934,7 +7045,7 @@
     <n v="1680000"/>
     <n v="6720000"/>
     <n v="4930000"/>
-    <n v="1790000"/>
+    <x v="59"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -6954,7 +7065,7 @@
     <n v="1360000"/>
     <n v="12240000"/>
     <n v="8500000"/>
-    <n v="3740000"/>
+    <x v="80"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -6974,7 +7085,7 @@
     <n v="1890000"/>
     <n v="4410000"/>
     <n v="3705000"/>
-    <n v="705000"/>
+    <x v="9"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -6994,7 +7105,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17100000"/>
-    <n v="6900000"/>
+    <x v="45"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -7014,7 +7125,7 @@
     <n v="1020000"/>
     <n v="4080000"/>
     <n v="3090000"/>
-    <n v="990000"/>
+    <x v="31"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -7034,7 +7145,7 @@
     <n v="210000"/>
     <n v="1890000"/>
     <n v="1225000"/>
-    <n v="665000"/>
+    <x v="32"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -7054,7 +7165,7 @@
     <n v="3060000"/>
     <n v="7140000"/>
     <n v="6405000"/>
-    <n v="735000"/>
+    <x v="69"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -7074,7 +7185,7 @@
     <n v="0"/>
     <n v="21000000"/>
     <n v="12250000"/>
-    <n v="8750000"/>
+    <x v="81"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -7094,7 +7205,7 @@
     <n v="4800000"/>
     <n v="19200000"/>
     <n v="17130000"/>
-    <n v="2070000"/>
+    <x v="15"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -7114,7 +7225,7 @@
     <n v="255000"/>
     <n v="2295000"/>
     <n v="1425000"/>
-    <n v="870000"/>
+    <x v="36"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -7134,7 +7245,7 @@
     <n v="5040000"/>
     <n v="11760000"/>
     <n v="9740000"/>
-    <n v="2020000"/>
+    <x v="64"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -7154,7 +7265,7 @@
     <n v="0"/>
     <n v="6800000"/>
     <n v="4300000"/>
-    <n v="2500000"/>
+    <x v="18"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -7174,7 +7285,7 @@
     <n v="2100000"/>
     <n v="8400000"/>
     <n v="6325000"/>
-    <n v="2075000"/>
+    <x v="82"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -7194,7 +7305,7 @@
     <n v="3600000"/>
     <n v="32400000"/>
     <n v="25575000"/>
-    <n v="6825000"/>
+    <x v="20"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -7214,7 +7325,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="3880000"/>
-    <n v="880000"/>
+    <x v="41"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -7234,7 +7345,7 @@
     <n v="0"/>
     <n v="2100000"/>
     <n v="1250000"/>
-    <n v="850000"/>
+    <x v="2"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -7254,7 +7365,7 @@
     <n v="2720000"/>
     <n v="10880000"/>
     <n v="8660000"/>
-    <n v="2220000"/>
+    <x v="56"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -7274,7 +7385,7 @@
     <n v="840000"/>
     <n v="7560000"/>
     <n v="4850000"/>
-    <n v="2710000"/>
+    <x v="4"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -7294,7 +7405,7 @@
     <n v="0"/>
     <n v="36000000"/>
     <n v="25605000"/>
-    <n v="10395000"/>
+    <x v="58"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -7314,7 +7425,7 @@
     <n v="1275000"/>
     <n v="2975000"/>
     <n v="2500000"/>
-    <n v="475000"/>
+    <x v="42"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -7334,7 +7445,7 @@
     <n v="840000"/>
     <n v="3360000"/>
     <n v="2465000"/>
-    <n v="895000"/>
+    <x v="27"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -7354,7 +7465,7 @@
     <n v="680000"/>
     <n v="6120000"/>
     <n v="4250000"/>
-    <n v="1870000"/>
+    <x v="8"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -7374,7 +7485,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4940000"/>
-    <n v="940000"/>
+    <x v="44"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -7394,7 +7505,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8550000"/>
-    <n v="3450000"/>
+    <x v="10"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -7414,7 +7525,7 @@
     <n v="1190000"/>
     <n v="4760000"/>
     <n v="3605000"/>
-    <n v="1155000"/>
+    <x v="46"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -7434,7 +7545,7 @@
     <n v="420000"/>
     <n v="3780000"/>
     <n v="2450000"/>
-    <n v="1330000"/>
+    <x v="12"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -7454,7 +7565,7 @@
     <n v="6120000"/>
     <n v="14280000"/>
     <n v="12810000"/>
-    <n v="1470000"/>
+    <x v="83"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -7474,7 +7585,7 @@
     <n v="0"/>
     <n v="12600000"/>
     <n v="7350000"/>
-    <n v="5250000"/>
+    <x v="63"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -7494,7 +7605,7 @@
     <n v="2400000"/>
     <n v="9600000"/>
     <n v="8565000"/>
-    <n v="1035000"/>
+    <x v="35"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -7514,7 +7625,7 @@
     <n v="340000"/>
     <n v="3060000"/>
     <n v="1900000"/>
-    <n v="1160000"/>
+    <x v="51"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -7534,7 +7645,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4870000"/>
-    <n v="1010000"/>
+    <x v="37"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -7554,7 +7665,7 @@
     <n v="0"/>
     <n v="17000000"/>
     <n v="10750000"/>
-    <n v="6250000"/>
+    <x v="38"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -7574,7 +7685,7 @@
     <n v="1260000"/>
     <n v="5040000"/>
     <n v="3795000"/>
-    <n v="1245000"/>
+    <x v="66"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -7594,7 +7705,7 @@
     <n v="2400000"/>
     <n v="21600000"/>
     <n v="17050000"/>
-    <n v="4550000"/>
+    <x v="0"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -7614,7 +7725,7 @@
     <n v="1530000"/>
     <n v="3570000"/>
     <n v="2910000"/>
-    <n v="660000"/>
+    <x v="54"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -7634,7 +7745,7 @@
     <n v="0"/>
     <n v="4200000"/>
     <n v="2500000"/>
-    <n v="1700000"/>
+    <x v="22"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -7654,7 +7765,7 @@
     <n v="2040000"/>
     <n v="8160000"/>
     <n v="6495000"/>
-    <n v="1665000"/>
+    <x v="3"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -7674,7 +7785,7 @@
     <n v="420000"/>
     <n v="3780000"/>
     <n v="2425000"/>
-    <n v="1355000"/>
+    <x v="57"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -7694,7 +7805,7 @@
     <n v="0"/>
     <n v="48000000"/>
     <n v="34140000"/>
-    <n v="13860000"/>
+    <x v="84"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -7714,7 +7825,7 @@
     <n v="1785000"/>
     <n v="4165000"/>
     <n v="3500000"/>
-    <n v="665000"/>
+    <x v="32"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -7734,7 +7845,7 @@
     <n v="1680000"/>
     <n v="6720000"/>
     <n v="4930000"/>
-    <n v="1790000"/>
+    <x v="59"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -7754,7 +7865,7 @@
     <n v="340000"/>
     <n v="3060000"/>
     <n v="2125000"/>
-    <n v="935000"/>
+    <x v="85"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -7774,7 +7885,7 @@
     <n v="1890000"/>
     <n v="4410000"/>
     <n v="3705000"/>
-    <n v="705000"/>
+    <x v="9"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -7794,7 +7905,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17100000"/>
-    <n v="6900000"/>
+    <x v="45"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -7814,7 +7925,7 @@
     <n v="1360000"/>
     <n v="5440000"/>
     <n v="4120000"/>
-    <n v="1320000"/>
+    <x v="11"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -7834,7 +7945,7 @@
     <n v="1050000"/>
     <n v="9450000"/>
     <n v="6125000"/>
-    <n v="3325000"/>
+    <x v="86"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -7854,7 +7965,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="4270000"/>
-    <n v="490000"/>
+    <x v="33"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -7874,7 +7985,7 @@
     <n v="0"/>
     <n v="16800000"/>
     <n v="9800000"/>
-    <n v="7000000"/>
+    <x v="34"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -7894,7 +8005,7 @@
     <n v="4800000"/>
     <n v="19200000"/>
     <n v="17130000"/>
-    <n v="2070000"/>
+    <x v="15"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -7914,7 +8025,7 @@
     <n v="255000"/>
     <n v="2295000"/>
     <n v="1425000"/>
-    <n v="870000"/>
+    <x v="36"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -7934,7 +8045,7 @@
     <n v="6300000"/>
     <n v="14700000"/>
     <n v="12175000"/>
-    <n v="2525000"/>
+    <x v="87"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -7954,7 +8065,7 @@
     <n v="0"/>
     <n v="3400000"/>
     <n v="2150000"/>
-    <n v="1250000"/>
+    <x v="65"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -7974,7 +8085,7 @@
     <n v="1680000"/>
     <n v="6720000"/>
     <n v="5060000"/>
-    <n v="1660000"/>
+    <x v="19"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -7994,7 +8105,7 @@
     <n v="3600000"/>
     <n v="32400000"/>
     <n v="25575000"/>
-    <n v="6825000"/>
+    <x v="20"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -8014,7 +8125,7 @@
     <n v="1275000"/>
     <n v="2975000"/>
     <n v="2425000"/>
-    <n v="550000"/>
+    <x v="1"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -8034,7 +8145,7 @@
     <n v="0"/>
     <n v="2100000"/>
     <n v="1250000"/>
-    <n v="850000"/>
+    <x v="2"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -8054,7 +8165,7 @@
     <n v="1360000"/>
     <n v="5440000"/>
     <n v="4330000"/>
-    <n v="1110000"/>
+    <x v="73"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -8074,7 +8185,7 @@
     <n v="1260000"/>
     <n v="11340000"/>
     <n v="7275000"/>
-    <n v="4065000"/>
+    <x v="24"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -8094,7 +8205,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8535000"/>
-    <n v="3465000"/>
+    <x v="5"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -8114,7 +8225,7 @@
     <n v="1530000"/>
     <n v="3570000"/>
     <n v="3000000"/>
-    <n v="570000"/>
+    <x v="6"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -8134,7 +8245,7 @@
     <n v="3360000"/>
     <n v="13440000"/>
     <n v="9860000"/>
-    <n v="3580000"/>
+    <x v="7"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -8154,7 +8265,7 @@
     <n v="680000"/>
     <n v="6120000"/>
     <n v="4250000"/>
-    <n v="1870000"/>
+    <x v="8"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -8174,7 +8285,7 @@
     <n v="1890000"/>
     <n v="4410000"/>
     <n v="3705000"/>
-    <n v="705000"/>
+    <x v="9"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -8194,7 +8305,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17100000"/>
-    <n v="6900000"/>
+    <x v="45"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -8214,7 +8325,7 @@
     <n v="1190000"/>
     <n v="4760000"/>
     <n v="3605000"/>
-    <n v="1155000"/>
+    <x v="46"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -8234,7 +8345,7 @@
     <n v="840000"/>
     <n v="7560000"/>
     <n v="4900000"/>
-    <n v="2660000"/>
+    <x v="62"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -8254,7 +8365,7 @@
     <n v="1020000"/>
     <n v="2380000"/>
     <n v="2135000"/>
-    <n v="245000"/>
+    <x v="48"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -8274,7 +8385,7 @@
     <n v="0"/>
     <n v="8400000"/>
     <n v="4900000"/>
-    <n v="3500000"/>
+    <x v="49"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -8294,7 +8405,7 @@
     <n v="7200000"/>
     <n v="28800000"/>
     <n v="25695000"/>
-    <n v="3105000"/>
+    <x v="50"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -8314,7 +8425,7 @@
     <n v="425000"/>
     <n v="3825000"/>
     <n v="2375000"/>
-    <n v="1450000"/>
+    <x v="16"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -8334,7 +8445,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4870000"/>
-    <n v="1010000"/>
+    <x v="37"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -8354,7 +8465,7 @@
     <n v="0"/>
     <n v="13600000"/>
     <n v="8600000"/>
-    <n v="5000000"/>
+    <x v="71"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -8374,7 +8485,7 @@
     <n v="420000"/>
     <n v="1680000"/>
     <n v="1265000"/>
-    <n v="415000"/>
+    <x v="78"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -8394,7 +8505,7 @@
     <n v="2400000"/>
     <n v="21600000"/>
     <n v="17050000"/>
-    <n v="4550000"/>
+    <x v="0"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -8414,7 +8525,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="3880000"/>
-    <n v="880000"/>
+    <x v="41"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -8434,7 +8545,7 @@
     <n v="0"/>
     <n v="6300000"/>
     <n v="3750000"/>
-    <n v="2550000"/>
+    <x v="55"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -8454,7 +8565,7 @@
     <n v="3400000"/>
     <n v="13600000"/>
     <n v="10825000"/>
-    <n v="2775000"/>
+    <x v="67"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -8474,7 +8585,7 @@
     <n v="420000"/>
     <n v="3780000"/>
     <n v="2425000"/>
-    <n v="1355000"/>
+    <x v="57"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -8494,7 +8605,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17070000"/>
-    <n v="6930000"/>
+    <x v="25"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -8514,7 +8625,7 @@
     <n v="1020000"/>
     <n v="2380000"/>
     <n v="2000000"/>
-    <n v="380000"/>
+    <x v="26"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -8534,7 +8645,7 @@
     <n v="2520000"/>
     <n v="10080000"/>
     <n v="7395000"/>
-    <n v="2685000"/>
+    <x v="43"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -8554,7 +8665,7 @@
     <n v="1020000"/>
     <n v="9180000"/>
     <n v="6375000"/>
-    <n v="2805000"/>
+    <x v="60"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -8574,7 +8685,7 @@
     <n v="1260000"/>
     <n v="2940000"/>
     <n v="2470000"/>
-    <n v="470000"/>
+    <x v="29"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -8594,7 +8705,7 @@
     <n v="0"/>
     <n v="48000000"/>
     <n v="34200000"/>
-    <n v="13800000"/>
+    <x v="75"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -8614,7 +8725,7 @@
     <n v="1020000"/>
     <n v="4080000"/>
     <n v="3090000"/>
-    <n v="990000"/>
+    <x v="31"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -8634,7 +8745,7 @@
     <n v="210000"/>
     <n v="1890000"/>
     <n v="1225000"/>
-    <n v="665000"/>
+    <x v="32"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -8654,7 +8765,7 @@
     <n v="4080000"/>
     <n v="9520000"/>
     <n v="8540000"/>
-    <n v="980000"/>
+    <x v="13"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -8674,7 +8785,7 @@
     <n v="0"/>
     <n v="8400000"/>
     <n v="4900000"/>
-    <n v="3500000"/>
+    <x v="49"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -8694,7 +8805,7 @@
     <n v="2400000"/>
     <n v="9600000"/>
     <n v="8565000"/>
-    <n v="1035000"/>
+    <x v="35"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -8714,7 +8825,7 @@
     <n v="425000"/>
     <n v="3825000"/>
     <n v="2375000"/>
-    <n v="1450000"/>
+    <x v="16"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -8734,7 +8845,7 @@
     <n v="3780000"/>
     <n v="8820000"/>
     <n v="7305000"/>
-    <n v="1515000"/>
+    <x v="17"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -8754,7 +8865,7 @@
     <n v="0"/>
     <n v="6800000"/>
     <n v="4300000"/>
-    <n v="2500000"/>
+    <x v="18"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -8774,7 +8885,7 @@
     <n v="1680000"/>
     <n v="6720000"/>
     <n v="5060000"/>
-    <n v="1660000"/>
+    <x v="19"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -8794,7 +8905,7 @@
     <n v="3600000"/>
     <n v="32400000"/>
     <n v="25575000"/>
-    <n v="6825000"/>
+    <x v="20"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -8814,7 +8925,7 @@
     <n v="1785000"/>
     <n v="4165000"/>
     <n v="3395000"/>
-    <n v="770000"/>
+    <x v="21"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -8834,7 +8945,7 @@
     <n v="0"/>
     <n v="4200000"/>
     <n v="2500000"/>
-    <n v="1700000"/>
+    <x v="22"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -8854,7 +8965,7 @@
     <n v="680000"/>
     <n v="2720000"/>
     <n v="2165000"/>
-    <n v="555000"/>
+    <x v="23"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -8874,7 +8985,7 @@
     <n v="1680000"/>
     <n v="15120000"/>
     <n v="9700000"/>
-    <n v="5420000"/>
+    <x v="74"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -8894,7 +9005,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17070000"/>
-    <n v="6930000"/>
+    <x v="25"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -8914,7 +9025,7 @@
     <n v="1530000"/>
     <n v="3570000"/>
     <n v="3000000"/>
-    <n v="570000"/>
+    <x v="6"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -8934,7 +9045,7 @@
     <n v="840000"/>
     <n v="3360000"/>
     <n v="2465000"/>
-    <n v="895000"/>
+    <x v="27"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -8954,7 +9065,7 @@
     <n v="1700000"/>
     <n v="15300000"/>
     <n v="10625000"/>
-    <n v="4675000"/>
+    <x v="28"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -8974,7 +9085,7 @@
     <n v="1890000"/>
     <n v="4410000"/>
     <n v="3705000"/>
-    <n v="705000"/>
+    <x v="9"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -8994,7 +9105,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8550000"/>
-    <n v="3450000"/>
+    <x v="10"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -9014,7 +9125,7 @@
     <n v="1360000"/>
     <n v="5440000"/>
     <n v="4120000"/>
-    <n v="1320000"/>
+    <x v="11"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -9034,7 +9145,7 @@
     <n v="420000"/>
     <n v="3780000"/>
     <n v="2450000"/>
-    <n v="1330000"/>
+    <x v="12"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -9054,7 +9165,7 @@
     <n v="3060000"/>
     <n v="7140000"/>
     <n v="6405000"/>
-    <n v="735000"/>
+    <x v="69"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -9074,7 +9185,7 @@
     <n v="0"/>
     <n v="16800000"/>
     <n v="9800000"/>
-    <n v="7000000"/>
+    <x v="34"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -9094,7 +9205,7 @@
     <n v="4800000"/>
     <n v="19200000"/>
     <n v="17130000"/>
-    <n v="2070000"/>
+    <x v="15"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -9114,7 +9225,7 @@
     <n v="255000"/>
     <n v="2295000"/>
     <n v="1425000"/>
-    <n v="870000"/>
+    <x v="36"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -9134,7 +9245,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4870000"/>
-    <n v="1010000"/>
+    <x v="37"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -9154,7 +9265,7 @@
     <n v="0"/>
     <n v="20400000"/>
     <n v="12900000"/>
-    <n v="7500000"/>
+    <x v="53"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -9174,7 +9285,7 @@
     <n v="420000"/>
     <n v="1680000"/>
     <n v="1265000"/>
-    <n v="415000"/>
+    <x v="78"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -9194,7 +9305,7 @@
     <n v="4800000"/>
     <n v="43200000"/>
     <n v="34100000"/>
-    <n v="9100000"/>
+    <x v="40"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -9214,7 +9325,7 @@
     <n v="1275000"/>
     <n v="2975000"/>
     <n v="2425000"/>
-    <n v="550000"/>
+    <x v="1"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -9234,7 +9345,7 @@
     <n v="0"/>
     <n v="6300000"/>
     <n v="3750000"/>
-    <n v="2550000"/>
+    <x v="55"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -9254,7 +9365,7 @@
     <n v="1360000"/>
     <n v="5440000"/>
     <n v="4330000"/>
-    <n v="1110000"/>
+    <x v="73"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -9274,7 +9385,7 @@
     <n v="840000"/>
     <n v="7560000"/>
     <n v="4850000"/>
-    <n v="2710000"/>
+    <x v="4"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -9294,7 +9405,7 @@
     <n v="0"/>
     <n v="36000000"/>
     <n v="25605000"/>
-    <n v="10395000"/>
+    <x v="58"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -9314,7 +9425,7 @@
     <n v="1785000"/>
     <n v="4165000"/>
     <n v="3500000"/>
-    <n v="665000"/>
+    <x v="32"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -9334,7 +9445,7 @@
     <n v="3360000"/>
     <n v="13440000"/>
     <n v="9860000"/>
-    <n v="3580000"/>
+    <x v="7"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -9354,7 +9465,7 @@
     <n v="340000"/>
     <n v="3060000"/>
     <n v="2125000"/>
-    <n v="935000"/>
+    <x v="85"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -9374,7 +9485,7 @@
     <n v="1260000"/>
     <n v="2940000"/>
     <n v="2470000"/>
-    <n v="470000"/>
+    <x v="29"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -9394,7 +9505,7 @@
     <n v="0"/>
     <n v="36000000"/>
     <n v="25650000"/>
-    <n v="10350000"/>
+    <x v="30"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -9414,7 +9525,7 @@
     <n v="1020000"/>
     <n v="4080000"/>
     <n v="3090000"/>
-    <n v="990000"/>
+    <x v="31"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -9434,7 +9545,7 @@
     <n v="1050000"/>
     <n v="9450000"/>
     <n v="6125000"/>
-    <n v="3325000"/>
+    <x v="86"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -9454,7 +9565,7 @@
     <n v="4080000"/>
     <n v="9520000"/>
     <n v="8540000"/>
-    <n v="980000"/>
+    <x v="13"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -9474,7 +9585,7 @@
     <n v="0"/>
     <n v="4200000"/>
     <n v="2450000"/>
-    <n v="1750000"/>
+    <x v="14"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -9494,7 +9605,7 @@
     <n v="4800000"/>
     <n v="19200000"/>
     <n v="17130000"/>
-    <n v="2070000"/>
+    <x v="15"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -9514,7 +9625,7 @@
     <n v="340000"/>
     <n v="3060000"/>
     <n v="1900000"/>
-    <n v="1160000"/>
+    <x v="51"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -9534,7 +9645,7 @@
     <n v="3780000"/>
     <n v="8820000"/>
     <n v="7305000"/>
-    <n v="1515000"/>
+    <x v="17"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -9554,7 +9665,7 @@
     <n v="0"/>
     <n v="6800000"/>
     <n v="4300000"/>
-    <n v="2500000"/>
+    <x v="18"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -9574,7 +9685,7 @@
     <n v="1260000"/>
     <n v="5040000"/>
     <n v="3795000"/>
-    <n v="1245000"/>
+    <x v="66"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -9594,7 +9705,7 @@
     <n v="1200000"/>
     <n v="10800000"/>
     <n v="8525000"/>
-    <n v="2275000"/>
+    <x v="72"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -9614,7 +9725,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="3880000"/>
-    <n v="880000"/>
+    <x v="41"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -9634,7 +9745,7 @@
     <n v="0"/>
     <n v="4200000"/>
     <n v="2500000"/>
-    <n v="1700000"/>
+    <x v="22"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -9654,7 +9765,7 @@
     <n v="3400000"/>
     <n v="13600000"/>
     <n v="10825000"/>
-    <n v="2775000"/>
+    <x v="67"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -9674,7 +9785,7 @@
     <n v="1260000"/>
     <n v="11340000"/>
     <n v="7275000"/>
-    <n v="4065000"/>
+    <x v="24"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -9694,7 +9805,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8535000"/>
-    <n v="3465000"/>
+    <x v="5"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -9714,7 +9825,7 @@
     <n v="1275000"/>
     <n v="2975000"/>
     <n v="2500000"/>
-    <n v="475000"/>
+    <x v="42"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -9734,7 +9845,7 @@
     <n v="1680000"/>
     <n v="6720000"/>
     <n v="4930000"/>
-    <n v="1790000"/>
+    <x v="59"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -9754,7 +9865,7 @@
     <n v="1360000"/>
     <n v="12240000"/>
     <n v="8500000"/>
-    <n v="3740000"/>
+    <x v="80"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -9774,7 +9885,7 @@
     <n v="630000"/>
     <n v="1470000"/>
     <n v="1235000"/>
-    <n v="235000"/>
+    <x v="61"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -9794,7 +9905,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17100000"/>
-    <n v="6900000"/>
+    <x v="45"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -9814,7 +9925,7 @@
     <n v="1190000"/>
     <n v="4760000"/>
     <n v="3605000"/>
-    <n v="1155000"/>
+    <x v="46"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -9834,7 +9945,7 @@
     <n v="630000"/>
     <n v="5670000"/>
     <n v="3675000"/>
-    <n v="1995000"/>
+    <x v="47"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -9854,7 +9965,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="4270000"/>
-    <n v="490000"/>
+    <x v="33"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -9874,7 +9985,7 @@
     <n v="0"/>
     <n v="16800000"/>
     <n v="9800000"/>
-    <n v="7000000"/>
+    <x v="34"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -9894,7 +10005,7 @@
     <n v="7200000"/>
     <n v="28800000"/>
     <n v="25695000"/>
-    <n v="3105000"/>
+    <x v="50"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -9914,7 +10025,7 @@
     <n v="510000"/>
     <n v="4590000"/>
     <n v="2850000"/>
-    <n v="1740000"/>
+    <x v="88"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -9934,7 +10045,7 @@
     <n v="1260000"/>
     <n v="2940000"/>
     <n v="2435000"/>
-    <n v="505000"/>
+    <x v="52"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -9954,7 +10065,7 @@
     <n v="0"/>
     <n v="10200000"/>
     <n v="6450000"/>
-    <n v="3750000"/>
+    <x v="77"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -9974,7 +10085,7 @@
     <n v="840000"/>
     <n v="3360000"/>
     <n v="2530000"/>
-    <n v="830000"/>
+    <x v="39"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -9994,7 +10105,7 @@
     <n v="2400000"/>
     <n v="21600000"/>
     <n v="17050000"/>
-    <n v="4550000"/>
+    <x v="0"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -10014,7 +10125,7 @@
     <n v="1275000"/>
     <n v="2975000"/>
     <n v="2425000"/>
-    <n v="550000"/>
+    <x v="1"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -10034,7 +10145,7 @@
     <n v="0"/>
     <n v="8400000"/>
     <n v="5000000"/>
-    <n v="3400000"/>
+    <x v="79"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -10054,7 +10165,7 @@
     <n v="680000"/>
     <n v="2720000"/>
     <n v="2165000"/>
-    <n v="555000"/>
+    <x v="23"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -10074,7 +10185,7 @@
     <n v="840000"/>
     <n v="7560000"/>
     <n v="4850000"/>
-    <n v="2710000"/>
+    <x v="4"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -10094,7 +10205,7 @@
     <n v="0"/>
     <n v="36000000"/>
     <n v="25605000"/>
-    <n v="10395000"/>
+    <x v="58"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -10114,7 +10225,7 @@
     <n v="1785000"/>
     <n v="4165000"/>
     <n v="3500000"/>
-    <n v="665000"/>
+    <x v="32"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -10134,7 +10245,7 @@
     <n v="2520000"/>
     <n v="10080000"/>
     <n v="7395000"/>
-    <n v="2685000"/>
+    <x v="43"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -10154,7 +10265,7 @@
     <n v="680000"/>
     <n v="6120000"/>
     <n v="4250000"/>
-    <n v="1870000"/>
+    <x v="8"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -10174,7 +10285,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4940000"/>
-    <n v="940000"/>
+    <x v="44"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -10194,7 +10305,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8550000"/>
-    <n v="3450000"/>
+    <x v="10"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -10214,7 +10325,7 @@
     <n v="1020000"/>
     <n v="4080000"/>
     <n v="3090000"/>
-    <n v="990000"/>
+    <x v="31"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -10234,7 +10345,7 @@
     <n v="420000"/>
     <n v="3780000"/>
     <n v="2450000"/>
-    <n v="1330000"/>
+    <x v="12"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -10254,7 +10365,7 @@
     <n v="5100000"/>
     <n v="11900000"/>
     <n v="10675000"/>
-    <n v="1225000"/>
+    <x v="76"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -10274,7 +10385,7 @@
     <n v="0"/>
     <n v="12600000"/>
     <n v="7350000"/>
-    <n v="5250000"/>
+    <x v="63"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -10294,7 +10405,7 @@
     <n v="2400000"/>
     <n v="9600000"/>
     <n v="8565000"/>
-    <n v="1035000"/>
+    <x v="35"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -10314,7 +10425,7 @@
     <n v="680000"/>
     <n v="6120000"/>
     <n v="3800000"/>
-    <n v="2320000"/>
+    <x v="89"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -10334,7 +10445,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4870000"/>
-    <n v="1010000"/>
+    <x v="37"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -10354,7 +10465,7 @@
     <n v="0"/>
     <n v="13600000"/>
     <n v="8600000"/>
-    <n v="5000000"/>
+    <x v="71"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -10374,7 +10485,7 @@
     <n v="420000"/>
     <n v="1680000"/>
     <n v="1265000"/>
-    <n v="415000"/>
+    <x v="78"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -10394,7 +10505,7 @@
     <n v="3600000"/>
     <n v="32400000"/>
     <n v="25575000"/>
-    <n v="6825000"/>
+    <x v="20"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -10414,7 +10525,7 @@
     <n v="1020000"/>
     <n v="2380000"/>
     <n v="1940000"/>
-    <n v="440000"/>
+    <x v="90"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -10434,7 +10545,7 @@
     <n v="0"/>
     <n v="4200000"/>
     <n v="2500000"/>
-    <n v="1700000"/>
+    <x v="22"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -10454,7 +10565,7 @@
     <n v="2040000"/>
     <n v="8160000"/>
     <n v="6495000"/>
-    <n v="1665000"/>
+    <x v="3"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -10474,7 +10585,7 @@
     <n v="1680000"/>
     <n v="15120000"/>
     <n v="9700000"/>
-    <n v="5420000"/>
+    <x v="74"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -10494,7 +10605,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8535000"/>
-    <n v="3465000"/>
+    <x v="5"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -10514,7 +10625,7 @@
     <n v="1530000"/>
     <n v="3570000"/>
     <n v="3000000"/>
-    <n v="570000"/>
+    <x v="6"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -10534,7 +10645,7 @@
     <n v="1680000"/>
     <n v="6720000"/>
     <n v="4930000"/>
-    <n v="1790000"/>
+    <x v="59"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -10554,7 +10665,7 @@
     <n v="1700000"/>
     <n v="15300000"/>
     <n v="10625000"/>
-    <n v="4675000"/>
+    <x v="28"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -10574,7 +10685,7 @@
     <n v="1890000"/>
     <n v="4410000"/>
     <n v="3705000"/>
-    <n v="705000"/>
+    <x v="9"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -10594,7 +10705,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17100000"/>
-    <n v="6900000"/>
+    <x v="45"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -10614,7 +10725,7 @@
     <n v="1190000"/>
     <n v="4760000"/>
     <n v="3605000"/>
-    <n v="1155000"/>
+    <x v="46"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -10634,7 +10745,7 @@
     <n v="210000"/>
     <n v="1890000"/>
     <n v="1225000"/>
-    <n v="665000"/>
+    <x v="32"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -10654,7 +10765,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="4270000"/>
-    <n v="490000"/>
+    <x v="33"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -10674,7 +10785,7 @@
     <n v="0"/>
     <n v="21000000"/>
     <n v="12250000"/>
-    <n v="8750000"/>
+    <x v="81"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -10694,7 +10805,7 @@
     <n v="4800000"/>
     <n v="19200000"/>
     <n v="17130000"/>
-    <n v="2070000"/>
+    <x v="15"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -10714,7 +10825,7 @@
     <n v="340000"/>
     <n v="3060000"/>
     <n v="1900000"/>
-    <n v="1160000"/>
+    <x v="51"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -10734,7 +10845,7 @@
     <n v="3780000"/>
     <n v="8820000"/>
     <n v="7305000"/>
-    <n v="1515000"/>
+    <x v="17"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -10754,7 +10865,7 @@
     <n v="0"/>
     <n v="3400000"/>
     <n v="2150000"/>
-    <n v="1250000"/>
+    <x v="65"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -10774,7 +10885,7 @@
     <n v="1680000"/>
     <n v="6720000"/>
     <n v="5060000"/>
-    <n v="1660000"/>
+    <x v="19"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -10794,7 +10905,7 @@
     <n v="3600000"/>
     <n v="32400000"/>
     <n v="25575000"/>
-    <n v="6825000"/>
+    <x v="20"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -10814,7 +10925,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="3880000"/>
-    <n v="880000"/>
+    <x v="41"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -10834,7 +10945,7 @@
     <n v="0"/>
     <n v="4200000"/>
     <n v="2500000"/>
-    <n v="1700000"/>
+    <x v="22"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -10854,7 +10965,7 @@
     <n v="2720000"/>
     <n v="10880000"/>
     <n v="8660000"/>
-    <n v="2220000"/>
+    <x v="56"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -10874,7 +10985,7 @@
     <n v="420000"/>
     <n v="3780000"/>
     <n v="2425000"/>
-    <n v="1355000"/>
+    <x v="57"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -10894,7 +11005,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17070000"/>
-    <n v="6930000"/>
+    <x v="25"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -10914,7 +11025,7 @@
     <n v="1275000"/>
     <n v="2975000"/>
     <n v="2500000"/>
-    <n v="475000"/>
+    <x v="42"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -10934,7 +11045,7 @@
     <n v="3360000"/>
     <n v="13440000"/>
     <n v="9860000"/>
-    <n v="3580000"/>
+    <x v="7"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -10954,7 +11065,7 @@
     <n v="680000"/>
     <n v="6120000"/>
     <n v="4250000"/>
-    <n v="1870000"/>
+    <x v="8"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -10974,7 +11085,7 @@
     <n v="630000"/>
     <n v="1470000"/>
     <n v="1235000"/>
-    <n v="235000"/>
+    <x v="61"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -10994,7 +11105,7 @@
     <n v="0"/>
     <n v="48000000"/>
     <n v="34200000"/>
-    <n v="13800000"/>
+    <x v="75"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -11014,7 +11125,7 @@
     <n v="1020000"/>
     <n v="4080000"/>
     <n v="3090000"/>
-    <n v="990000"/>
+    <x v="31"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -11034,7 +11145,7 @@
     <n v="630000"/>
     <n v="5670000"/>
     <n v="3675000"/>
-    <n v="1995000"/>
+    <x v="47"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -11054,7 +11165,7 @@
     <n v="5100000"/>
     <n v="11900000"/>
     <n v="10675000"/>
-    <n v="1225000"/>
+    <x v="76"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -11074,7 +11185,7 @@
     <n v="0"/>
     <n v="8400000"/>
     <n v="4900000"/>
-    <n v="3500000"/>
+    <x v="49"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -11094,7 +11205,7 @@
     <n v="2400000"/>
     <n v="9600000"/>
     <n v="8565000"/>
-    <n v="1035000"/>
+    <x v="35"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -11114,7 +11225,7 @@
     <n v="595000"/>
     <n v="5355000"/>
     <n v="3325000"/>
-    <n v="2030000"/>
+    <x v="70"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -11134,7 +11245,7 @@
     <n v="3780000"/>
     <n v="8820000"/>
     <n v="7305000"/>
-    <n v="1515000"/>
+    <x v="17"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -11154,7 +11265,7 @@
     <n v="0"/>
     <n v="13600000"/>
     <n v="8600000"/>
-    <n v="5000000"/>
+    <x v="71"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -11174,7 +11285,7 @@
     <n v="840000"/>
     <n v="3360000"/>
     <n v="2530000"/>
-    <n v="830000"/>
+    <x v="39"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -11194,7 +11305,7 @@
     <n v="4800000"/>
     <n v="43200000"/>
     <n v="34100000"/>
-    <n v="9100000"/>
+    <x v="40"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -11214,7 +11325,7 @@
     <n v="1530000"/>
     <n v="3570000"/>
     <n v="2910000"/>
-    <n v="660000"/>
+    <x v="54"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -11234,7 +11345,7 @@
     <n v="0"/>
     <n v="2100000"/>
     <n v="1250000"/>
-    <n v="850000"/>
+    <x v="2"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -11254,7 +11365,7 @@
     <n v="2040000"/>
     <n v="8160000"/>
     <n v="6495000"/>
-    <n v="1665000"/>
+    <x v="3"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -11274,7 +11385,7 @@
     <n v="840000"/>
     <n v="7560000"/>
     <n v="4850000"/>
-    <n v="2710000"/>
+    <x v="4"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -11294,7 +11405,7 @@
     <n v="0"/>
     <n v="60000000"/>
     <n v="42675000"/>
-    <n v="17325000"/>
+    <x v="91"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -11314,7 +11425,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="4000000"/>
-    <n v="760000"/>
+    <x v="92"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -11334,7 +11445,7 @@
     <n v="840000"/>
     <n v="3360000"/>
     <n v="2465000"/>
-    <n v="895000"/>
+    <x v="27"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -11354,7 +11465,7 @@
     <n v="1020000"/>
     <n v="9180000"/>
     <n v="6375000"/>
-    <n v="2805000"/>
+    <x v="60"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -11374,7 +11485,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4940000"/>
-    <n v="940000"/>
+    <x v="44"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -11394,7 +11505,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17100000"/>
-    <n v="6900000"/>
+    <x v="45"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -11414,7 +11525,7 @@
     <n v="850000"/>
     <n v="3400000"/>
     <n v="2575000"/>
-    <n v="825000"/>
+    <x v="93"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -11434,7 +11545,7 @@
     <n v="420000"/>
     <n v="3780000"/>
     <n v="2450000"/>
-    <n v="1330000"/>
+    <x v="12"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -11454,7 +11565,7 @@
     <n v="1020000"/>
     <n v="2380000"/>
     <n v="2135000"/>
-    <n v="245000"/>
+    <x v="48"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -11474,7 +11585,7 @@
     <n v="0"/>
     <n v="12600000"/>
     <n v="7350000"/>
-    <n v="5250000"/>
+    <x v="63"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -11494,7 +11605,7 @@
     <n v="4800000"/>
     <n v="19200000"/>
     <n v="17130000"/>
-    <n v="2070000"/>
+    <x v="15"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -11514,7 +11625,7 @@
     <n v="510000"/>
     <n v="4590000"/>
     <n v="2850000"/>
-    <n v="1740000"/>
+    <x v="88"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -11534,7 +11645,7 @@
     <n v="5040000"/>
     <n v="11760000"/>
     <n v="9740000"/>
-    <n v="2020000"/>
+    <x v="64"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -11554,7 +11665,7 @@
     <n v="0"/>
     <n v="6800000"/>
     <n v="4300000"/>
-    <n v="2500000"/>
+    <x v="18"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -11574,7 +11685,7 @@
     <n v="1260000"/>
     <n v="5040000"/>
     <n v="3795000"/>
-    <n v="1245000"/>
+    <x v="66"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -11594,7 +11705,7 @@
     <n v="3600000"/>
     <n v="32400000"/>
     <n v="25575000"/>
-    <n v="6825000"/>
+    <x v="20"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -11614,7 +11725,7 @@
     <n v="1785000"/>
     <n v="4165000"/>
     <n v="3395000"/>
-    <n v="770000"/>
+    <x v="21"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -11634,7 +11745,7 @@
     <n v="0"/>
     <n v="2100000"/>
     <n v="1250000"/>
-    <n v="850000"/>
+    <x v="2"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -11654,7 +11765,7 @@
     <n v="2720000"/>
     <n v="10880000"/>
     <n v="8660000"/>
-    <n v="2220000"/>
+    <x v="56"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -11674,7 +11785,7 @@
     <n v="2100000"/>
     <n v="18900000"/>
     <n v="12125000"/>
-    <n v="6775000"/>
+    <x v="94"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -11694,7 +11805,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17070000"/>
-    <n v="6930000"/>
+    <x v="25"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -11714,7 +11825,7 @@
     <n v="1530000"/>
     <n v="3570000"/>
     <n v="3000000"/>
-    <n v="570000"/>
+    <x v="6"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -11734,7 +11845,7 @@
     <n v="2040000"/>
     <n v="8160000"/>
     <n v="6495000"/>
-    <n v="1665000"/>
+    <x v="3"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -11754,7 +11865,7 @@
     <n v="840000"/>
     <n v="7560000"/>
     <n v="4900000"/>
-    <n v="2660000"/>
+    <x v="62"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -11774,7 +11885,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4870000"/>
-    <n v="1010000"/>
+    <x v="37"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -11794,7 +11905,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8550000"/>
-    <n v="3450000"/>
+    <x v="10"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -11814,7 +11925,7 @@
     <n v="1190000"/>
     <n v="4760000"/>
     <n v="3605000"/>
-    <n v="1155000"/>
+    <x v="46"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -11834,7 +11945,7 @@
     <n v="1700000"/>
     <n v="15300000"/>
     <n v="10625000"/>
-    <n v="4675000"/>
+    <x v="28"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -11854,7 +11965,7 @@
     <n v="1260000"/>
     <n v="2940000"/>
     <n v="2470000"/>
-    <n v="470000"/>
+    <x v="29"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -11874,7 +11985,7 @@
     <n v="0"/>
     <n v="12600000"/>
     <n v="7350000"/>
-    <n v="5250000"/>
+    <x v="63"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -11894,7 +12005,7 @@
     <n v="4800000"/>
     <n v="19200000"/>
     <n v="17130000"/>
-    <n v="2070000"/>
+    <x v="15"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -11914,7 +12025,7 @@
     <n v="680000"/>
     <n v="6120000"/>
     <n v="3800000"/>
-    <n v="2320000"/>
+    <x v="89"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -11934,7 +12045,7 @@
     <n v="1020000"/>
     <n v="2380000"/>
     <n v="2135000"/>
-    <n v="245000"/>
+    <x v="48"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -11954,7 +12065,7 @@
     <n v="0"/>
     <n v="6300000"/>
     <n v="3750000"/>
-    <n v="2550000"/>
+    <x v="55"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -11974,7 +12085,7 @@
     <n v="3360000"/>
     <n v="13440000"/>
     <n v="9860000"/>
-    <n v="3580000"/>
+    <x v="7"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -11994,7 +12105,7 @@
     <n v="3600000"/>
     <n v="32400000"/>
     <n v="25575000"/>
-    <n v="6825000"/>
+    <x v="20"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -12014,7 +12125,7 @@
     <n v="1275000"/>
     <n v="2975000"/>
     <n v="2425000"/>
-    <n v="550000"/>
+    <x v="1"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -12034,7 +12145,7 @@
     <n v="0"/>
     <n v="6800000"/>
     <n v="4300000"/>
-    <n v="2500000"/>
+    <x v="18"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -12054,7 +12165,7 @@
     <n v="1680000"/>
     <n v="6720000"/>
     <n v="5060000"/>
-    <n v="1660000"/>
+    <x v="19"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -12074,7 +12185,7 @@
     <n v="420000"/>
     <n v="3780000"/>
     <n v="2425000"/>
-    <n v="1355000"/>
+    <x v="57"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -12094,7 +12205,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17070000"/>
-    <n v="6930000"/>
+    <x v="25"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -12114,7 +12225,7 @@
     <n v="1530000"/>
     <n v="3570000"/>
     <n v="3000000"/>
-    <n v="570000"/>
+    <x v="6"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -12134,7 +12245,7 @@
     <n v="2040000"/>
     <n v="8160000"/>
     <n v="6495000"/>
-    <n v="1665000"/>
+    <x v="3"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -12154,7 +12265,7 @@
     <n v="1050000"/>
     <n v="9450000"/>
     <n v="6125000"/>
-    <n v="3325000"/>
+    <x v="86"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -12174,7 +12285,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4870000"/>
-    <n v="1010000"/>
+    <x v="37"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -12194,7 +12305,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8550000"/>
-    <n v="3450000"/>
+    <x v="10"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -12214,7 +12325,7 @@
     <n v="1190000"/>
     <n v="4760000"/>
     <n v="3605000"/>
-    <n v="1155000"/>
+    <x v="46"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -12234,7 +12345,7 @@
     <n v="1360000"/>
     <n v="12240000"/>
     <n v="8500000"/>
-    <n v="3740000"/>
+    <x v="80"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -12254,7 +12365,7 @@
     <n v="1890000"/>
     <n v="4410000"/>
     <n v="3705000"/>
-    <n v="705000"/>
+    <x v="9"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -12274,7 +12385,7 @@
     <n v="0"/>
     <n v="8400000"/>
     <n v="4900000"/>
-    <n v="3500000"/>
+    <x v="49"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -12294,7 +12405,7 @@
     <n v="7200000"/>
     <n v="28800000"/>
     <n v="25695000"/>
-    <n v="3105000"/>
+    <x v="50"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -12314,7 +12425,7 @@
     <n v="510000"/>
     <n v="4590000"/>
     <n v="2850000"/>
-    <n v="1740000"/>
+    <x v="88"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -12334,7 +12445,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="4270000"/>
-    <n v="490000"/>
+    <x v="33"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -12354,7 +12465,7 @@
     <n v="0"/>
     <n v="8400000"/>
     <n v="5000000"/>
-    <n v="3400000"/>
+    <x v="79"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -12374,7 +12485,7 @@
     <n v="840000"/>
     <n v="3360000"/>
     <n v="2465000"/>
-    <n v="895000"/>
+    <x v="27"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -12394,7 +12505,7 @@
     <n v="2400000"/>
     <n v="21600000"/>
     <n v="17050000"/>
-    <n v="4550000"/>
+    <x v="0"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -12414,7 +12525,7 @@
     <n v="1275000"/>
     <n v="2975000"/>
     <n v="2425000"/>
-    <n v="550000"/>
+    <x v="1"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -12434,7 +12545,7 @@
     <n v="0"/>
     <n v="10200000"/>
     <n v="6450000"/>
-    <n v="3750000"/>
+    <x v="77"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -12454,7 +12565,7 @@
     <n v="840000"/>
     <n v="3360000"/>
     <n v="2530000"/>
-    <n v="830000"/>
+    <x v="39"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -12474,7 +12585,7 @@
     <n v="1680000"/>
     <n v="15120000"/>
     <n v="9700000"/>
-    <n v="5420000"/>
+    <x v="74"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -12494,7 +12605,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8535000"/>
-    <n v="3465000"/>
+    <x v="5"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -12514,7 +12625,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="4000000"/>
-    <n v="760000"/>
+    <x v="92"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -12534,7 +12645,7 @@
     <n v="1360000"/>
     <n v="5440000"/>
     <n v="4330000"/>
-    <n v="1110000"/>
+    <x v="73"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -12554,7 +12665,7 @@
     <n v="630000"/>
     <n v="5670000"/>
     <n v="3675000"/>
-    <n v="1995000"/>
+    <x v="47"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -12574,7 +12685,7 @@
     <n v="6300000"/>
     <n v="14700000"/>
     <n v="12175000"/>
-    <n v="2525000"/>
+    <x v="87"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -12594,7 +12705,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17100000"/>
-    <n v="6900000"/>
+    <x v="45"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -12614,7 +12725,7 @@
     <n v="1020000"/>
     <n v="4080000"/>
     <n v="3090000"/>
-    <n v="990000"/>
+    <x v="31"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -12634,7 +12745,7 @@
     <n v="340000"/>
     <n v="3060000"/>
     <n v="2125000"/>
-    <n v="935000"/>
+    <x v="85"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -12654,7 +12765,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4940000"/>
-    <n v="940000"/>
+    <x v="44"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -12674,7 +12785,7 @@
     <n v="0"/>
     <n v="12600000"/>
     <n v="7350000"/>
-    <n v="5250000"/>
+    <x v="63"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -12694,7 +12805,7 @@
     <n v="4800000"/>
     <n v="19200000"/>
     <n v="17130000"/>
-    <n v="2070000"/>
+    <x v="15"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -12714,7 +12825,7 @@
     <n v="595000"/>
     <n v="5355000"/>
     <n v="3325000"/>
-    <n v="2030000"/>
+    <x v="70"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -12734,7 +12845,7 @@
     <n v="3060000"/>
     <n v="7140000"/>
     <n v="6405000"/>
-    <n v="735000"/>
+    <x v="69"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -12754,7 +12865,7 @@
     <n v="0"/>
     <n v="4200000"/>
     <n v="2500000"/>
-    <n v="1700000"/>
+    <x v="22"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -12774,7 +12885,7 @@
     <n v="840000"/>
     <n v="3360000"/>
     <n v="2465000"/>
-    <n v="895000"/>
+    <x v="27"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -12794,7 +12905,7 @@
     <n v="4800000"/>
     <n v="43200000"/>
     <n v="34100000"/>
-    <n v="9100000"/>
+    <x v="40"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -12814,7 +12925,7 @@
     <n v="1530000"/>
     <n v="3570000"/>
     <n v="2910000"/>
-    <n v="660000"/>
+    <x v="54"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -12834,7 +12945,7 @@
     <n v="0"/>
     <n v="6800000"/>
     <n v="4300000"/>
-    <n v="2500000"/>
+    <x v="18"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -12854,7 +12965,7 @@
     <n v="2100000"/>
     <n v="8400000"/>
     <n v="6325000"/>
-    <n v="2075000"/>
+    <x v="82"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -12874,7 +12985,7 @@
     <n v="840000"/>
     <n v="7560000"/>
     <n v="4850000"/>
-    <n v="2710000"/>
+    <x v="4"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -12894,7 +13005,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8535000"/>
-    <n v="3465000"/>
+    <x v="5"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -12914,7 +13025,7 @@
     <n v="1785000"/>
     <n v="4165000"/>
     <n v="3500000"/>
-    <n v="665000"/>
+    <x v="32"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -12934,7 +13045,7 @@
     <n v="2720000"/>
     <n v="10880000"/>
     <n v="8660000"/>
-    <n v="2220000"/>
+    <x v="56"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -12954,7 +13065,7 @@
     <n v="630000"/>
     <n v="5670000"/>
     <n v="3675000"/>
-    <n v="1995000"/>
+    <x v="47"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -12974,7 +13085,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4870000"/>
-    <n v="1010000"/>
+    <x v="37"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -12994,7 +13105,7 @@
     <n v="0"/>
     <n v="36000000"/>
     <n v="25650000"/>
-    <n v="10350000"/>
+    <x v="30"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -13014,7 +13125,7 @@
     <n v="850000"/>
     <n v="3400000"/>
     <n v="2575000"/>
-    <n v="825000"/>
+    <x v="93"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -13034,7 +13145,7 @@
     <n v="680000"/>
     <n v="6120000"/>
     <n v="4250000"/>
-    <n v="1870000"/>
+    <x v="8"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -13054,7 +13165,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4940000"/>
-    <n v="940000"/>
+    <x v="44"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -13074,7 +13185,7 @@
     <n v="0"/>
     <n v="4200000"/>
     <n v="2450000"/>
-    <n v="1750000"/>
+    <x v="14"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -13094,7 +13205,7 @@
     <n v="4800000"/>
     <n v="19200000"/>
     <n v="17130000"/>
-    <n v="2070000"/>
+    <x v="15"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -13114,7 +13225,7 @@
     <n v="680000"/>
     <n v="6120000"/>
     <n v="3800000"/>
-    <n v="2320000"/>
+    <x v="89"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -13134,7 +13245,7 @@
     <n v="3060000"/>
     <n v="7140000"/>
     <n v="6405000"/>
-    <n v="735000"/>
+    <x v="69"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -13154,7 +13265,7 @@
     <n v="0"/>
     <n v="4200000"/>
     <n v="2500000"/>
-    <n v="1700000"/>
+    <x v="22"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -13174,7 +13285,7 @@
     <n v="4200000"/>
     <n v="16800000"/>
     <n v="12325000"/>
-    <n v="4475000"/>
+    <x v="95"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -13194,7 +13305,7 @@
     <n v="1200000"/>
     <n v="10800000"/>
     <n v="8525000"/>
-    <n v="2275000"/>
+    <x v="72"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -13214,7 +13325,7 @@
     <n v="1530000"/>
     <n v="3570000"/>
     <n v="2910000"/>
-    <n v="660000"/>
+    <x v="54"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -13234,7 +13345,7 @@
     <n v="0"/>
     <n v="13600000"/>
     <n v="8600000"/>
-    <n v="5000000"/>
+    <x v="71"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -13254,7 +13365,7 @@
     <n v="840000"/>
     <n v="3360000"/>
     <n v="2530000"/>
-    <n v="830000"/>
+    <x v="39"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -13274,7 +13385,7 @@
     <n v="1260000"/>
     <n v="11340000"/>
     <n v="7275000"/>
-    <n v="4065000"/>
+    <x v="24"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -13294,7 +13405,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17070000"/>
-    <n v="6930000"/>
+    <x v="25"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -13314,7 +13425,7 @@
     <n v="1785000"/>
     <n v="4165000"/>
     <n v="3500000"/>
-    <n v="665000"/>
+    <x v="32"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -13334,7 +13445,7 @@
     <n v="680000"/>
     <n v="2720000"/>
     <n v="2165000"/>
-    <n v="555000"/>
+    <x v="23"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -13354,7 +13465,7 @@
     <n v="840000"/>
     <n v="7560000"/>
     <n v="4900000"/>
-    <n v="2660000"/>
+    <x v="62"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -13374,7 +13485,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4870000"/>
-    <n v="1010000"/>
+    <x v="37"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -13394,7 +13505,7 @@
     <n v="0"/>
     <n v="36000000"/>
     <n v="25650000"/>
-    <n v="10350000"/>
+    <x v="30"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -13414,7 +13525,7 @@
     <n v="850000"/>
     <n v="3400000"/>
     <n v="2575000"/>
-    <n v="825000"/>
+    <x v="93"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -13434,7 +13545,7 @@
     <n v="680000"/>
     <n v="6120000"/>
     <n v="4250000"/>
-    <n v="1870000"/>
+    <x v="8"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -13454,7 +13565,7 @@
     <n v="3780000"/>
     <n v="8820000"/>
     <n v="7410000"/>
-    <n v="1410000"/>
+    <x v="96"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -13474,7 +13585,7 @@
     <n v="0"/>
     <n v="4200000"/>
     <n v="2450000"/>
-    <n v="1750000"/>
+    <x v="14"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -13494,7 +13605,7 @@
     <n v="9600000"/>
     <n v="38400000"/>
     <n v="34260000"/>
-    <n v="4140000"/>
+    <x v="97"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -13514,7 +13625,7 @@
     <n v="255000"/>
     <n v="2295000"/>
     <n v="1425000"/>
-    <n v="870000"/>
+    <x v="36"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -13534,7 +13645,7 @@
     <n v="5100000"/>
     <n v="11900000"/>
     <n v="10675000"/>
-    <n v="1225000"/>
+    <x v="76"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -13554,7 +13665,7 @@
     <n v="0"/>
     <n v="4200000"/>
     <n v="2500000"/>
-    <n v="1700000"/>
+    <x v="22"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -13574,7 +13685,7 @@
     <n v="2520000"/>
     <n v="10080000"/>
     <n v="7395000"/>
-    <n v="2685000"/>
+    <x v="43"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -13594,7 +13705,7 @@
     <n v="2400000"/>
     <n v="21600000"/>
     <n v="17050000"/>
-    <n v="4550000"/>
+    <x v="0"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -13614,7 +13725,7 @@
     <n v="1785000"/>
     <n v="4165000"/>
     <n v="3395000"/>
-    <n v="770000"/>
+    <x v="21"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -13634,7 +13745,7 @@
     <n v="0"/>
     <n v="13600000"/>
     <n v="8600000"/>
-    <n v="5000000"/>
+    <x v="71"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -13654,7 +13765,7 @@
     <n v="420000"/>
     <n v="1680000"/>
     <n v="1265000"/>
-    <n v="415000"/>
+    <x v="78"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -13674,7 +13785,7 @@
     <n v="840000"/>
     <n v="7560000"/>
     <n v="4850000"/>
-    <n v="2710000"/>
+    <x v="4"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -13694,7 +13805,7 @@
     <n v="0"/>
     <n v="36000000"/>
     <n v="25605000"/>
-    <n v="10395000"/>
+    <x v="58"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -13714,7 +13825,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="4000000"/>
-    <n v="760000"/>
+    <x v="92"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -13734,7 +13845,7 @@
     <n v="1360000"/>
     <n v="5440000"/>
     <n v="4330000"/>
-    <n v="1110000"/>
+    <x v="73"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -13754,7 +13865,7 @@
     <n v="1050000"/>
     <n v="9450000"/>
     <n v="6125000"/>
-    <n v="3325000"/>
+    <x v="86"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -13774,7 +13885,7 @@
     <n v="1260000"/>
     <n v="2940000"/>
     <n v="2435000"/>
-    <n v="505000"/>
+    <x v="52"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -13794,7 +13905,7 @@
     <n v="0"/>
     <n v="24000000"/>
     <n v="17100000"/>
-    <n v="6900000"/>
+    <x v="45"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -13814,7 +13925,7 @@
     <n v="1020000"/>
     <n v="4080000"/>
     <n v="3090000"/>
-    <n v="990000"/>
+    <x v="31"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -13834,7 +13945,7 @@
     <n v="1020000"/>
     <n v="9180000"/>
     <n v="6375000"/>
-    <n v="2805000"/>
+    <x v="60"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -13854,7 +13965,7 @@
     <n v="2520000"/>
     <n v="5880000"/>
     <n v="4940000"/>
-    <n v="940000"/>
+    <x v="44"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -13874,7 +13985,7 @@
     <n v="0"/>
     <n v="8400000"/>
     <n v="4900000"/>
-    <n v="3500000"/>
+    <x v="49"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -13894,7 +14005,7 @@
     <n v="7200000"/>
     <n v="28800000"/>
     <n v="25695000"/>
-    <n v="3105000"/>
+    <x v="50"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -13914,7 +14025,7 @@
     <n v="425000"/>
     <n v="3825000"/>
     <n v="2375000"/>
-    <n v="1450000"/>
+    <x v="16"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -13934,7 +14045,7 @@
     <n v="1020000"/>
     <n v="2380000"/>
     <n v="2135000"/>
-    <n v="245000"/>
+    <x v="48"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -13954,7 +14065,7 @@
     <n v="0"/>
     <n v="6300000"/>
     <n v="3750000"/>
-    <n v="2550000"/>
+    <x v="55"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -13974,7 +14085,7 @@
     <n v="3360000"/>
     <n v="13440000"/>
     <n v="9860000"/>
-    <n v="3580000"/>
+    <x v="7"/>
     <n v="0.26636904761904762"/>
   </r>
   <r>
@@ -13994,7 +14105,7 @@
     <n v="2400000"/>
     <n v="21600000"/>
     <n v="17050000"/>
-    <n v="4550000"/>
+    <x v="0"/>
     <n v="0.21064814814814814"/>
   </r>
   <r>
@@ -14014,7 +14125,7 @@
     <n v="1785000"/>
     <n v="4165000"/>
     <n v="3395000"/>
-    <n v="770000"/>
+    <x v="21"/>
     <n v="0.18487394957983194"/>
   </r>
   <r>
@@ -14034,7 +14145,7 @@
     <n v="0"/>
     <n v="6800000"/>
     <n v="4300000"/>
-    <n v="2500000"/>
+    <x v="18"/>
     <n v="0.36764705882352944"/>
   </r>
   <r>
@@ -14054,7 +14165,7 @@
     <n v="2100000"/>
     <n v="8400000"/>
     <n v="6325000"/>
-    <n v="2075000"/>
+    <x v="82"/>
     <n v="0.24702380952380953"/>
   </r>
   <r>
@@ -14074,7 +14185,7 @@
     <n v="420000"/>
     <n v="3780000"/>
     <n v="2425000"/>
-    <n v="1355000"/>
+    <x v="57"/>
     <n v="0.35846560846560849"/>
   </r>
   <r>
@@ -14094,7 +14205,7 @@
     <n v="0"/>
     <n v="48000000"/>
     <n v="34140000"/>
-    <n v="13860000"/>
+    <x v="84"/>
     <n v="0.28875000000000001"/>
   </r>
   <r>
@@ -14114,7 +14225,7 @@
     <n v="1530000"/>
     <n v="3570000"/>
     <n v="3000000"/>
-    <n v="570000"/>
+    <x v="6"/>
     <n v="0.15966386554621848"/>
   </r>
   <r>
@@ -14134,7 +14245,7 @@
     <n v="2040000"/>
     <n v="8160000"/>
     <n v="6495000"/>
-    <n v="1665000"/>
+    <x v="3"/>
     <n v="0.20404411764705882"/>
   </r>
   <r>
@@ -14154,7 +14265,7 @@
     <n v="420000"/>
     <n v="3780000"/>
     <n v="2450000"/>
-    <n v="1330000"/>
+    <x v="12"/>
     <n v="0.35185185185185186"/>
   </r>
   <r>
@@ -14174,7 +14285,7 @@
     <n v="3780000"/>
     <n v="8820000"/>
     <n v="7305000"/>
-    <n v="1515000"/>
+    <x v="17"/>
     <n v="0.17176870748299319"/>
   </r>
   <r>
@@ -14194,7 +14305,7 @@
     <n v="0"/>
     <n v="12000000"/>
     <n v="8550000"/>
-    <n v="3450000"/>
+    <x v="10"/>
     <n v="0.28749999999999998"/>
   </r>
   <r>
@@ -14214,7 +14325,7 @@
     <n v="1360000"/>
     <n v="5440000"/>
     <n v="4120000"/>
-    <n v="1320000"/>
+    <x v="11"/>
     <n v="0.24264705882352941"/>
   </r>
   <r>
@@ -14234,7 +14345,7 @@
     <n v="1360000"/>
     <n v="12240000"/>
     <n v="8500000"/>
-    <n v="3740000"/>
+    <x v="80"/>
     <n v="0.30555555555555558"/>
   </r>
   <r>
@@ -14254,7 +14365,7 @@
     <n v="1260000"/>
     <n v="2940000"/>
     <n v="2470000"/>
-    <n v="470000"/>
+    <x v="29"/>
     <n v="0.1598639455782313"/>
   </r>
   <r>
@@ -14274,7 +14385,7 @@
     <n v="0"/>
     <n v="21000000"/>
     <n v="12250000"/>
-    <n v="8750000"/>
+    <x v="81"/>
     <n v="0.41666666666666669"/>
   </r>
   <r>
@@ -14294,7 +14405,7 @@
     <n v="7200000"/>
     <n v="28800000"/>
     <n v="25695000"/>
-    <n v="3105000"/>
+    <x v="50"/>
     <n v="0.10781250000000001"/>
   </r>
   <r>
@@ -14314,7 +14425,7 @@
     <n v="340000"/>
     <n v="3060000"/>
     <n v="1900000"/>
-    <n v="1160000"/>
+    <x v="51"/>
     <n v="0.37908496732026142"/>
   </r>
   <r>
@@ -14334,7 +14445,7 @@
     <n v="2040000"/>
     <n v="4760000"/>
     <n v="4270000"/>
-    <n v="490000"/>
+    <x v="33"/>
     <n v="0.10294117647058823"/>
   </r>
   <r>
@@ -14354,7 +14465,7 @@
     <n v="0"/>
     <n v="6300000"/>
     <n v="3750000"/>
-    <n v="2550000"/>
+    <x v="55"/>
     <n v="0.40476190476190477"/>
   </r>
   <r>
@@ -14374,15 +14485,15 @@
     <n v="1680000"/>
     <n v="6720000"/>
     <n v="4930000"/>
-    <n v="1790000"/>
+    <x v="59"/>
     <n v="0.26636904761904762"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{02B21EAE-34C8-4902-A826-4942B23E8318}" name="PivotTable4" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="I3:J8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{33554939-956D-4BE9-A88C-42E3B53823EE}" name="analisis" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" numFmtId="164" outline="0" showAll="0" defaultSubtotal="0">
@@ -14764,7 +14875,7 @@
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
       <items count="5">
         <item x="2"/>
         <item x="0"/>
@@ -14772,856 +14883,7 @@
         <item x="4"/>
         <item x="3"/>
       </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
     </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
-      <items count="368">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item sd="0" x="14"/>
-        <item sd="0" x="15"/>
-        <item sd="0" x="16"/>
-        <item sd="0" x="17"/>
-        <item sd="0" x="18"/>
-        <item sd="0" x="19"/>
-        <item sd="0" x="20"/>
-        <item sd="0" x="21"/>
-        <item sd="0" x="22"/>
-        <item sd="0" x="23"/>
-        <item sd="0" x="24"/>
-        <item sd="0" x="25"/>
-        <item sd="0" x="26"/>
-        <item sd="0" x="27"/>
-        <item sd="0" x="28"/>
-        <item sd="0" x="29"/>
-        <item sd="0" x="30"/>
-        <item sd="0" x="31"/>
-        <item sd="0" x="32"/>
-        <item sd="0" x="33"/>
-        <item sd="0" x="34"/>
-        <item sd="0" x="35"/>
-        <item sd="0" x="36"/>
-        <item sd="0" x="37"/>
-        <item sd="0" x="38"/>
-        <item sd="0" x="39"/>
-        <item sd="0" x="40"/>
-        <item sd="0" x="41"/>
-        <item sd="0" x="42"/>
-        <item sd="0" x="43"/>
-        <item sd="0" x="44"/>
-        <item sd="0" x="45"/>
-        <item sd="0" x="46"/>
-        <item sd="0" x="47"/>
-        <item sd="0" x="48"/>
-        <item sd="0" x="49"/>
-        <item sd="0" x="50"/>
-        <item sd="0" x="51"/>
-        <item sd="0" x="52"/>
-        <item sd="0" x="53"/>
-        <item sd="0" x="54"/>
-        <item sd="0" x="55"/>
-        <item sd="0" x="56"/>
-        <item sd="0" x="57"/>
-        <item sd="0" x="58"/>
-        <item sd="0" x="59"/>
-        <item sd="0" x="60"/>
-        <item sd="0" x="61"/>
-        <item sd="0" x="62"/>
-        <item sd="0" x="63"/>
-        <item sd="0" x="64"/>
-        <item sd="0" x="65"/>
-        <item sd="0" x="66"/>
-        <item sd="0" x="67"/>
-        <item sd="0" x="68"/>
-        <item sd="0" x="69"/>
-        <item sd="0" x="70"/>
-        <item sd="0" x="71"/>
-        <item sd="0" x="72"/>
-        <item sd="0" x="73"/>
-        <item sd="0" x="74"/>
-        <item sd="0" x="75"/>
-        <item sd="0" x="76"/>
-        <item sd="0" x="77"/>
-        <item sd="0" x="78"/>
-        <item sd="0" x="79"/>
-        <item sd="0" x="80"/>
-        <item sd="0" x="81"/>
-        <item sd="0" x="82"/>
-        <item sd="0" x="83"/>
-        <item sd="0" x="84"/>
-        <item sd="0" x="85"/>
-        <item sd="0" x="86"/>
-        <item sd="0" x="87"/>
-        <item sd="0" x="88"/>
-        <item sd="0" x="89"/>
-        <item sd="0" x="90"/>
-        <item sd="0" x="91"/>
-        <item sd="0" x="92"/>
-        <item sd="0" x="93"/>
-        <item sd="0" x="94"/>
-        <item sd="0" x="95"/>
-        <item sd="0" x="96"/>
-        <item sd="0" x="97"/>
-        <item sd="0" x="98"/>
-        <item sd="0" x="99"/>
-        <item sd="0" x="100"/>
-        <item sd="0" x="101"/>
-        <item sd="0" x="102"/>
-        <item sd="0" x="103"/>
-        <item sd="0" x="104"/>
-        <item sd="0" x="105"/>
-        <item sd="0" x="106"/>
-        <item sd="0" x="107"/>
-        <item sd="0" x="108"/>
-        <item sd="0" x="109"/>
-        <item sd="0" x="110"/>
-        <item sd="0" x="111"/>
-        <item sd="0" x="112"/>
-        <item sd="0" x="113"/>
-        <item sd="0" x="114"/>
-        <item sd="0" x="115"/>
-        <item sd="0" x="116"/>
-        <item sd="0" x="117"/>
-        <item sd="0" x="118"/>
-        <item sd="0" x="119"/>
-        <item sd="0" x="120"/>
-        <item sd="0" x="121"/>
-        <item sd="0" x="122"/>
-        <item sd="0" x="123"/>
-        <item sd="0" x="124"/>
-        <item sd="0" x="125"/>
-        <item sd="0" x="126"/>
-        <item sd="0" x="127"/>
-        <item sd="0" x="128"/>
-        <item sd="0" x="129"/>
-        <item sd="0" x="130"/>
-        <item sd="0" x="131"/>
-        <item sd="0" x="132"/>
-        <item sd="0" x="133"/>
-        <item sd="0" x="134"/>
-        <item sd="0" x="135"/>
-        <item sd="0" x="136"/>
-        <item sd="0" x="137"/>
-        <item sd="0" x="138"/>
-        <item sd="0" x="139"/>
-        <item sd="0" x="140"/>
-        <item sd="0" x="141"/>
-        <item sd="0" x="142"/>
-        <item sd="0" x="143"/>
-        <item sd="0" x="144"/>
-        <item sd="0" x="145"/>
-        <item sd="0" x="146"/>
-        <item sd="0" x="147"/>
-        <item sd="0" x="148"/>
-        <item sd="0" x="149"/>
-        <item sd="0" x="150"/>
-        <item sd="0" x="151"/>
-        <item sd="0" x="152"/>
-        <item sd="0" x="153"/>
-        <item sd="0" x="154"/>
-        <item sd="0" x="155"/>
-        <item sd="0" x="156"/>
-        <item sd="0" x="157"/>
-        <item sd="0" x="158"/>
-        <item sd="0" x="159"/>
-        <item sd="0" x="160"/>
-        <item sd="0" x="161"/>
-        <item sd="0" x="162"/>
-        <item sd="0" x="163"/>
-        <item sd="0" x="164"/>
-        <item sd="0" x="165"/>
-        <item sd="0" x="166"/>
-        <item sd="0" x="167"/>
-        <item sd="0" x="168"/>
-        <item sd="0" x="169"/>
-        <item sd="0" x="170"/>
-        <item sd="0" x="171"/>
-        <item sd="0" x="172"/>
-        <item sd="0" x="173"/>
-        <item sd="0" x="174"/>
-        <item sd="0" x="175"/>
-        <item sd="0" x="176"/>
-        <item sd="0" x="177"/>
-        <item sd="0" x="178"/>
-        <item sd="0" x="179"/>
-        <item sd="0" x="180"/>
-        <item sd="0" x="181"/>
-        <item sd="0" x="182"/>
-        <item sd="0" x="183"/>
-        <item sd="0" x="184"/>
-        <item sd="0" x="185"/>
-        <item sd="0" x="186"/>
-        <item sd="0" x="187"/>
-        <item sd="0" x="188"/>
-        <item sd="0" x="189"/>
-        <item sd="0" x="190"/>
-        <item sd="0" x="191"/>
-        <item sd="0" x="192"/>
-        <item sd="0" x="193"/>
-        <item sd="0" x="194"/>
-        <item sd="0" x="195"/>
-        <item sd="0" x="196"/>
-        <item sd="0" x="197"/>
-        <item sd="0" x="198"/>
-        <item sd="0" x="199"/>
-        <item sd="0" x="200"/>
-        <item sd="0" x="201"/>
-        <item sd="0" x="202"/>
-        <item sd="0" x="203"/>
-        <item sd="0" x="204"/>
-        <item sd="0" x="205"/>
-        <item sd="0" x="206"/>
-        <item sd="0" x="207"/>
-        <item sd="0" x="208"/>
-        <item sd="0" x="209"/>
-        <item sd="0" x="210"/>
-        <item sd="0" x="211"/>
-        <item sd="0" x="212"/>
-        <item sd="0" x="213"/>
-        <item sd="0" x="214"/>
-        <item sd="0" x="215"/>
-        <item sd="0" x="216"/>
-        <item sd="0" x="217"/>
-        <item sd="0" x="218"/>
-        <item sd="0" x="219"/>
-        <item sd="0" x="220"/>
-        <item sd="0" x="221"/>
-        <item sd="0" x="222"/>
-        <item sd="0" x="223"/>
-        <item sd="0" x="224"/>
-        <item sd="0" x="225"/>
-        <item sd="0" x="226"/>
-        <item sd="0" x="227"/>
-        <item sd="0" x="228"/>
-        <item sd="0" x="229"/>
-        <item sd="0" x="230"/>
-        <item sd="0" x="231"/>
-        <item sd="0" x="232"/>
-        <item sd="0" x="233"/>
-        <item sd="0" x="234"/>
-        <item sd="0" x="235"/>
-        <item sd="0" x="236"/>
-        <item sd="0" x="237"/>
-        <item sd="0" x="238"/>
-        <item sd="0" x="239"/>
-        <item sd="0" x="240"/>
-        <item sd="0" x="241"/>
-        <item sd="0" x="242"/>
-        <item sd="0" x="243"/>
-        <item sd="0" x="244"/>
-        <item sd="0" x="245"/>
-        <item sd="0" x="246"/>
-        <item sd="0" x="247"/>
-        <item sd="0" x="248"/>
-        <item sd="0" x="249"/>
-        <item sd="0" x="250"/>
-        <item sd="0" x="251"/>
-        <item sd="0" x="252"/>
-        <item sd="0" x="253"/>
-        <item sd="0" x="254"/>
-        <item sd="0" x="255"/>
-        <item sd="0" x="256"/>
-        <item sd="0" x="257"/>
-        <item sd="0" x="258"/>
-        <item sd="0" x="259"/>
-        <item sd="0" x="260"/>
-        <item sd="0" x="261"/>
-        <item sd="0" x="262"/>
-        <item sd="0" x="263"/>
-        <item sd="0" x="264"/>
-        <item sd="0" x="265"/>
-        <item sd="0" x="266"/>
-        <item sd="0" x="267"/>
-        <item sd="0" x="268"/>
-        <item sd="0" x="269"/>
-        <item sd="0" x="270"/>
-        <item sd="0" x="271"/>
-        <item sd="0" x="272"/>
-        <item sd="0" x="273"/>
-        <item sd="0" x="274"/>
-        <item sd="0" x="275"/>
-        <item sd="0" x="276"/>
-        <item sd="0" x="277"/>
-        <item sd="0" x="278"/>
-        <item sd="0" x="279"/>
-        <item sd="0" x="280"/>
-        <item sd="0" x="281"/>
-        <item sd="0" x="282"/>
-        <item sd="0" x="283"/>
-        <item sd="0" x="284"/>
-        <item sd="0" x="285"/>
-        <item sd="0" x="286"/>
-        <item sd="0" x="287"/>
-        <item sd="0" x="288"/>
-        <item sd="0" x="289"/>
-        <item sd="0" x="290"/>
-        <item sd="0" x="291"/>
-        <item sd="0" x="292"/>
-        <item sd="0" x="293"/>
-        <item sd="0" x="294"/>
-        <item sd="0" x="295"/>
-        <item sd="0" x="296"/>
-        <item sd="0" x="297"/>
-        <item sd="0" x="298"/>
-        <item sd="0" x="299"/>
-        <item sd="0" x="300"/>
-        <item sd="0" x="301"/>
-        <item sd="0" x="302"/>
-        <item sd="0" x="303"/>
-        <item sd="0" x="304"/>
-        <item sd="0" x="305"/>
-        <item sd="0" x="306"/>
-        <item sd="0" x="307"/>
-        <item sd="0" x="308"/>
-        <item sd="0" x="309"/>
-        <item sd="0" x="310"/>
-        <item sd="0" x="311"/>
-        <item sd="0" x="312"/>
-        <item sd="0" x="313"/>
-        <item sd="0" x="314"/>
-        <item sd="0" x="315"/>
-        <item sd="0" x="316"/>
-        <item sd="0" x="317"/>
-        <item sd="0" x="318"/>
-        <item sd="0" x="319"/>
-        <item sd="0" x="320"/>
-        <item sd="0" x="321"/>
-        <item sd="0" x="322"/>
-        <item sd="0" x="323"/>
-        <item sd="0" x="324"/>
-        <item sd="0" x="325"/>
-        <item sd="0" x="326"/>
-        <item sd="0" x="327"/>
-        <item sd="0" x="328"/>
-        <item sd="0" x="329"/>
-        <item sd="0" x="330"/>
-        <item sd="0" x="331"/>
-        <item sd="0" x="332"/>
-        <item sd="0" x="333"/>
-        <item sd="0" x="334"/>
-        <item sd="0" x="335"/>
-        <item sd="0" x="336"/>
-        <item sd="0" x="337"/>
-        <item sd="0" x="338"/>
-        <item sd="0" x="339"/>
-        <item sd="0" x="340"/>
-        <item sd="0" x="341"/>
-        <item sd="0" x="342"/>
-        <item sd="0" x="343"/>
-        <item sd="0" x="344"/>
-        <item sd="0" x="345"/>
-        <item sd="0" x="346"/>
-        <item sd="0" x="347"/>
-        <item sd="0" x="348"/>
-        <item sd="0" x="349"/>
-        <item sd="0" x="350"/>
-        <item sd="0" x="351"/>
-        <item sd="0" x="352"/>
-        <item sd="0" x="353"/>
-        <item sd="0" x="354"/>
-        <item sd="0" x="355"/>
-        <item sd="0" x="356"/>
-        <item sd="0" x="357"/>
-        <item sd="0" x="358"/>
-        <item sd="0" x="359"/>
-        <item sd="0" x="360"/>
-        <item sd="0" x="361"/>
-        <item sd="0" x="362"/>
-        <item sd="0" x="363"/>
-        <item sd="0" x="364"/>
-        <item sd="0" x="365"/>
-        <item sd="0" x="366"/>
-        <item sd="0" x="367"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
-      <items count="14">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total_Pendapatan_Bersih" fld="14" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="6" type="count" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="5" filterVal="5"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AB0713F1-3E17-453F-AB30-F21366BFC2CA}" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="F3:G15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="364">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
       <items count="3">
         <item x="1"/>
@@ -15637,859 +14899,108 @@
     <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
-      <items count="368">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item sd="0" x="14"/>
-        <item sd="0" x="15"/>
-        <item sd="0" x="16"/>
-        <item sd="0" x="17"/>
-        <item sd="0" x="18"/>
-        <item sd="0" x="19"/>
-        <item sd="0" x="20"/>
-        <item sd="0" x="21"/>
-        <item sd="0" x="22"/>
-        <item sd="0" x="23"/>
-        <item sd="0" x="24"/>
-        <item sd="0" x="25"/>
-        <item sd="0" x="26"/>
-        <item sd="0" x="27"/>
-        <item sd="0" x="28"/>
-        <item sd="0" x="29"/>
-        <item sd="0" x="30"/>
-        <item sd="0" x="31"/>
-        <item sd="0" x="32"/>
-        <item sd="0" x="33"/>
-        <item sd="0" x="34"/>
-        <item sd="0" x="35"/>
-        <item sd="0" x="36"/>
-        <item sd="0" x="37"/>
-        <item sd="0" x="38"/>
-        <item sd="0" x="39"/>
-        <item sd="0" x="40"/>
-        <item sd="0" x="41"/>
-        <item sd="0" x="42"/>
-        <item sd="0" x="43"/>
-        <item sd="0" x="44"/>
-        <item sd="0" x="45"/>
-        <item sd="0" x="46"/>
-        <item sd="0" x="47"/>
-        <item sd="0" x="48"/>
-        <item sd="0" x="49"/>
-        <item sd="0" x="50"/>
-        <item sd="0" x="51"/>
-        <item sd="0" x="52"/>
-        <item sd="0" x="53"/>
-        <item sd="0" x="54"/>
-        <item sd="0" x="55"/>
-        <item sd="0" x="56"/>
-        <item sd="0" x="57"/>
-        <item sd="0" x="58"/>
-        <item sd="0" x="59"/>
-        <item sd="0" x="60"/>
-        <item sd="0" x="61"/>
-        <item sd="0" x="62"/>
-        <item sd="0" x="63"/>
-        <item sd="0" x="64"/>
-        <item sd="0" x="65"/>
-        <item sd="0" x="66"/>
-        <item sd="0" x="67"/>
-        <item sd="0" x="68"/>
-        <item sd="0" x="69"/>
-        <item sd="0" x="70"/>
-        <item sd="0" x="71"/>
-        <item sd="0" x="72"/>
-        <item sd="0" x="73"/>
-        <item sd="0" x="74"/>
-        <item sd="0" x="75"/>
-        <item sd="0" x="76"/>
-        <item sd="0" x="77"/>
-        <item sd="0" x="78"/>
-        <item sd="0" x="79"/>
-        <item sd="0" x="80"/>
-        <item sd="0" x="81"/>
-        <item sd="0" x="82"/>
-        <item sd="0" x="83"/>
-        <item sd="0" x="84"/>
-        <item sd="0" x="85"/>
-        <item sd="0" x="86"/>
-        <item sd="0" x="87"/>
-        <item sd="0" x="88"/>
-        <item sd="0" x="89"/>
-        <item sd="0" x="90"/>
-        <item sd="0" x="91"/>
-        <item sd="0" x="92"/>
-        <item sd="0" x="93"/>
-        <item sd="0" x="94"/>
-        <item sd="0" x="95"/>
-        <item sd="0" x="96"/>
-        <item sd="0" x="97"/>
-        <item sd="0" x="98"/>
-        <item sd="0" x="99"/>
-        <item sd="0" x="100"/>
-        <item sd="0" x="101"/>
-        <item sd="0" x="102"/>
-        <item sd="0" x="103"/>
-        <item sd="0" x="104"/>
-        <item sd="0" x="105"/>
-        <item sd="0" x="106"/>
-        <item sd="0" x="107"/>
-        <item sd="0" x="108"/>
-        <item sd="0" x="109"/>
-        <item sd="0" x="110"/>
-        <item sd="0" x="111"/>
-        <item sd="0" x="112"/>
-        <item sd="0" x="113"/>
-        <item sd="0" x="114"/>
-        <item sd="0" x="115"/>
-        <item sd="0" x="116"/>
-        <item sd="0" x="117"/>
-        <item sd="0" x="118"/>
-        <item sd="0" x="119"/>
-        <item sd="0" x="120"/>
-        <item sd="0" x="121"/>
-        <item sd="0" x="122"/>
-        <item sd="0" x="123"/>
-        <item sd="0" x="124"/>
-        <item sd="0" x="125"/>
-        <item sd="0" x="126"/>
-        <item sd="0" x="127"/>
-        <item sd="0" x="128"/>
-        <item sd="0" x="129"/>
-        <item sd="0" x="130"/>
-        <item sd="0" x="131"/>
-        <item sd="0" x="132"/>
-        <item sd="0" x="133"/>
-        <item sd="0" x="134"/>
-        <item sd="0" x="135"/>
-        <item sd="0" x="136"/>
-        <item sd="0" x="137"/>
-        <item sd="0" x="138"/>
-        <item sd="0" x="139"/>
-        <item sd="0" x="140"/>
-        <item sd="0" x="141"/>
-        <item sd="0" x="142"/>
-        <item sd="0" x="143"/>
-        <item sd="0" x="144"/>
-        <item sd="0" x="145"/>
-        <item sd="0" x="146"/>
-        <item sd="0" x="147"/>
-        <item sd="0" x="148"/>
-        <item sd="0" x="149"/>
-        <item sd="0" x="150"/>
-        <item sd="0" x="151"/>
-        <item sd="0" x="152"/>
-        <item sd="0" x="153"/>
-        <item sd="0" x="154"/>
-        <item sd="0" x="155"/>
-        <item sd="0" x="156"/>
-        <item sd="0" x="157"/>
-        <item sd="0" x="158"/>
-        <item sd="0" x="159"/>
-        <item sd="0" x="160"/>
-        <item sd="0" x="161"/>
-        <item sd="0" x="162"/>
-        <item sd="0" x="163"/>
-        <item sd="0" x="164"/>
-        <item sd="0" x="165"/>
-        <item sd="0" x="166"/>
-        <item sd="0" x="167"/>
-        <item sd="0" x="168"/>
-        <item sd="0" x="169"/>
-        <item sd="0" x="170"/>
-        <item sd="0" x="171"/>
-        <item sd="0" x="172"/>
-        <item sd="0" x="173"/>
-        <item sd="0" x="174"/>
-        <item sd="0" x="175"/>
-        <item sd="0" x="176"/>
-        <item sd="0" x="177"/>
-        <item sd="0" x="178"/>
-        <item sd="0" x="179"/>
-        <item sd="0" x="180"/>
-        <item sd="0" x="181"/>
-        <item sd="0" x="182"/>
-        <item sd="0" x="183"/>
-        <item sd="0" x="184"/>
-        <item sd="0" x="185"/>
-        <item sd="0" x="186"/>
-        <item sd="0" x="187"/>
-        <item sd="0" x="188"/>
-        <item sd="0" x="189"/>
-        <item sd="0" x="190"/>
-        <item sd="0" x="191"/>
-        <item sd="0" x="192"/>
-        <item sd="0" x="193"/>
-        <item sd="0" x="194"/>
-        <item sd="0" x="195"/>
-        <item sd="0" x="196"/>
-        <item sd="0" x="197"/>
-        <item sd="0" x="198"/>
-        <item sd="0" x="199"/>
-        <item sd="0" x="200"/>
-        <item sd="0" x="201"/>
-        <item sd="0" x="202"/>
-        <item sd="0" x="203"/>
-        <item sd="0" x="204"/>
-        <item sd="0" x="205"/>
-        <item sd="0" x="206"/>
-        <item sd="0" x="207"/>
-        <item sd="0" x="208"/>
-        <item sd="0" x="209"/>
-        <item sd="0" x="210"/>
-        <item sd="0" x="211"/>
-        <item sd="0" x="212"/>
-        <item sd="0" x="213"/>
-        <item sd="0" x="214"/>
-        <item sd="0" x="215"/>
-        <item sd="0" x="216"/>
-        <item sd="0" x="217"/>
-        <item sd="0" x="218"/>
-        <item sd="0" x="219"/>
-        <item sd="0" x="220"/>
-        <item sd="0" x="221"/>
-        <item sd="0" x="222"/>
-        <item sd="0" x="223"/>
-        <item sd="0" x="224"/>
-        <item sd="0" x="225"/>
-        <item sd="0" x="226"/>
-        <item sd="0" x="227"/>
-        <item sd="0" x="228"/>
-        <item sd="0" x="229"/>
-        <item sd="0" x="230"/>
-        <item sd="0" x="231"/>
-        <item sd="0" x="232"/>
-        <item sd="0" x="233"/>
-        <item sd="0" x="234"/>
-        <item sd="0" x="235"/>
-        <item sd="0" x="236"/>
-        <item sd="0" x="237"/>
-        <item sd="0" x="238"/>
-        <item sd="0" x="239"/>
-        <item sd="0" x="240"/>
-        <item sd="0" x="241"/>
-        <item sd="0" x="242"/>
-        <item sd="0" x="243"/>
-        <item sd="0" x="244"/>
-        <item sd="0" x="245"/>
-        <item sd="0" x="246"/>
-        <item sd="0" x="247"/>
-        <item sd="0" x="248"/>
-        <item sd="0" x="249"/>
-        <item sd="0" x="250"/>
-        <item sd="0" x="251"/>
-        <item sd="0" x="252"/>
-        <item sd="0" x="253"/>
-        <item sd="0" x="254"/>
-        <item sd="0" x="255"/>
-        <item sd="0" x="256"/>
-        <item sd="0" x="257"/>
-        <item sd="0" x="258"/>
-        <item sd="0" x="259"/>
-        <item sd="0" x="260"/>
-        <item sd="0" x="261"/>
-        <item sd="0" x="262"/>
-        <item sd="0" x="263"/>
-        <item sd="0" x="264"/>
-        <item sd="0" x="265"/>
-        <item sd="0" x="266"/>
-        <item sd="0" x="267"/>
-        <item sd="0" x="268"/>
-        <item sd="0" x="269"/>
-        <item sd="0" x="270"/>
-        <item sd="0" x="271"/>
-        <item sd="0" x="272"/>
-        <item sd="0" x="273"/>
-        <item sd="0" x="274"/>
-        <item sd="0" x="275"/>
-        <item sd="0" x="276"/>
-        <item sd="0" x="277"/>
-        <item sd="0" x="278"/>
-        <item sd="0" x="279"/>
-        <item sd="0" x="280"/>
-        <item sd="0" x="281"/>
-        <item sd="0" x="282"/>
-        <item sd="0" x="283"/>
-        <item sd="0" x="284"/>
-        <item sd="0" x="285"/>
-        <item sd="0" x="286"/>
-        <item sd="0" x="287"/>
-        <item sd="0" x="288"/>
-        <item sd="0" x="289"/>
-        <item sd="0" x="290"/>
-        <item sd="0" x="291"/>
-        <item sd="0" x="292"/>
-        <item sd="0" x="293"/>
-        <item sd="0" x="294"/>
-        <item sd="0" x="295"/>
-        <item sd="0" x="296"/>
-        <item sd="0" x="297"/>
-        <item sd="0" x="298"/>
-        <item sd="0" x="299"/>
-        <item sd="0" x="300"/>
-        <item sd="0" x="301"/>
-        <item sd="0" x="302"/>
-        <item sd="0" x="303"/>
-        <item sd="0" x="304"/>
-        <item sd="0" x="305"/>
-        <item sd="0" x="306"/>
-        <item sd="0" x="307"/>
-        <item sd="0" x="308"/>
-        <item sd="0" x="309"/>
-        <item sd="0" x="310"/>
-        <item sd="0" x="311"/>
-        <item sd="0" x="312"/>
-        <item sd="0" x="313"/>
-        <item sd="0" x="314"/>
-        <item sd="0" x="315"/>
-        <item sd="0" x="316"/>
-        <item sd="0" x="317"/>
-        <item sd="0" x="318"/>
-        <item sd="0" x="319"/>
-        <item sd="0" x="320"/>
-        <item sd="0" x="321"/>
-        <item sd="0" x="322"/>
-        <item sd="0" x="323"/>
-        <item sd="0" x="324"/>
-        <item sd="0" x="325"/>
-        <item sd="0" x="326"/>
-        <item sd="0" x="327"/>
-        <item sd="0" x="328"/>
-        <item sd="0" x="329"/>
-        <item sd="0" x="330"/>
-        <item sd="0" x="331"/>
-        <item sd="0" x="332"/>
-        <item sd="0" x="333"/>
-        <item sd="0" x="334"/>
-        <item sd="0" x="335"/>
-        <item sd="0" x="336"/>
-        <item sd="0" x="337"/>
-        <item sd="0" x="338"/>
-        <item sd="0" x="339"/>
-        <item sd="0" x="340"/>
-        <item sd="0" x="341"/>
-        <item sd="0" x="342"/>
-        <item sd="0" x="343"/>
-        <item sd="0" x="344"/>
-        <item sd="0" x="345"/>
-        <item sd="0" x="346"/>
-        <item sd="0" x="347"/>
-        <item sd="0" x="348"/>
-        <item sd="0" x="349"/>
-        <item sd="0" x="350"/>
-        <item sd="0" x="351"/>
-        <item sd="0" x="352"/>
-        <item sd="0" x="353"/>
-        <item sd="0" x="354"/>
-        <item sd="0" x="355"/>
-        <item sd="0" x="356"/>
-        <item sd="0" x="357"/>
-        <item sd="0" x="358"/>
-        <item sd="0" x="359"/>
-        <item sd="0" x="360"/>
-        <item sd="0" x="361"/>
-        <item sd="0" x="362"/>
-        <item sd="0" x="363"/>
-        <item sd="0" x="364"/>
-        <item sd="0" x="365"/>
-        <item sd="0" x="366"/>
-        <item sd="0" x="367"/>
+    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="98">
+        <item x="61"/>
+        <item x="48"/>
+        <item x="26"/>
+        <item x="78"/>
+        <item x="90"/>
+        <item x="29"/>
+        <item x="42"/>
+        <item x="33"/>
+        <item x="52"/>
+        <item x="1"/>
+        <item x="23"/>
+        <item x="6"/>
+        <item x="54"/>
+        <item x="32"/>
+        <item x="9"/>
+        <item x="69"/>
+        <item x="92"/>
+        <item x="21"/>
+        <item x="93"/>
+        <item x="39"/>
+        <item x="2"/>
+        <item x="36"/>
+        <item x="41"/>
+        <item x="27"/>
+        <item x="85"/>
+        <item x="44"/>
+        <item x="13"/>
+        <item x="31"/>
+        <item x="37"/>
+        <item x="35"/>
+        <item x="73"/>
+        <item x="46"/>
+        <item x="51"/>
+        <item x="68"/>
+        <item x="76"/>
+        <item x="66"/>
+        <item x="65"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="57"/>
+        <item x="96"/>
+        <item x="16"/>
+        <item x="83"/>
+        <item x="17"/>
+        <item x="19"/>
+        <item x="3"/>
+        <item x="22"/>
+        <item x="88"/>
+        <item x="14"/>
+        <item x="59"/>
+        <item x="8"/>
+        <item x="47"/>
+        <item x="64"/>
+        <item x="70"/>
+        <item x="15"/>
+        <item x="82"/>
+        <item x="56"/>
+        <item x="72"/>
+        <item x="89"/>
+        <item x="18"/>
+        <item x="87"/>
+        <item x="55"/>
+        <item x="62"/>
+        <item x="43"/>
+        <item x="4"/>
+        <item x="67"/>
+        <item x="60"/>
+        <item x="50"/>
+        <item x="86"/>
+        <item x="79"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="49"/>
+        <item x="7"/>
+        <item x="80"/>
+        <item x="77"/>
+        <item x="24"/>
+        <item x="97"/>
+        <item x="95"/>
+        <item x="0"/>
+        <item x="28"/>
+        <item x="71"/>
+        <item x="63"/>
+        <item x="74"/>
+        <item x="38"/>
+        <item x="94"/>
+        <item x="20"/>
+        <item x="45"/>
+        <item x="25"/>
+        <item x="34"/>
+        <item x="53"/>
+        <item x="81"/>
+        <item x="40"/>
+        <item x="30"/>
+        <item x="58"/>
+        <item x="75"/>
+        <item x="84"/>
+        <item x="91"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
-      <items count="14">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="19"/>
-  </rowFields>
-  <rowItems count="12">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Laba_Kotor" fld="16" showDataAs="difference" baseField="19" baseItem="1048828" numFmtId="165"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{33554939-956D-4BE9-A88C-42E3B53823EE}" name="analisis" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A3:D15" firstHeaderRow="0" firstDataRow="1" firstDataCol="2"/>
-  <pivotFields count="20">
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="364">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
       <items count="368">
@@ -16882,65 +15393,33 @@
       </items>
     </pivotField>
   </pivotFields>
-  <rowFields count="2">
-    <field x="2"/>
-    <field x="7"/>
+  <rowFields count="1">
+    <field x="6"/>
   </rowFields>
-  <rowItems count="12">
+  <rowItems count="6">
     <i>
       <x/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
     </i>
     <i>
       <x v="1"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
     </i>
     <i>
-      <x v="2"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
       <x v="2"/>
     </i>
     <i>
       <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
       <x/>
     </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
   </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
+  <colItems count="1">
+    <i/>
   </colItems>
-  <dataFields count="2">
-    <dataField name="Sum of Laba_Kotor" fld="16" baseField="0" baseItem="0" numFmtId="165"/>
+  <dataFields count="1">
     <dataField name="Sum of Margin_Keuntungan" fld="17" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -16956,49 +15435,49 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91C63E51-A52D-46AB-91EB-CF63578A5333}" name="Table1" displayName="Table1" ref="A1:R501" totalsRowShown="0" headerRowDxfId="53" dataDxfId="51" headerRowBorderDxfId="52" tableBorderDxfId="50" totalsRowBorderDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91C63E51-A52D-46AB-91EB-CF63578A5333}" name="Table1" displayName="Table1" ref="A1:R501" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41" totalsRowBorderDxfId="40">
   <autoFilter ref="A1:R501" xr:uid="{91C63E51-A52D-46AB-91EB-CF63578A5333}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{535352A0-284A-4EC3-BEA5-FCAC4589AD45}" name="ID_Transaksi" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{60F5C6B6-2EE4-4C37-834D-803292CD8C49}" name="Tanggal" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{E56A6511-4721-46F1-A464-627EE6ED25E5}" name="Kota" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{D6C78C85-4803-494C-B4E3-8459D877E28E}" name="SKU" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{0C6A6903-F5CE-4107-9FDE-CC53F5F04204}" name="Jumlah_Unit" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{048E2C98-E916-4C7C-AA4A-3150159A27E8}" name="Kode_Promo" dataDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{3B8F5B69-10F0-4AEE-8CCF-65814EF6B3D8}" name="Nama_Produk" dataDxfId="42">
+    <tableColumn id="1" xr3:uid="{535352A0-284A-4EC3-BEA5-FCAC4589AD45}" name="ID_Transaksi" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{60F5C6B6-2EE4-4C37-834D-803292CD8C49}" name="Tanggal" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{E56A6511-4721-46F1-A464-627EE6ED25E5}" name="Kota" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{D6C78C85-4803-494C-B4E3-8459D877E28E}" name="SKU" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{0C6A6903-F5CE-4107-9FDE-CC53F5F04204}" name="Jumlah_Unit" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{048E2C98-E916-4C7C-AA4A-3150159A27E8}" name="Kode_Promo" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{3B8F5B69-10F0-4AEE-8CCF-65814EF6B3D8}" name="Nama_Produk" dataDxfId="33">
       <calculatedColumnFormula>INDEX(Table2[Nama Produk],MATCH(Table1[[#This Row],[SKU]],Table2[SKU],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{735DE14D-F3A8-4241-B953-035F6E26A6A0}" name="Kategori" dataDxfId="41">
+    <tableColumn id="8" xr3:uid="{735DE14D-F3A8-4241-B953-035F6E26A6A0}" name="Kategori" dataDxfId="32">
       <calculatedColumnFormula>VLOOKUP(Table1[[#This Row],[SKU]],Table2[],3,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{ECD5AF4E-B3F4-41BB-B37B-443DEE5B7141}" name="Harga_Satuan" dataDxfId="40">
+    <tableColumn id="9" xr3:uid="{ECD5AF4E-B3F4-41BB-B37B-443DEE5B7141}" name="Harga_Satuan" dataDxfId="31">
       <calculatedColumnFormula>INDEX(Table2[Harga Jual],MATCH(Table1[[#This Row],[SKU]],Table2[SKU],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C465DBB9-4C64-4E93-9532-CB6D42B2E695}" name="HPP_Satuan" dataDxfId="39">
+    <tableColumn id="10" xr3:uid="{C465DBB9-4C64-4E93-9532-CB6D42B2E695}" name="HPP_Satuan" dataDxfId="30">
       <calculatedColumnFormula>VLOOKUP(Table1[[#This Row],[SKU]],Table2[],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FBA65091-B8F3-4737-AD43-21E2351C753A}" name="Biaya_Kirim_Satuan" dataDxfId="38">
+    <tableColumn id="11" xr3:uid="{FBA65091-B8F3-4737-AD43-21E2351C753A}" name="Biaya_Kirim_Satuan" dataDxfId="29">
       <calculatedColumnFormula>INDEX(Table3[Biaya Kirim per Unit],MATCH(Table1[[#This Row],[Kota]],Table3[Kota],))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{236D1E61-E310-4595-8E7E-18D3E9DD1768}" name="Persentase_Diskon" dataDxfId="37" dataCellStyle="Percent">
+    <tableColumn id="12" xr3:uid="{236D1E61-E310-4595-8E7E-18D3E9DD1768}" name="Persentase_Diskon" dataDxfId="28" dataCellStyle="Percent">
       <calculatedColumnFormula>VLOOKUP(Table1[[#This Row],[Kode_Promo]],Table4[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{CA31B10C-74E5-409B-A9BB-69CF31F44850}" name="Total_Pendapatan_Kotor" dataDxfId="5">
+    <tableColumn id="13" xr3:uid="{CA31B10C-74E5-409B-A9BB-69CF31F44850}" name="Total_Pendapatan_Kotor" dataDxfId="27">
       <calculatedColumnFormula>Table1[[#This Row],[Jumlah_Unit]]*Table1[[#This Row],[Harga_Satuan]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3AE5F5BA-9CCD-4247-B4FB-CBB68DB0342F}" name="Potongan_Diskon" dataDxfId="4">
+    <tableColumn id="14" xr3:uid="{3AE5F5BA-9CCD-4247-B4FB-CBB68DB0342F}" name="Potongan_Diskon" dataDxfId="26">
       <calculatedColumnFormula>Table1[[#This Row],[Total_Pendapatan_Kotor]]*Table1[[#This Row],[Persentase_Diskon]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{83ED65EB-9A6F-4F9C-A403-5E4DEC52A650}" name="Total_Pendapatan_Bersih" dataDxfId="3">
+    <tableColumn id="15" xr3:uid="{83ED65EB-9A6F-4F9C-A403-5E4DEC52A650}" name="Total_Pendapatan_Bersih" dataDxfId="25">
       <calculatedColumnFormula>Table1[[#This Row],[Total_Pendapatan_Kotor]]-Table1[[#This Row],[Potongan_Diskon]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C66B6AE0-9825-4E7F-9199-125CC56ED9A7}" name="Total_Biaya" dataDxfId="2">
+    <tableColumn id="16" xr3:uid="{C66B6AE0-9825-4E7F-9199-125CC56ED9A7}" name="Total_Biaya" dataDxfId="24">
       <calculatedColumnFormula>(Table1[[#This Row],[Jumlah_Unit]]*Table1[[#This Row],[HPP_Satuan]])+(Table1[[#This Row],[Jumlah_Unit]]*Table1[[#This Row],[Biaya_Kirim_Satuan]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{8448139B-E35F-403D-88B7-2B81687ED76E}" name="Laba_Kotor" dataDxfId="1">
+    <tableColumn id="17" xr3:uid="{8448139B-E35F-403D-88B7-2B81687ED76E}" name="Laba_Kotor" dataDxfId="23">
       <calculatedColumnFormula>Table1[[#This Row],[Total_Pendapatan_Bersih]]-Table1[[#This Row],[Total_Biaya]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{19F6E599-1DA2-4A17-B20A-85FAA9CAA88F}" name="Margin_Keuntungan" dataDxfId="0">
+    <tableColumn id="18" xr3:uid="{19F6E599-1DA2-4A17-B20A-85FAA9CAA88F}" name="Margin_Keuntungan" dataDxfId="22">
       <calculatedColumnFormula>Table1[[#This Row],[Laba_Kotor]]/Table1[[#This Row],[Total_Pendapatan_Bersih]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -17007,51 +15486,51 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FDD45560-B6D3-41C6-AE2A-F8AD6BBACE68}" name="Table2" displayName="Table2" ref="A1:E6" totalsRowShown="0" headerRowDxfId="36" headerRowBorderDxfId="35" tableBorderDxfId="34" totalsRowBorderDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FDD45560-B6D3-41C6-AE2A-F8AD6BBACE68}" name="Table2" displayName="Table2" ref="A1:E6" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A1:E6" xr:uid="{FDD45560-B6D3-41C6-AE2A-F8AD6BBACE68}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8EB14854-7AF6-49A4-88AA-B3FDDCC42382}" name="SKU" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{5D2A612D-0698-4443-8219-30640E779857}" name="Nama Produk" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{A6103524-5795-4C97-B3D5-365566612506}" name="Kategori" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{E99EBFAC-0288-49E8-A2CE-BA8095F96A66}" name="HPP" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{3D2D3651-2CAB-4DFC-ABF1-674CCD068115}" name="Harga Jual" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{8EB14854-7AF6-49A4-88AA-B3FDDCC42382}" name="SKU" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{5D2A612D-0698-4443-8219-30640E779857}" name="Nama Produk" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{A6103524-5795-4C97-B3D5-365566612506}" name="Kategori" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{E99EBFAC-0288-49E8-A2CE-BA8095F96A66}" name="HPP" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{3D2D3651-2CAB-4DFC-ABF1-674CCD068115}" name="Harga Jual" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{10F71EA0-F0EC-4DFE-A2AB-43A6531E908A}" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0" headerRowBorderDxfId="27" tableBorderDxfId="26" totalsRowBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{10F71EA0-F0EC-4DFE-A2AB-43A6531E908A}" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="A1:C5" xr:uid="{10F71EA0-F0EC-4DFE-A2AB-43A6531E908A}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0A45B6A5-0536-4D20-A5E2-7E4BD4BDCE05}" name="Kota" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{636D6F2C-8691-45F9-87EF-3C4669C8D4FE}" name="Wilayah" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{873955BF-A08E-404A-897B-9A4966E646E3}" name="Biaya Kirim per Unit" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{0A45B6A5-0536-4D20-A5E2-7E4BD4BDCE05}" name="Kota" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{636D6F2C-8691-45F9-87EF-3C4669C8D4FE}" name="Wilayah" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{873955BF-A08E-404A-897B-9A4966E646E3}" name="Biaya Kirim per Unit" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DA8C010A-5D31-4A19-AF5C-380C4883E588}" name="Table4" displayName="Table4" ref="A1:C5" totalsRowShown="0" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DA8C010A-5D31-4A19-AF5C-380C4883E588}" name="Table4" displayName="Table4" ref="A1:C5" totalsRowShown="0" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
   <autoFilter ref="A1:C5" xr:uid="{DA8C010A-5D31-4A19-AF5C-380C4883E588}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0FEAB7C0-9975-4BB3-97C0-65272C933D59}" name="Kode Promo" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{7268390E-5820-4F31-AA85-AF2D35552741}" name="Besaran Diskon" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{95D74BC3-E24F-46CD-A305-3DE4BBBB44D9}" name="Keterangan Syarat" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{0FEAB7C0-9975-4BB3-97C0-65272C933D59}" name="Kode Promo" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{7268390E-5820-4F31-AA85-AF2D35552741}" name="Besaran Diskon" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{95D74BC3-E24F-46CD-A305-3DE4BBBB44D9}" name="Keterangan Syarat" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2D8BD81D-9F01-414B-A4EE-0F3E3758FAD8}" name="Table5" displayName="Table5" ref="A5:D12" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11" dataCellStyle="Percent">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2D8BD81D-9F01-414B-A4EE-0F3E3758FAD8}" name="Table5" displayName="Table5" ref="A5:D12" totalsRowShown="0" headerRowDxfId="53" dataDxfId="51" headerRowBorderDxfId="52" tableBorderDxfId="50" totalsRowBorderDxfId="49" dataCellStyle="Percent">
   <autoFilter ref="A5:D12" xr:uid="{2D8BD81D-9F01-414B-A4EE-0F3E3758FAD8}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C0DB13C7-69BD-4B04-AD37-A903E9718342}" name="Nomor Soal" dataDxfId="10" dataCellStyle="Percent"/>
-    <tableColumn id="2" xr3:uid="{0024CB6F-4755-4E2C-8351-AEB7946C3495}" name="Kategori Keterampilan" dataDxfId="9" dataCellStyle="Percent"/>
-    <tableColumn id="3" xr3:uid="{E54C8867-FE29-4C25-A0EC-89B409159D7E}" name="Instruksi Pengerjaan" dataDxfId="8" dataCellStyle="Percent"/>
-    <tableColumn id="4" xr3:uid="{2E3FF913-4ABB-4AED-AD44-A625313457B5}" name="Output yang Diharapkan" dataDxfId="7" dataCellStyle="Percent"/>
+    <tableColumn id="1" xr3:uid="{C0DB13C7-69BD-4B04-AD37-A903E9718342}" name="Nomor Soal" dataDxfId="48" dataCellStyle="Percent"/>
+    <tableColumn id="2" xr3:uid="{0024CB6F-4755-4E2C-8351-AEB7946C3495}" name="Kategori Keterampilan" dataDxfId="47" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{E54C8867-FE29-4C25-A0EC-89B409159D7E}" name="Instruksi Pengerjaan" dataDxfId="46" dataCellStyle="Percent"/>
+    <tableColumn id="4" xr3:uid="{2E3FF913-4ABB-4AED-AD44-A625313457B5}" name="Output yang Diharapkan" dataDxfId="45" dataCellStyle="Percent"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -51435,7 +49914,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:R501">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$E2 &gt; 5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -51717,12 +50196,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB7F205-A472-48BE-8BFF-99A604B10656}">
-  <dimension ref="A3:J15"/>
+  <dimension ref="A3:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -51730,274 +50209,60 @@
     <col min="10" max="11" width="30.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>587</v>
       </c>
-      <c r="D3" t="s">
-        <v>588</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>589</v>
-      </c>
-      <c r="G3" t="s">
-        <v>587</v>
-      </c>
-      <c r="I3" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>537</v>
-      </c>
-      <c r="C4" s="26">
-        <v>36830000</v>
-      </c>
-      <c r="D4" s="42">
-        <v>9.4771241830065414</v>
-      </c>
-      <c r="F4" t="s">
-        <v>590</v>
-      </c>
-      <c r="G4" s="26"/>
-      <c r="I4" t="s">
+        <v>539</v>
+      </c>
+      <c r="B4" s="48">
+        <v>29.245275888133023</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>534</v>
       </c>
-      <c r="J4" s="26">
-        <v>2473200000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>535</v>
-      </c>
-      <c r="C5" s="26">
-        <v>210645000</v>
-      </c>
-      <c r="D5" s="42">
-        <v>12.905092592592592</v>
-      </c>
-      <c r="F5" t="s">
-        <v>591</v>
-      </c>
-      <c r="G5" s="26">
-        <v>-15940000</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="B5" s="48">
+        <v>22.367766203703731</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>536</v>
+      </c>
+      <c r="B6" s="48">
+        <v>24.156746031746</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>541</v>
       </c>
-      <c r="J5" s="26">
-        <v>912240000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>540</v>
-      </c>
-      <c r="C6" s="26">
-        <v>127850000</v>
-      </c>
-      <c r="D6" s="42">
-        <v>17.75793650793651</v>
-      </c>
-      <c r="F6" t="s">
-        <v>592</v>
-      </c>
-      <c r="G6" s="26">
-        <v>4775000</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="B7" s="48">
+        <v>30.3317507558579</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>538</v>
       </c>
-      <c r="J6" s="26">
-        <v>847280000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C7" s="26">
-        <v>27225000</v>
-      </c>
-      <c r="D7" s="42">
-        <v>6.066176470588232</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="B8" s="48">
+        <v>24.34109477124181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>593</v>
       </c>
-      <c r="G7" s="26">
-        <v>15520000</v>
-      </c>
-      <c r="I7" t="s">
-        <v>539</v>
-      </c>
-      <c r="J7" s="26">
-        <v>477330000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>535</v>
-      </c>
-      <c r="C8" s="26">
-        <v>96480000</v>
-      </c>
-      <c r="D8" s="42">
-        <v>8.0004595588235272</v>
-      </c>
-      <c r="F8" t="s">
-        <v>594</v>
-      </c>
-      <c r="G8" s="26">
-        <v>-3320000</v>
-      </c>
-      <c r="I8" t="s">
-        <v>536</v>
-      </c>
-      <c r="J8" s="26">
-        <v>392615000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>540</v>
-      </c>
-      <c r="C9" s="26">
-        <v>83775000</v>
-      </c>
-      <c r="D9" s="42">
-        <v>12.587797619047619</v>
-      </c>
-      <c r="F9" t="s">
-        <v>595</v>
-      </c>
-      <c r="G9" s="26">
-        <v>730000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" t="s">
-        <v>537</v>
-      </c>
-      <c r="C10" s="26">
-        <v>14155000</v>
-      </c>
-      <c r="D10" s="42">
-        <v>3.99159663865546</v>
-      </c>
-      <c r="F10" t="s">
-        <v>596</v>
-      </c>
-      <c r="G10" s="26">
-        <v>5120000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>535</v>
-      </c>
-      <c r="C11" s="26">
-        <v>278800000</v>
-      </c>
-      <c r="D11" s="42">
-        <v>16.011029411764692</v>
-      </c>
-      <c r="F11" t="s">
-        <v>597</v>
-      </c>
-      <c r="G11" s="26">
-        <v>5460000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>540</v>
-      </c>
-      <c r="C12" s="26">
-        <v>169150000</v>
-      </c>
-      <c r="D12" s="42">
-        <v>20.9404761904762</v>
-      </c>
-      <c r="F12" t="s">
-        <v>598</v>
-      </c>
-      <c r="G12" s="26">
-        <v>-22640000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>537</v>
-      </c>
-      <c r="C13" s="26">
-        <v>17490000</v>
-      </c>
-      <c r="D13" s="42">
-        <v>4.6218487394958014</v>
-      </c>
-      <c r="F13" t="s">
-        <v>599</v>
-      </c>
-      <c r="G13" s="26">
-        <v>10335000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>535</v>
-      </c>
-      <c r="C14" s="26">
-        <v>201285000</v>
-      </c>
-      <c r="D14" s="42">
-        <v>9.7922794117647083</v>
-      </c>
-      <c r="F14" t="s">
-        <v>600</v>
-      </c>
-      <c r="G14" s="26">
-        <v>7605000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>540</v>
-      </c>
-      <c r="C15" s="26">
-        <v>49945000</v>
-      </c>
-      <c r="D15" s="42">
-        <v>8.2908163265306118</v>
-      </c>
-      <c r="F15" t="s">
-        <v>601</v>
-      </c>
-      <c r="G15" s="26">
-        <v>15535000</v>
+      <c r="B9" s="48">
+        <v>130.44263365068247</v>
       </c>
     </row>
   </sheetData>
@@ -52154,9 +50419,286 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F40FF0D9-1060-45F4-9C12-4DBC7EB60C19}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:Z13"/>
+  <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="14" customWidth="1"/>
+    <col min="2" max="7" width="9.140625" style="14"/>
+    <col min="8" max="8" width="1.140625" style="14" customWidth="1"/>
+    <col min="9" max="13" width="9.140625" style="14"/>
+    <col min="14" max="14" width="1.140625" style="14" customWidth="1"/>
+    <col min="15" max="19" width="9.140625" style="14"/>
+    <col min="20" max="20" width="1.140625" style="14" customWidth="1"/>
+    <col min="21" max="25" width="9.140625" style="14"/>
+    <col min="26" max="26" width="1.140625" style="14" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="42" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="42"/>
+      <c r="W1" s="42"/>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="42"/>
+      <c r="V2" s="42"/>
+      <c r="W2" s="42"/>
+      <c r="X2" s="42"/>
+      <c r="Y2" s="42"/>
+      <c r="Z2" s="42"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="42"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="42"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="42"/>
+      <c r="W3" s="42"/>
+      <c r="X3" s="42"/>
+      <c r="Y3" s="42"/>
+      <c r="Z3" s="42"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="44" t="s">
+        <v>589</v>
+      </c>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="I4" s="44" t="s">
+        <v>590</v>
+      </c>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="O4" s="44" t="s">
+        <v>591</v>
+      </c>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
+      <c r="S4" s="44"/>
+      <c r="U4" s="44" t="s">
+        <v>592</v>
+      </c>
+      <c r="V4" s="44"/>
+      <c r="W4" s="44"/>
+      <c r="X4" s="44"/>
+      <c r="Y4" s="44"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="44"/>
+      <c r="Q5" s="44"/>
+      <c r="R5" s="44"/>
+      <c r="S5" s="44"/>
+      <c r="U5" s="44"/>
+      <c r="V5" s="44"/>
+      <c r="W5" s="44"/>
+      <c r="X5" s="44"/>
+      <c r="Y5" s="44"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="52">
+        <v>5820200000</v>
+      </c>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="50">
+        <v>1313630000</v>
+      </c>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="50"/>
+      <c r="M6" s="50"/>
+      <c r="O6" s="49">
+        <v>130.44263365068247</v>
+      </c>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49"/>
+      <c r="U6" s="45"/>
+      <c r="V6" s="45"/>
+      <c r="W6" s="45"/>
+      <c r="X6" s="45"/>
+      <c r="Y6" s="45"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="50"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="U7" s="45"/>
+      <c r="V7" s="45"/>
+      <c r="W7" s="45"/>
+      <c r="X7" s="45"/>
+      <c r="Y7" s="45"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="43"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="43"/>
+      <c r="W8" s="43"/>
+      <c r="X8" s="43"/>
+      <c r="Y8" s="43"/>
+      <c r="Z8" s="43"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="M10" s="46"/>
+      <c r="N10" s="46"/>
+      <c r="O10" s="46"/>
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="46"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="46"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="M12" s="47"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="M13" s="47"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="47"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="I4:M5"/>
+    <mergeCell ref="O4:S5"/>
+    <mergeCell ref="U4:Y5"/>
+    <mergeCell ref="I6:M7"/>
+    <mergeCell ref="O6:S7"/>
+    <mergeCell ref="U6:Y7"/>
+    <mergeCell ref="A1:Z3"/>
+    <mergeCell ref="B4:G5"/>
+    <mergeCell ref="B6:G7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Analisis Retail Bisnis Omni-Channel.xlsx
+++ b/Analisis Retail Bisnis Omni-Channel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aldy\Documents\DATA ANALYST\MICROSOFT EXCEL\PORTOFOLIO\Analisis Retail Bisnis Omni-Channel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EA1C2C-50F4-4DE2-B540-46896F24CC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C5CC35-AD3A-4B58-AA65-CD1A76E986E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="2" activeTab="6" xr2:uid="{0FABD09F-C599-4D8F-AE1F-66CDC9C9D3DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="1" activeTab="6" xr2:uid="{0FABD09F-C599-4D8F-AE1F-66CDC9C9D3DB}"/>
   </bookViews>
   <sheets>
     <sheet name="penjualan" sheetId="1" r:id="rId1"/>
@@ -19,11 +19,11 @@
     <sheet name="promo" sheetId="4" r:id="rId4"/>
     <sheet name="analisis" sheetId="6" r:id="rId5"/>
     <sheet name="soal" sheetId="5" r:id="rId6"/>
-    <sheet name="dashboard" sheetId="7" r:id="rId7"/>
+    <sheet name="Dashboard" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="592">
   <si>
     <t>ID_Transaksi</t>
   </si>
@@ -1806,9 +1806,6 @@
     <t>Dasbor visual interaktif untuk portofolio LinkedIn/GitHub</t>
   </si>
   <si>
-    <t>Sum of Margin_Keuntungan</t>
-  </si>
-  <si>
     <t>ANALISIS BISNIS RETAIL OMNI-CHANNEL</t>
   </si>
   <si>
@@ -1818,13 +1815,10 @@
     <t>TOTAL NET PROFIT</t>
   </si>
   <si>
-    <t>OVERALL PROFIT MARGIN%</t>
-  </si>
-  <si>
-    <t>TOTAL UNITS SOLD</t>
-  </si>
-  <si>
     <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Laba_Kotor</t>
   </si>
 </sst>
 </file>
@@ -1835,9 +1829,9 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="&quot;Rp&quot;#,##0"/>
+    <numFmt numFmtId="167" formatCode="&quot;Rp&quot;#,##0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1864,9 +1858,26 @@
       <name val="Poppins"/>
     </font>
     <font>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Poppins"/>
+    </font>
+    <font>
       <b/>
-      <sz val="24"/>
-      <color theme="1"/>
+      <sz val="28"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Poppins"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="4" tint="0.79998168889431442"/>
+      <name val="Poppins"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="4" tint="0.39997558519241921"/>
       <name val="Poppins"/>
     </font>
   </fonts>
@@ -1885,7 +1896,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="4" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2014,7 +2025,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2132,32 +2143,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2170,6 +2173,191 @@
           <bgColor rgb="FFFFFF9F"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right/>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -3300,191 +3488,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right/>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Poppins"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -14492,7 +14495,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{33554939-956D-4BE9-A88C-42E3B53823EE}" name="analisis" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{33554939-956D-4BE9-A88C-42E3B53823EE}" name="analisis" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -14899,7 +14902,7 @@
     <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0">
+    <pivotField dataField="1" compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0">
       <items count="98">
         <item x="61"/>
         <item x="48"/>
@@ -15001,7 +15004,7 @@
         <item x="91"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
       <items count="368">
         <item x="0"/>
@@ -15420,7 +15423,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Margin_Keuntungan" fld="17" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Laba_Kotor" fld="16" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -15435,49 +15438,49 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91C63E51-A52D-46AB-91EB-CF63578A5333}" name="Table1" displayName="Table1" ref="A1:R501" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41" totalsRowBorderDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91C63E51-A52D-46AB-91EB-CF63578A5333}" name="Table1" displayName="Table1" ref="A1:R501" totalsRowShown="0" headerRowDxfId="53" dataDxfId="51" headerRowBorderDxfId="52" tableBorderDxfId="50" totalsRowBorderDxfId="49">
   <autoFilter ref="A1:R501" xr:uid="{91C63E51-A52D-46AB-91EB-CF63578A5333}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{535352A0-284A-4EC3-BEA5-FCAC4589AD45}" name="ID_Transaksi" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{60F5C6B6-2EE4-4C37-834D-803292CD8C49}" name="Tanggal" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{E56A6511-4721-46F1-A464-627EE6ED25E5}" name="Kota" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{D6C78C85-4803-494C-B4E3-8459D877E28E}" name="SKU" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{0C6A6903-F5CE-4107-9FDE-CC53F5F04204}" name="Jumlah_Unit" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{048E2C98-E916-4C7C-AA4A-3150159A27E8}" name="Kode_Promo" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{3B8F5B69-10F0-4AEE-8CCF-65814EF6B3D8}" name="Nama_Produk" dataDxfId="33">
+    <tableColumn id="1" xr3:uid="{535352A0-284A-4EC3-BEA5-FCAC4589AD45}" name="ID_Transaksi" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{60F5C6B6-2EE4-4C37-834D-803292CD8C49}" name="Tanggal" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{E56A6511-4721-46F1-A464-627EE6ED25E5}" name="Kota" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{D6C78C85-4803-494C-B4E3-8459D877E28E}" name="SKU" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{0C6A6903-F5CE-4107-9FDE-CC53F5F04204}" name="Jumlah_Unit" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{048E2C98-E916-4C7C-AA4A-3150159A27E8}" name="Kode_Promo" dataDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{3B8F5B69-10F0-4AEE-8CCF-65814EF6B3D8}" name="Nama_Produk" dataDxfId="42">
       <calculatedColumnFormula>INDEX(Table2[Nama Produk],MATCH(Table1[[#This Row],[SKU]],Table2[SKU],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{735DE14D-F3A8-4241-B953-035F6E26A6A0}" name="Kategori" dataDxfId="32">
+    <tableColumn id="8" xr3:uid="{735DE14D-F3A8-4241-B953-035F6E26A6A0}" name="Kategori" dataDxfId="41">
       <calculatedColumnFormula>VLOOKUP(Table1[[#This Row],[SKU]],Table2[],3,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{ECD5AF4E-B3F4-41BB-B37B-443DEE5B7141}" name="Harga_Satuan" dataDxfId="31">
+    <tableColumn id="9" xr3:uid="{ECD5AF4E-B3F4-41BB-B37B-443DEE5B7141}" name="Harga_Satuan" dataDxfId="40">
       <calculatedColumnFormula>INDEX(Table2[Harga Jual],MATCH(Table1[[#This Row],[SKU]],Table2[SKU],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C465DBB9-4C64-4E93-9532-CB6D42B2E695}" name="HPP_Satuan" dataDxfId="30">
+    <tableColumn id="10" xr3:uid="{C465DBB9-4C64-4E93-9532-CB6D42B2E695}" name="HPP_Satuan" dataDxfId="39">
       <calculatedColumnFormula>VLOOKUP(Table1[[#This Row],[SKU]],Table2[],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FBA65091-B8F3-4737-AD43-21E2351C753A}" name="Biaya_Kirim_Satuan" dataDxfId="29">
+    <tableColumn id="11" xr3:uid="{FBA65091-B8F3-4737-AD43-21E2351C753A}" name="Biaya_Kirim_Satuan" dataDxfId="38">
       <calculatedColumnFormula>INDEX(Table3[Biaya Kirim per Unit],MATCH(Table1[[#This Row],[Kota]],Table3[Kota],))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{236D1E61-E310-4595-8E7E-18D3E9DD1768}" name="Persentase_Diskon" dataDxfId="28" dataCellStyle="Percent">
+    <tableColumn id="12" xr3:uid="{236D1E61-E310-4595-8E7E-18D3E9DD1768}" name="Persentase_Diskon" dataDxfId="37" dataCellStyle="Percent">
       <calculatedColumnFormula>VLOOKUP(Table1[[#This Row],[Kode_Promo]],Table4[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{CA31B10C-74E5-409B-A9BB-69CF31F44850}" name="Total_Pendapatan_Kotor" dataDxfId="27">
+    <tableColumn id="13" xr3:uid="{CA31B10C-74E5-409B-A9BB-69CF31F44850}" name="Total_Pendapatan_Kotor" dataDxfId="36">
       <calculatedColumnFormula>Table1[[#This Row],[Jumlah_Unit]]*Table1[[#This Row],[Harga_Satuan]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3AE5F5BA-9CCD-4247-B4FB-CBB68DB0342F}" name="Potongan_Diskon" dataDxfId="26">
+    <tableColumn id="14" xr3:uid="{3AE5F5BA-9CCD-4247-B4FB-CBB68DB0342F}" name="Potongan_Diskon" dataDxfId="35">
       <calculatedColumnFormula>Table1[[#This Row],[Total_Pendapatan_Kotor]]*Table1[[#This Row],[Persentase_Diskon]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{83ED65EB-9A6F-4F9C-A403-5E4DEC52A650}" name="Total_Pendapatan_Bersih" dataDxfId="25">
+    <tableColumn id="15" xr3:uid="{83ED65EB-9A6F-4F9C-A403-5E4DEC52A650}" name="Total_Pendapatan_Bersih" dataDxfId="34">
       <calculatedColumnFormula>Table1[[#This Row],[Total_Pendapatan_Kotor]]-Table1[[#This Row],[Potongan_Diskon]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C66B6AE0-9825-4E7F-9199-125CC56ED9A7}" name="Total_Biaya" dataDxfId="24">
+    <tableColumn id="16" xr3:uid="{C66B6AE0-9825-4E7F-9199-125CC56ED9A7}" name="Total_Biaya" dataDxfId="33">
       <calculatedColumnFormula>(Table1[[#This Row],[Jumlah_Unit]]*Table1[[#This Row],[HPP_Satuan]])+(Table1[[#This Row],[Jumlah_Unit]]*Table1[[#This Row],[Biaya_Kirim_Satuan]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{8448139B-E35F-403D-88B7-2B81687ED76E}" name="Laba_Kotor" dataDxfId="23">
+    <tableColumn id="17" xr3:uid="{8448139B-E35F-403D-88B7-2B81687ED76E}" name="Laba_Kotor" dataDxfId="32">
       <calculatedColumnFormula>Table1[[#This Row],[Total_Pendapatan_Bersih]]-Table1[[#This Row],[Total_Biaya]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{19F6E599-1DA2-4A17-B20A-85FAA9CAA88F}" name="Margin_Keuntungan" dataDxfId="22">
+    <tableColumn id="18" xr3:uid="{19F6E599-1DA2-4A17-B20A-85FAA9CAA88F}" name="Margin_Keuntungan" dataDxfId="31">
       <calculatedColumnFormula>Table1[[#This Row],[Laba_Kotor]]/Table1[[#This Row],[Total_Pendapatan_Bersih]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -15486,51 +15489,51 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FDD45560-B6D3-41C6-AE2A-F8AD6BBACE68}" name="Table2" displayName="Table2" ref="A1:E6" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FDD45560-B6D3-41C6-AE2A-F8AD6BBACE68}" name="Table2" displayName="Table2" ref="A1:E6" totalsRowShown="0" headerRowDxfId="30" headerRowBorderDxfId="29" tableBorderDxfId="28" totalsRowBorderDxfId="27">
   <autoFilter ref="A1:E6" xr:uid="{FDD45560-B6D3-41C6-AE2A-F8AD6BBACE68}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8EB14854-7AF6-49A4-88AA-B3FDDCC42382}" name="SKU" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{5D2A612D-0698-4443-8219-30640E779857}" name="Nama Produk" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{A6103524-5795-4C97-B3D5-365566612506}" name="Kategori" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{E99EBFAC-0288-49E8-A2CE-BA8095F96A66}" name="HPP" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{3D2D3651-2CAB-4DFC-ABF1-674CCD068115}" name="Harga Jual" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{8EB14854-7AF6-49A4-88AA-B3FDDCC42382}" name="SKU" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{5D2A612D-0698-4443-8219-30640E779857}" name="Nama Produk" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{A6103524-5795-4C97-B3D5-365566612506}" name="Kategori" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{E99EBFAC-0288-49E8-A2CE-BA8095F96A66}" name="HPP" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{3D2D3651-2CAB-4DFC-ABF1-674CCD068115}" name="Harga Jual" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{10F71EA0-F0EC-4DFE-A2AB-43A6531E908A}" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{10F71EA0-F0EC-4DFE-A2AB-43A6531E908A}" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
   <autoFilter ref="A1:C5" xr:uid="{10F71EA0-F0EC-4DFE-A2AB-43A6531E908A}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0A45B6A5-0536-4D20-A5E2-7E4BD4BDCE05}" name="Kota" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{636D6F2C-8691-45F9-87EF-3C4669C8D4FE}" name="Wilayah" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{873955BF-A08E-404A-897B-9A4966E646E3}" name="Biaya Kirim per Unit" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{0A45B6A5-0536-4D20-A5E2-7E4BD4BDCE05}" name="Kota" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{636D6F2C-8691-45F9-87EF-3C4669C8D4FE}" name="Wilayah" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{873955BF-A08E-404A-897B-9A4966E646E3}" name="Biaya Kirim per Unit" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DA8C010A-5D31-4A19-AF5C-380C4883E588}" name="Table4" displayName="Table4" ref="A1:C5" totalsRowShown="0" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DA8C010A-5D31-4A19-AF5C-380C4883E588}" name="Table4" displayName="Table4" ref="A1:C5" totalsRowShown="0" headerRowBorderDxfId="15" tableBorderDxfId="14" totalsRowBorderDxfId="13">
   <autoFilter ref="A1:C5" xr:uid="{DA8C010A-5D31-4A19-AF5C-380C4883E588}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0FEAB7C0-9975-4BB3-97C0-65272C933D59}" name="Kode Promo" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{7268390E-5820-4F31-AA85-AF2D35552741}" name="Besaran Diskon" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{95D74BC3-E24F-46CD-A305-3DE4BBBB44D9}" name="Keterangan Syarat" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{0FEAB7C0-9975-4BB3-97C0-65272C933D59}" name="Kode Promo" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{7268390E-5820-4F31-AA85-AF2D35552741}" name="Besaran Diskon" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{95D74BC3-E24F-46CD-A305-3DE4BBBB44D9}" name="Keterangan Syarat" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2D8BD81D-9F01-414B-A4EE-0F3E3758FAD8}" name="Table5" displayName="Table5" ref="A5:D12" totalsRowShown="0" headerRowDxfId="53" dataDxfId="51" headerRowBorderDxfId="52" tableBorderDxfId="50" totalsRowBorderDxfId="49" dataCellStyle="Percent">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2D8BD81D-9F01-414B-A4EE-0F3E3758FAD8}" name="Table5" displayName="Table5" ref="A5:D12" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5" dataCellStyle="Percent">
   <autoFilter ref="A5:D12" xr:uid="{2D8BD81D-9F01-414B-A4EE-0F3E3758FAD8}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C0DB13C7-69BD-4B04-AD37-A903E9718342}" name="Nomor Soal" dataDxfId="48" dataCellStyle="Percent"/>
-    <tableColumn id="2" xr3:uid="{0024CB6F-4755-4E2C-8351-AEB7946C3495}" name="Kategori Keterampilan" dataDxfId="47" dataCellStyle="Percent"/>
-    <tableColumn id="3" xr3:uid="{E54C8867-FE29-4C25-A0EC-89B409159D7E}" name="Instruksi Pengerjaan" dataDxfId="46" dataCellStyle="Percent"/>
-    <tableColumn id="4" xr3:uid="{2E3FF913-4ABB-4AED-AD44-A625313457B5}" name="Output yang Diharapkan" dataDxfId="45" dataCellStyle="Percent"/>
+    <tableColumn id="1" xr3:uid="{C0DB13C7-69BD-4B04-AD37-A903E9718342}" name="Nomor Soal" dataDxfId="4" dataCellStyle="Percent"/>
+    <tableColumn id="2" xr3:uid="{0024CB6F-4755-4E2C-8351-AEB7946C3495}" name="Kategori Keterampilan" dataDxfId="3" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{E54C8867-FE29-4C25-A0EC-89B409159D7E}" name="Instruksi Pengerjaan" dataDxfId="2" dataCellStyle="Percent"/>
+    <tableColumn id="4" xr3:uid="{2E3FF913-4ABB-4AED-AD44-A625313457B5}" name="Output yang Diharapkan" dataDxfId="1" dataCellStyle="Percent"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -50200,7 +50203,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -50214,55 +50217,55 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>539</v>
       </c>
-      <c r="B4" s="48">
-        <v>29.245275888133023</v>
+      <c r="B4" s="26">
+        <v>141715000</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>534</v>
       </c>
-      <c r="B5" s="48">
-        <v>22.367766203703731</v>
+      <c r="B5" s="26">
+        <v>568125000</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>536</v>
       </c>
-      <c r="B6" s="48">
-        <v>24.156746031746</v>
+      <c r="B6" s="26">
+        <v>95700000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>541</v>
       </c>
-      <c r="B7" s="48">
-        <v>30.3317507558579</v>
+      <c r="B7" s="26">
+        <v>289005000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>538</v>
       </c>
-      <c r="B8" s="48">
-        <v>24.34109477124181</v>
+      <c r="B8" s="26">
+        <v>219085000</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>593</v>
-      </c>
-      <c r="B9" s="48">
-        <v>130.44263365068247</v>
+        <v>590</v>
+      </c>
+      <c r="B9" s="26">
+        <v>1313630000</v>
       </c>
     </row>
   </sheetData>
@@ -50418,286 +50421,295 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F40FF0D9-1060-45F4-9C12-4DBC7EB60C19}">
-  <dimension ref="A1:Z13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD4BEB8-677A-470D-90C9-6F3AB7B3C0BA}">
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="1.140625" style="14" customWidth="1"/>
-    <col min="2" max="7" width="9.140625" style="14"/>
-    <col min="8" max="8" width="1.140625" style="14" customWidth="1"/>
-    <col min="9" max="13" width="9.140625" style="14"/>
-    <col min="14" max="14" width="1.140625" style="14" customWidth="1"/>
-    <col min="15" max="19" width="9.140625" style="14"/>
-    <col min="20" max="20" width="1.140625" style="14" customWidth="1"/>
-    <col min="21" max="25" width="9.140625" style="14"/>
-    <col min="26" max="26" width="1.140625" style="14" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="14"/>
+    <col min="2" max="6" width="9.140625" style="14"/>
+    <col min="7" max="7" width="1.140625" style="14" customWidth="1"/>
+    <col min="8" max="12" width="9.140625" style="14"/>
+    <col min="13" max="13" width="1.140625" style="14" customWidth="1"/>
+    <col min="14" max="18" width="9.140625" style="14"/>
+    <col min="19" max="19" width="1.140625" style="14" customWidth="1"/>
+    <col min="20" max="24" width="9.140625" style="14"/>
+    <col min="25" max="25" width="1.140625" style="14" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="43" t="s">
+        <v>587</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="42"/>
+    </row>
+    <row r="2" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="43"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="42"/>
+    </row>
+    <row r="3" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="42"/>
+    </row>
+    <row r="4" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
+      <c r="V4" s="43"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="43"/>
+      <c r="Y4" s="43"/>
+      <c r="Z4" s="42"/>
+    </row>
+    <row r="5" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="43"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="43"/>
+      <c r="U5" s="43"/>
+      <c r="V5" s="43"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="43"/>
+      <c r="Y5" s="43"/>
+      <c r="Z5" s="42"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="48"/>
+      <c r="B6" s="46" t="s">
         <v>588</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="42"/>
-      <c r="W1" s="42"/>
-      <c r="X1" s="42"/>
-      <c r="Y1" s="42"/>
-      <c r="Z1" s="42"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="42"/>
-      <c r="W2" s="42"/>
-      <c r="X2" s="42"/>
-      <c r="Y2" s="42"/>
-      <c r="Z2" s="42"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="42"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="42"/>
-      <c r="U3" s="42"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
-      <c r="X3" s="42"/>
-      <c r="Y3" s="42"/>
-      <c r="Z3" s="42"/>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="44" t="s">
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="46" t="s">
         <v>589</v>
       </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="I4" s="44" t="s">
-        <v>590</v>
-      </c>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="O4" s="44" t="s">
-        <v>591</v>
-      </c>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44"/>
-      <c r="U4" s="44" t="s">
-        <v>592</v>
-      </c>
-      <c r="V4" s="44"/>
-      <c r="W4" s="44"/>
-      <c r="X4" s="44"/>
-      <c r="Y4" s="44"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="44"/>
-      <c r="U5" s="44"/>
-      <c r="V5" s="44"/>
-      <c r="W5" s="44"/>
-      <c r="X5" s="44"/>
-      <c r="Y5" s="44"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="52">
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45"/>
+      <c r="R6" s="45"/>
+      <c r="T6" s="44"/>
+      <c r="U6" s="44"/>
+      <c r="V6" s="44"/>
+      <c r="W6" s="44"/>
+      <c r="X6" s="44"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="48"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="45"/>
+      <c r="P7" s="45"/>
+      <c r="Q7" s="45"/>
+      <c r="R7" s="45"/>
+      <c r="T7" s="44"/>
+      <c r="U7" s="44"/>
+      <c r="V7" s="44"/>
+      <c r="W7" s="44"/>
+      <c r="X7" s="44"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="47">
         <v>5820200000</v>
       </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="50">
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
+      <c r="H8" s="47">
         <v>1313630000</v>
       </c>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="O6" s="49">
-        <v>130.44263365068247</v>
-      </c>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="U6" s="45"/>
-      <c r="V6" s="45"/>
-      <c r="W6" s="45"/>
-      <c r="X6" s="45"/>
-      <c r="Y6" s="45"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="50"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49"/>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="U7" s="45"/>
-      <c r="V7" s="45"/>
-      <c r="W7" s="45"/>
-      <c r="X7" s="45"/>
-      <c r="Y7" s="45"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="43"/>
-      <c r="S8" s="43"/>
-      <c r="T8" s="43"/>
-      <c r="U8" s="43"/>
-      <c r="V8" s="43"/>
-      <c r="W8" s="43"/>
-      <c r="X8" s="43"/>
-      <c r="Y8" s="43"/>
-      <c r="Z8" s="43"/>
+      <c r="I8" s="47"/>
+      <c r="J8" s="47"/>
+      <c r="K8" s="47"/>
+      <c r="L8" s="47"/>
+      <c r="N8" s="45"/>
+      <c r="O8" s="45"/>
+      <c r="P8" s="45"/>
+      <c r="Q8" s="45"/>
+      <c r="R8" s="45"/>
+      <c r="T8" s="44"/>
+      <c r="U8" s="44"/>
+      <c r="V8" s="44"/>
+      <c r="W8" s="44"/>
+      <c r="X8" s="44"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="47"/>
+      <c r="L9" s="47"/>
+      <c r="N9" s="45"/>
+      <c r="O9" s="45"/>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="45"/>
+      <c r="R9" s="45"/>
+      <c r="T9" s="44"/>
+      <c r="U9" s="44"/>
+      <c r="V9" s="44"/>
+      <c r="W9" s="44"/>
+      <c r="X9" s="44"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="M10" s="46"/>
-      <c r="N10" s="46"/>
-      <c r="O10" s="46"/>
-      <c r="P10" s="46"/>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="46"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="M11" s="46"/>
-      <c r="N11" s="46"/>
-      <c r="O11" s="46"/>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="46"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="M12" s="47"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="M13" s="47"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="47"/>
-      <c r="R13" s="47"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="47"/>
+      <c r="N10" s="45"/>
+      <c r="O10" s="45"/>
+      <c r="P10" s="45"/>
+      <c r="Q10" s="45"/>
+      <c r="R10" s="45"/>
+      <c r="T10" s="44"/>
+      <c r="U10" s="44"/>
+      <c r="V10" s="44"/>
+      <c r="W10" s="44"/>
+      <c r="X10" s="44"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="I4:M5"/>
-    <mergeCell ref="O4:S5"/>
-    <mergeCell ref="U4:Y5"/>
-    <mergeCell ref="I6:M7"/>
-    <mergeCell ref="O6:S7"/>
-    <mergeCell ref="U6:Y7"/>
-    <mergeCell ref="A1:Z3"/>
-    <mergeCell ref="B4:G5"/>
-    <mergeCell ref="B6:G7"/>
+  <mergeCells count="7">
+    <mergeCell ref="N6:R10"/>
+    <mergeCell ref="T6:X10"/>
+    <mergeCell ref="A1:Y5"/>
+    <mergeCell ref="B6:F7"/>
+    <mergeCell ref="B8:F10"/>
+    <mergeCell ref="H6:L7"/>
+    <mergeCell ref="H8:L10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Analisis Retail Bisnis Omni-Channel.xlsx
+++ b/Analisis Retail Bisnis Omni-Channel.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aldy\Documents\DATA ANALYST\MICROSOFT EXCEL\PORTOFOLIO\Analisis Retail Bisnis Omni-Channel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C5CC35-AD3A-4B58-AA65-CD1A76E986E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94E4536-B5C3-411B-931B-277CBB987045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="1" activeTab="6" xr2:uid="{0FABD09F-C599-4D8F-AE1F-66CDC9C9D3DB}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2109" uniqueCount="595">
   <si>
     <t>ID_Transaksi</t>
   </si>
@@ -1818,7 +1818,16 @@
     <t>Grand Total</t>
   </si>
   <si>
-    <t>Sum of Laba_Kotor</t>
+    <t>OVERALL PROFIT MARGIN%</t>
+  </si>
+  <si>
+    <t>Sum of Total_Pendapatan_Kotor</t>
+  </si>
+  <si>
+    <t>TOTAL UNITS SOLD</t>
+  </si>
+  <si>
+    <t>Sum of Margin_Keuntungan</t>
   </si>
 </sst>
 </file>
@@ -2025,7 +2034,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2145,13 +2154,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2160,7 +2164,13 @@
     <xf numFmtId="167" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3528,6 +3538,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF8C6047"/>
       <color rgb="FFFFFF9F"/>
       <color rgb="FFFFFFA7"/>
       <color rgb="FFFFFF5D"/>
@@ -3542,6 +3553,1193 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Analisis Retail Bisnis Omni-Channel.xlsx]analisis!analisis</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:srgbClr val="8C6047"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>analisis!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Total_Pendapatan_Kotor</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>analisis!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Kursi Kerja Ergonomis</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Laptop Pro 14</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mechanical Keyboard</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Meja Adjustable</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Monitor Ergonomis 27</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>analisis!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>567000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2676000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>510000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1071000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>996200000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-63F6-46B0-9AFF-3C647A8F7E08}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="1382423807"/>
+        <c:axId val="1382839439"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>analisis!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Margin_Keuntungan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="8C6047"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>analisis!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Kursi Kerja Ergonomis</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Laptop Pro 14</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mechanical Keyboard</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Meja Adjustable</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Monitor Ergonomis 27</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>analisis!$C$4:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>29.245275888133023</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.367766203703731</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24.156746031746</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30.3317507558579</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24.34109477124181</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-63F6-46B0-9AFF-3C647A8F7E08}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1440727599"/>
+        <c:axId val="1382842799"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1382423807"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1382839439"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1382839439"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="85000"/>
+                    <a:lumOff val="15000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1382423807"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1382842799"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1440727599"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1440727599"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1382842799"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="322">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>952499</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0580262D-F0D7-6767-4290-2A419F72E9FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4082,7 +5280,28 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Margin_Keuntungan" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.10294117647058823" maxValue="0.41666666666666669"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.10294117647058823" maxValue="0.41666666666666669" count="20">
+        <n v="0.21064814814814814"/>
+        <n v="0.18487394957983194"/>
+        <n v="0.40476190476190477"/>
+        <n v="0.20404411764705882"/>
+        <n v="0.35846560846560849"/>
+        <n v="0.28875000000000001"/>
+        <n v="0.15966386554621848"/>
+        <n v="0.26636904761904762"/>
+        <n v="0.30555555555555558"/>
+        <n v="0.1598639455782313"/>
+        <n v="0.28749999999999998"/>
+        <n v="0.24264705882352941"/>
+        <n v="0.35185185185185186"/>
+        <n v="0.10294117647058823"/>
+        <n v="0.41666666666666669"/>
+        <n v="0.10781250000000001"/>
+        <n v="0.37908496732026142"/>
+        <n v="0.17176870748299319"/>
+        <n v="0.36764705882352944"/>
+        <n v="0.24702380952380953"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Days (Tanggal)" numFmtId="0" databaseField="0">
       <fieldGroup base="1">
@@ -4509,7 +5728,7 @@
     <n v="21600000"/>
     <n v="17050000"/>
     <x v="0"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0002"/>
@@ -4529,7 +5748,7 @@
     <n v="2975000"/>
     <n v="2425000"/>
     <x v="1"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0003"/>
@@ -4549,7 +5768,7 @@
     <n v="2100000"/>
     <n v="1250000"/>
     <x v="2"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0004"/>
@@ -4569,7 +5788,7 @@
     <n v="8160000"/>
     <n v="6495000"/>
     <x v="3"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0005"/>
@@ -4589,7 +5808,7 @@
     <n v="7560000"/>
     <n v="4850000"/>
     <x v="4"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0006"/>
@@ -4609,7 +5828,7 @@
     <n v="12000000"/>
     <n v="8535000"/>
     <x v="5"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0007"/>
@@ -4629,7 +5848,7 @@
     <n v="3570000"/>
     <n v="3000000"/>
     <x v="6"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0008"/>
@@ -4649,7 +5868,7 @@
     <n v="13440000"/>
     <n v="9860000"/>
     <x v="7"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0009"/>
@@ -4669,7 +5888,7 @@
     <n v="6120000"/>
     <n v="4250000"/>
     <x v="8"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0010"/>
@@ -4689,7 +5908,7 @@
     <n v="4410000"/>
     <n v="3705000"/>
     <x v="9"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0011"/>
@@ -4709,7 +5928,7 @@
     <n v="12000000"/>
     <n v="8550000"/>
     <x v="10"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0012"/>
@@ -4729,7 +5948,7 @@
     <n v="5440000"/>
     <n v="4120000"/>
     <x v="11"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0013"/>
@@ -4749,7 +5968,7 @@
     <n v="3780000"/>
     <n v="2450000"/>
     <x v="12"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0014"/>
@@ -4769,7 +5988,7 @@
     <n v="9520000"/>
     <n v="8540000"/>
     <x v="13"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0015"/>
@@ -4789,7 +6008,7 @@
     <n v="4200000"/>
     <n v="2450000"/>
     <x v="14"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0016"/>
@@ -4809,7 +6028,7 @@
     <n v="19200000"/>
     <n v="17130000"/>
     <x v="15"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0017"/>
@@ -4829,7 +6048,7 @@
     <n v="3825000"/>
     <n v="2375000"/>
     <x v="16"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0018"/>
@@ -4849,7 +6068,7 @@
     <n v="8820000"/>
     <n v="7305000"/>
     <x v="17"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0019"/>
@@ -4869,7 +6088,7 @@
     <n v="6800000"/>
     <n v="4300000"/>
     <x v="18"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0020"/>
@@ -4889,7 +6108,7 @@
     <n v="6720000"/>
     <n v="5060000"/>
     <x v="19"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0021"/>
@@ -4909,7 +6128,7 @@
     <n v="32400000"/>
     <n v="25575000"/>
     <x v="20"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0022"/>
@@ -4929,7 +6148,7 @@
     <n v="4165000"/>
     <n v="3395000"/>
     <x v="21"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0023"/>
@@ -4949,7 +6168,7 @@
     <n v="4200000"/>
     <n v="2500000"/>
     <x v="22"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0024"/>
@@ -4969,7 +6188,7 @@
     <n v="2720000"/>
     <n v="2165000"/>
     <x v="23"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0025"/>
@@ -4989,7 +6208,7 @@
     <n v="11340000"/>
     <n v="7275000"/>
     <x v="24"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0026"/>
@@ -5009,7 +6228,7 @@
     <n v="24000000"/>
     <n v="17070000"/>
     <x v="25"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0027"/>
@@ -5029,7 +6248,7 @@
     <n v="2380000"/>
     <n v="2000000"/>
     <x v="26"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0028"/>
@@ -5049,7 +6268,7 @@
     <n v="3360000"/>
     <n v="2465000"/>
     <x v="27"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0029"/>
@@ -5069,7 +6288,7 @@
     <n v="15300000"/>
     <n v="10625000"/>
     <x v="28"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0030"/>
@@ -5089,7 +6308,7 @@
     <n v="2940000"/>
     <n v="2470000"/>
     <x v="29"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0031"/>
@@ -5109,7 +6328,7 @@
     <n v="36000000"/>
     <n v="25650000"/>
     <x v="30"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0032"/>
@@ -5129,7 +6348,7 @@
     <n v="4080000"/>
     <n v="3090000"/>
     <x v="31"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0033"/>
@@ -5149,7 +6368,7 @@
     <n v="1890000"/>
     <n v="1225000"/>
     <x v="32"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0034"/>
@@ -5169,7 +6388,7 @@
     <n v="4760000"/>
     <n v="4270000"/>
     <x v="33"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0035"/>
@@ -5189,7 +6408,7 @@
     <n v="16800000"/>
     <n v="9800000"/>
     <x v="34"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0036"/>
@@ -5209,7 +6428,7 @@
     <n v="9600000"/>
     <n v="8565000"/>
     <x v="35"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0037"/>
@@ -5229,7 +6448,7 @@
     <n v="2295000"/>
     <n v="1425000"/>
     <x v="36"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0038"/>
@@ -5249,7 +6468,7 @@
     <n v="5880000"/>
     <n v="4870000"/>
     <x v="37"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0039"/>
@@ -5269,7 +6488,7 @@
     <n v="17000000"/>
     <n v="10750000"/>
     <x v="38"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0040"/>
@@ -5289,7 +6508,7 @@
     <n v="3360000"/>
     <n v="2530000"/>
     <x v="39"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0041"/>
@@ -5309,7 +6528,7 @@
     <n v="43200000"/>
     <n v="34100000"/>
     <x v="40"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0042"/>
@@ -5329,7 +6548,7 @@
     <n v="4760000"/>
     <n v="3880000"/>
     <x v="41"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0043"/>
@@ -5349,7 +6568,7 @@
     <n v="2100000"/>
     <n v="1250000"/>
     <x v="2"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0044"/>
@@ -5369,7 +6588,7 @@
     <n v="8160000"/>
     <n v="6495000"/>
     <x v="3"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0045"/>
@@ -5389,7 +6608,7 @@
     <n v="7560000"/>
     <n v="4850000"/>
     <x v="4"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0046"/>
@@ -5409,7 +6628,7 @@
     <n v="12000000"/>
     <n v="8535000"/>
     <x v="5"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0047"/>
@@ -5429,7 +6648,7 @@
     <n v="2975000"/>
     <n v="2500000"/>
     <x v="42"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0048"/>
@@ -5449,7 +6668,7 @@
     <n v="10080000"/>
     <n v="7395000"/>
     <x v="43"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0049"/>
@@ -5469,7 +6688,7 @@
     <n v="6120000"/>
     <n v="4250000"/>
     <x v="8"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0050"/>
@@ -5489,7 +6708,7 @@
     <n v="5880000"/>
     <n v="4940000"/>
     <x v="44"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0051"/>
@@ -5509,7 +6728,7 @@
     <n v="24000000"/>
     <n v="17100000"/>
     <x v="45"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0052"/>
@@ -5529,7 +6748,7 @@
     <n v="4760000"/>
     <n v="3605000"/>
     <x v="46"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0053"/>
@@ -5549,7 +6768,7 @@
     <n v="5670000"/>
     <n v="3675000"/>
     <x v="47"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0054"/>
@@ -5569,7 +6788,7 @@
     <n v="2380000"/>
     <n v="2135000"/>
     <x v="48"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0055"/>
@@ -5589,7 +6808,7 @@
     <n v="8400000"/>
     <n v="4900000"/>
     <x v="49"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0056"/>
@@ -5609,7 +6828,7 @@
     <n v="28800000"/>
     <n v="25695000"/>
     <x v="50"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0057"/>
@@ -5629,7 +6848,7 @@
     <n v="3060000"/>
     <n v="1900000"/>
     <x v="51"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0058"/>
@@ -5649,7 +6868,7 @@
     <n v="2940000"/>
     <n v="2435000"/>
     <x v="52"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0059"/>
@@ -5669,7 +6888,7 @@
     <n v="20400000"/>
     <n v="12900000"/>
     <x v="53"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0060"/>
@@ -5689,7 +6908,7 @@
     <n v="3360000"/>
     <n v="2530000"/>
     <x v="39"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0061"/>
@@ -5709,7 +6928,7 @@
     <n v="21600000"/>
     <n v="17050000"/>
     <x v="0"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0062"/>
@@ -5729,7 +6948,7 @@
     <n v="3570000"/>
     <n v="2910000"/>
     <x v="54"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0063"/>
@@ -5749,7 +6968,7 @@
     <n v="6300000"/>
     <n v="3750000"/>
     <x v="55"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0064"/>
@@ -5769,7 +6988,7 @@
     <n v="10880000"/>
     <n v="8660000"/>
     <x v="56"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0065"/>
@@ -5789,7 +7008,7 @@
     <n v="3780000"/>
     <n v="2425000"/>
     <x v="57"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0066"/>
@@ -5809,7 +7028,7 @@
     <n v="36000000"/>
     <n v="25605000"/>
     <x v="58"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0067"/>
@@ -5829,7 +7048,7 @@
     <n v="2975000"/>
     <n v="2500000"/>
     <x v="42"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0068"/>
@@ -5849,7 +7068,7 @@
     <n v="6720000"/>
     <n v="4930000"/>
     <x v="59"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0069"/>
@@ -5869,7 +7088,7 @@
     <n v="9180000"/>
     <n v="6375000"/>
     <x v="60"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0070"/>
@@ -5889,7 +7108,7 @@
     <n v="1470000"/>
     <n v="1235000"/>
     <x v="61"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0071"/>
@@ -5909,7 +7128,7 @@
     <n v="24000000"/>
     <n v="17100000"/>
     <x v="45"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0072"/>
@@ -5929,7 +7148,7 @@
     <n v="4760000"/>
     <n v="3605000"/>
     <x v="46"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0073"/>
@@ -5949,7 +7168,7 @@
     <n v="7560000"/>
     <n v="4900000"/>
     <x v="62"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0074"/>
@@ -5969,7 +7188,7 @@
     <n v="4760000"/>
     <n v="4270000"/>
     <x v="33"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0075"/>
@@ -5989,7 +7208,7 @@
     <n v="12600000"/>
     <n v="7350000"/>
     <x v="63"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0076"/>
@@ -6009,7 +7228,7 @@
     <n v="9600000"/>
     <n v="8565000"/>
     <x v="35"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0077"/>
@@ -6029,7 +7248,7 @@
     <n v="3825000"/>
     <n v="2375000"/>
     <x v="16"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0078"/>
@@ -6049,7 +7268,7 @@
     <n v="11760000"/>
     <n v="9740000"/>
     <x v="64"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0079"/>
@@ -6069,7 +7288,7 @@
     <n v="3400000"/>
     <n v="2150000"/>
     <x v="65"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0080"/>
@@ -6089,7 +7308,7 @@
     <n v="5040000"/>
     <n v="3795000"/>
     <x v="66"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0081"/>
@@ -6109,7 +7328,7 @@
     <n v="21600000"/>
     <n v="17050000"/>
     <x v="0"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0082"/>
@@ -6129,7 +7348,7 @@
     <n v="4760000"/>
     <n v="3880000"/>
     <x v="41"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0083"/>
@@ -6149,7 +7368,7 @@
     <n v="4200000"/>
     <n v="2500000"/>
     <x v="22"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0084"/>
@@ -6169,7 +7388,7 @@
     <n v="13600000"/>
     <n v="10825000"/>
     <x v="67"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0085"/>
@@ -6189,7 +7408,7 @@
     <n v="7560000"/>
     <n v="4850000"/>
     <x v="4"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0086"/>
@@ -6209,7 +7428,7 @@
     <n v="12000000"/>
     <n v="8535000"/>
     <x v="5"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0087"/>
@@ -6229,7 +7448,7 @@
     <n v="2380000"/>
     <n v="2000000"/>
     <x v="26"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0088"/>
@@ -6249,7 +7468,7 @@
     <n v="10080000"/>
     <n v="7395000"/>
     <x v="43"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0089"/>
@@ -6269,7 +7488,7 @@
     <n v="6120000"/>
     <n v="4250000"/>
     <x v="8"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0090"/>
@@ -6289,7 +7508,7 @@
     <n v="7350000"/>
     <n v="6175000"/>
     <x v="68"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0091"/>
@@ -6309,7 +7528,7 @@
     <n v="36000000"/>
     <n v="25650000"/>
     <x v="30"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0092"/>
@@ -6329,7 +7548,7 @@
     <n v="4080000"/>
     <n v="3090000"/>
     <x v="31"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0093"/>
@@ -6349,7 +7568,7 @@
     <n v="1890000"/>
     <n v="1225000"/>
     <x v="32"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0094"/>
@@ -6369,7 +7588,7 @@
     <n v="7140000"/>
     <n v="6405000"/>
     <x v="69"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0095"/>
@@ -6389,7 +7608,7 @@
     <n v="8400000"/>
     <n v="4900000"/>
     <x v="49"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0096"/>
@@ -6409,7 +7628,7 @@
     <n v="19200000"/>
     <n v="17130000"/>
     <x v="15"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0097"/>
@@ -6429,7 +7648,7 @@
     <n v="5355000"/>
     <n v="3325000"/>
     <x v="70"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0098"/>
@@ -6449,7 +7668,7 @@
     <n v="2940000"/>
     <n v="2435000"/>
     <x v="52"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0099"/>
@@ -6469,7 +7688,7 @@
     <n v="13600000"/>
     <n v="8600000"/>
     <x v="71"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0100"/>
@@ -6489,7 +7708,7 @@
     <n v="3360000"/>
     <n v="2530000"/>
     <x v="39"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0101"/>
@@ -6509,7 +7728,7 @@
     <n v="10800000"/>
     <n v="8525000"/>
     <x v="72"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0102"/>
@@ -6529,7 +7748,7 @@
     <n v="2975000"/>
     <n v="2425000"/>
     <x v="1"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0103"/>
@@ -6549,7 +7768,7 @@
     <n v="6300000"/>
     <n v="3750000"/>
     <x v="55"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0104"/>
@@ -6569,7 +7788,7 @@
     <n v="5440000"/>
     <n v="4330000"/>
     <x v="73"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0105"/>
@@ -6589,7 +7808,7 @@
     <n v="15120000"/>
     <n v="9700000"/>
     <x v="74"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0106"/>
@@ -6609,7 +7828,7 @@
     <n v="24000000"/>
     <n v="17070000"/>
     <x v="25"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0107"/>
@@ -6629,7 +7848,7 @@
     <n v="3570000"/>
     <n v="3000000"/>
     <x v="6"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0108"/>
@@ -6649,7 +7868,7 @@
     <n v="3360000"/>
     <n v="2465000"/>
     <x v="27"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0109"/>
@@ -6669,7 +7888,7 @@
     <n v="9180000"/>
     <n v="6375000"/>
     <x v="60"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0110"/>
@@ -6689,7 +7908,7 @@
     <n v="2940000"/>
     <n v="2470000"/>
     <x v="29"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0111"/>
@@ -6709,7 +7928,7 @@
     <n v="48000000"/>
     <n v="34200000"/>
     <x v="75"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0112"/>
@@ -6729,7 +7948,7 @@
     <n v="5440000"/>
     <n v="4120000"/>
     <x v="11"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0113"/>
@@ -6749,7 +7968,7 @@
     <n v="3780000"/>
     <n v="2450000"/>
     <x v="12"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0114"/>
@@ -6769,7 +7988,7 @@
     <n v="11900000"/>
     <n v="10675000"/>
     <x v="76"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0115"/>
@@ -6789,7 +8008,7 @@
     <n v="4200000"/>
     <n v="2450000"/>
     <x v="14"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0116"/>
@@ -6809,7 +8028,7 @@
     <n v="28800000"/>
     <n v="25695000"/>
     <x v="50"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0117"/>
@@ -6829,7 +8048,7 @@
     <n v="3060000"/>
     <n v="1900000"/>
     <x v="51"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0118"/>
@@ -6849,7 +8068,7 @@
     <n v="5880000"/>
     <n v="4870000"/>
     <x v="37"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0119"/>
@@ -6869,7 +8088,7 @@
     <n v="10200000"/>
     <n v="6450000"/>
     <x v="77"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0120"/>
@@ -6889,7 +8108,7 @@
     <n v="1680000"/>
     <n v="1265000"/>
     <x v="78"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0121"/>
@@ -6909,7 +8128,7 @@
     <n v="21600000"/>
     <n v="17050000"/>
     <x v="0"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0122"/>
@@ -6929,7 +8148,7 @@
     <n v="4165000"/>
     <n v="3395000"/>
     <x v="21"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0123"/>
@@ -6949,7 +8168,7 @@
     <n v="8400000"/>
     <n v="5000000"/>
     <x v="79"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0124"/>
@@ -6969,7 +8188,7 @@
     <n v="5440000"/>
     <n v="4330000"/>
     <x v="73"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0125"/>
@@ -6989,7 +8208,7 @@
     <n v="11340000"/>
     <n v="7275000"/>
     <x v="24"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0126"/>
@@ -7009,7 +8228,7 @@
     <n v="12000000"/>
     <n v="8535000"/>
     <x v="5"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0127"/>
@@ -7029,7 +8248,7 @@
     <n v="2975000"/>
     <n v="2500000"/>
     <x v="42"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0128"/>
@@ -7049,7 +8268,7 @@
     <n v="6720000"/>
     <n v="4930000"/>
     <x v="59"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0129"/>
@@ -7069,7 +8288,7 @@
     <n v="12240000"/>
     <n v="8500000"/>
     <x v="80"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0130"/>
@@ -7089,7 +8308,7 @@
     <n v="4410000"/>
     <n v="3705000"/>
     <x v="9"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0131"/>
@@ -7109,7 +8328,7 @@
     <n v="24000000"/>
     <n v="17100000"/>
     <x v="45"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0132"/>
@@ -7129,7 +8348,7 @@
     <n v="4080000"/>
     <n v="3090000"/>
     <x v="31"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0133"/>
@@ -7149,7 +8368,7 @@
     <n v="1890000"/>
     <n v="1225000"/>
     <x v="32"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0134"/>
@@ -7169,7 +8388,7 @@
     <n v="7140000"/>
     <n v="6405000"/>
     <x v="69"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0135"/>
@@ -7189,7 +8408,7 @@
     <n v="21000000"/>
     <n v="12250000"/>
     <x v="81"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0136"/>
@@ -7209,7 +8428,7 @@
     <n v="19200000"/>
     <n v="17130000"/>
     <x v="15"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0137"/>
@@ -7229,7 +8448,7 @@
     <n v="2295000"/>
     <n v="1425000"/>
     <x v="36"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0138"/>
@@ -7249,7 +8468,7 @@
     <n v="11760000"/>
     <n v="9740000"/>
     <x v="64"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0139"/>
@@ -7269,7 +8488,7 @@
     <n v="6800000"/>
     <n v="4300000"/>
     <x v="18"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0140"/>
@@ -7289,7 +8508,7 @@
     <n v="8400000"/>
     <n v="6325000"/>
     <x v="82"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0141"/>
@@ -7309,7 +8528,7 @@
     <n v="32400000"/>
     <n v="25575000"/>
     <x v="20"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0142"/>
@@ -7329,7 +8548,7 @@
     <n v="4760000"/>
     <n v="3880000"/>
     <x v="41"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0143"/>
@@ -7349,7 +8568,7 @@
     <n v="2100000"/>
     <n v="1250000"/>
     <x v="2"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0144"/>
@@ -7369,7 +8588,7 @@
     <n v="10880000"/>
     <n v="8660000"/>
     <x v="56"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0145"/>
@@ -7389,7 +8608,7 @@
     <n v="7560000"/>
     <n v="4850000"/>
     <x v="4"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0146"/>
@@ -7409,7 +8628,7 @@
     <n v="36000000"/>
     <n v="25605000"/>
     <x v="58"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0147"/>
@@ -7429,7 +8648,7 @@
     <n v="2975000"/>
     <n v="2500000"/>
     <x v="42"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0148"/>
@@ -7449,7 +8668,7 @@
     <n v="3360000"/>
     <n v="2465000"/>
     <x v="27"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0149"/>
@@ -7469,7 +8688,7 @@
     <n v="6120000"/>
     <n v="4250000"/>
     <x v="8"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0150"/>
@@ -7489,7 +8708,7 @@
     <n v="5880000"/>
     <n v="4940000"/>
     <x v="44"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0151"/>
@@ -7509,7 +8728,7 @@
     <n v="12000000"/>
     <n v="8550000"/>
     <x v="10"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0152"/>
@@ -7529,7 +8748,7 @@
     <n v="4760000"/>
     <n v="3605000"/>
     <x v="46"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0153"/>
@@ -7549,7 +8768,7 @@
     <n v="3780000"/>
     <n v="2450000"/>
     <x v="12"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0154"/>
@@ -7569,7 +8788,7 @@
     <n v="14280000"/>
     <n v="12810000"/>
     <x v="83"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0155"/>
@@ -7589,7 +8808,7 @@
     <n v="12600000"/>
     <n v="7350000"/>
     <x v="63"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0156"/>
@@ -7609,7 +8828,7 @@
     <n v="9600000"/>
     <n v="8565000"/>
     <x v="35"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0157"/>
@@ -7629,7 +8848,7 @@
     <n v="3060000"/>
     <n v="1900000"/>
     <x v="51"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0158"/>
@@ -7649,7 +8868,7 @@
     <n v="5880000"/>
     <n v="4870000"/>
     <x v="37"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0159"/>
@@ -7669,7 +8888,7 @@
     <n v="17000000"/>
     <n v="10750000"/>
     <x v="38"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0160"/>
@@ -7689,7 +8908,7 @@
     <n v="5040000"/>
     <n v="3795000"/>
     <x v="66"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0161"/>
@@ -7709,7 +8928,7 @@
     <n v="21600000"/>
     <n v="17050000"/>
     <x v="0"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0162"/>
@@ -7729,7 +8948,7 @@
     <n v="3570000"/>
     <n v="2910000"/>
     <x v="54"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0163"/>
@@ -7749,7 +8968,7 @@
     <n v="4200000"/>
     <n v="2500000"/>
     <x v="22"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0164"/>
@@ -7769,7 +8988,7 @@
     <n v="8160000"/>
     <n v="6495000"/>
     <x v="3"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0165"/>
@@ -7789,7 +9008,7 @@
     <n v="3780000"/>
     <n v="2425000"/>
     <x v="57"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0166"/>
@@ -7809,7 +9028,7 @@
     <n v="48000000"/>
     <n v="34140000"/>
     <x v="84"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0167"/>
@@ -7829,7 +9048,7 @@
     <n v="4165000"/>
     <n v="3500000"/>
     <x v="32"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0168"/>
@@ -7849,7 +9068,7 @@
     <n v="6720000"/>
     <n v="4930000"/>
     <x v="59"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0169"/>
@@ -7869,7 +9088,7 @@
     <n v="3060000"/>
     <n v="2125000"/>
     <x v="85"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0170"/>
@@ -7889,7 +9108,7 @@
     <n v="4410000"/>
     <n v="3705000"/>
     <x v="9"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0171"/>
@@ -7909,7 +9128,7 @@
     <n v="24000000"/>
     <n v="17100000"/>
     <x v="45"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0172"/>
@@ -7929,7 +9148,7 @@
     <n v="5440000"/>
     <n v="4120000"/>
     <x v="11"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0173"/>
@@ -7949,7 +9168,7 @@
     <n v="9450000"/>
     <n v="6125000"/>
     <x v="86"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0174"/>
@@ -7969,7 +9188,7 @@
     <n v="4760000"/>
     <n v="4270000"/>
     <x v="33"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0175"/>
@@ -7989,7 +9208,7 @@
     <n v="16800000"/>
     <n v="9800000"/>
     <x v="34"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0176"/>
@@ -8009,7 +9228,7 @@
     <n v="19200000"/>
     <n v="17130000"/>
     <x v="15"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0177"/>
@@ -8029,7 +9248,7 @@
     <n v="2295000"/>
     <n v="1425000"/>
     <x v="36"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0178"/>
@@ -8049,7 +9268,7 @@
     <n v="14700000"/>
     <n v="12175000"/>
     <x v="87"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0179"/>
@@ -8069,7 +9288,7 @@
     <n v="3400000"/>
     <n v="2150000"/>
     <x v="65"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0180"/>
@@ -8089,7 +9308,7 @@
     <n v="6720000"/>
     <n v="5060000"/>
     <x v="19"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0181"/>
@@ -8109,7 +9328,7 @@
     <n v="32400000"/>
     <n v="25575000"/>
     <x v="20"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0182"/>
@@ -8129,7 +9348,7 @@
     <n v="2975000"/>
     <n v="2425000"/>
     <x v="1"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0183"/>
@@ -8149,7 +9368,7 @@
     <n v="2100000"/>
     <n v="1250000"/>
     <x v="2"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0184"/>
@@ -8169,7 +9388,7 @@
     <n v="5440000"/>
     <n v="4330000"/>
     <x v="73"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0185"/>
@@ -8189,7 +9408,7 @@
     <n v="11340000"/>
     <n v="7275000"/>
     <x v="24"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0186"/>
@@ -8209,7 +9428,7 @@
     <n v="12000000"/>
     <n v="8535000"/>
     <x v="5"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0187"/>
@@ -8229,7 +9448,7 @@
     <n v="3570000"/>
     <n v="3000000"/>
     <x v="6"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0188"/>
@@ -8249,7 +9468,7 @@
     <n v="13440000"/>
     <n v="9860000"/>
     <x v="7"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0189"/>
@@ -8269,7 +9488,7 @@
     <n v="6120000"/>
     <n v="4250000"/>
     <x v="8"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0190"/>
@@ -8289,7 +9508,7 @@
     <n v="4410000"/>
     <n v="3705000"/>
     <x v="9"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0191"/>
@@ -8309,7 +9528,7 @@
     <n v="24000000"/>
     <n v="17100000"/>
     <x v="45"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0192"/>
@@ -8329,7 +9548,7 @@
     <n v="4760000"/>
     <n v="3605000"/>
     <x v="46"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0193"/>
@@ -8349,7 +9568,7 @@
     <n v="7560000"/>
     <n v="4900000"/>
     <x v="62"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0194"/>
@@ -8369,7 +9588,7 @@
     <n v="2380000"/>
     <n v="2135000"/>
     <x v="48"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0195"/>
@@ -8389,7 +9608,7 @@
     <n v="8400000"/>
     <n v="4900000"/>
     <x v="49"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0196"/>
@@ -8409,7 +9628,7 @@
     <n v="28800000"/>
     <n v="25695000"/>
     <x v="50"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0197"/>
@@ -8429,7 +9648,7 @@
     <n v="3825000"/>
     <n v="2375000"/>
     <x v="16"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0198"/>
@@ -8449,7 +9668,7 @@
     <n v="5880000"/>
     <n v="4870000"/>
     <x v="37"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0199"/>
@@ -8469,7 +9688,7 @@
     <n v="13600000"/>
     <n v="8600000"/>
     <x v="71"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0200"/>
@@ -8489,7 +9708,7 @@
     <n v="1680000"/>
     <n v="1265000"/>
     <x v="78"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0201"/>
@@ -8509,7 +9728,7 @@
     <n v="21600000"/>
     <n v="17050000"/>
     <x v="0"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0202"/>
@@ -8529,7 +9748,7 @@
     <n v="4760000"/>
     <n v="3880000"/>
     <x v="41"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0203"/>
@@ -8549,7 +9768,7 @@
     <n v="6300000"/>
     <n v="3750000"/>
     <x v="55"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0204"/>
@@ -8569,7 +9788,7 @@
     <n v="13600000"/>
     <n v="10825000"/>
     <x v="67"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0205"/>
@@ -8589,7 +9808,7 @@
     <n v="3780000"/>
     <n v="2425000"/>
     <x v="57"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0206"/>
@@ -8609,7 +9828,7 @@
     <n v="24000000"/>
     <n v="17070000"/>
     <x v="25"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0207"/>
@@ -8629,7 +9848,7 @@
     <n v="2380000"/>
     <n v="2000000"/>
     <x v="26"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0208"/>
@@ -8649,7 +9868,7 @@
     <n v="10080000"/>
     <n v="7395000"/>
     <x v="43"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0209"/>
@@ -8669,7 +9888,7 @@
     <n v="9180000"/>
     <n v="6375000"/>
     <x v="60"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0210"/>
@@ -8689,7 +9908,7 @@
     <n v="2940000"/>
     <n v="2470000"/>
     <x v="29"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0211"/>
@@ -8709,7 +9928,7 @@
     <n v="48000000"/>
     <n v="34200000"/>
     <x v="75"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0212"/>
@@ -8729,7 +9948,7 @@
     <n v="4080000"/>
     <n v="3090000"/>
     <x v="31"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0213"/>
@@ -8749,7 +9968,7 @@
     <n v="1890000"/>
     <n v="1225000"/>
     <x v="32"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0214"/>
@@ -8769,7 +9988,7 @@
     <n v="9520000"/>
     <n v="8540000"/>
     <x v="13"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0215"/>
@@ -8789,7 +10008,7 @@
     <n v="8400000"/>
     <n v="4900000"/>
     <x v="49"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0216"/>
@@ -8809,7 +10028,7 @@
     <n v="9600000"/>
     <n v="8565000"/>
     <x v="35"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0217"/>
@@ -8829,7 +10048,7 @@
     <n v="3825000"/>
     <n v="2375000"/>
     <x v="16"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0218"/>
@@ -8849,7 +10068,7 @@
     <n v="8820000"/>
     <n v="7305000"/>
     <x v="17"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0219"/>
@@ -8869,7 +10088,7 @@
     <n v="6800000"/>
     <n v="4300000"/>
     <x v="18"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0220"/>
@@ -8889,7 +10108,7 @@
     <n v="6720000"/>
     <n v="5060000"/>
     <x v="19"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0221"/>
@@ -8909,7 +10128,7 @@
     <n v="32400000"/>
     <n v="25575000"/>
     <x v="20"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0222"/>
@@ -8929,7 +10148,7 @@
     <n v="4165000"/>
     <n v="3395000"/>
     <x v="21"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0223"/>
@@ -8949,7 +10168,7 @@
     <n v="4200000"/>
     <n v="2500000"/>
     <x v="22"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0224"/>
@@ -8969,7 +10188,7 @@
     <n v="2720000"/>
     <n v="2165000"/>
     <x v="23"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0225"/>
@@ -8989,7 +10208,7 @@
     <n v="15120000"/>
     <n v="9700000"/>
     <x v="74"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0226"/>
@@ -9009,7 +10228,7 @@
     <n v="24000000"/>
     <n v="17070000"/>
     <x v="25"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0227"/>
@@ -9029,7 +10248,7 @@
     <n v="3570000"/>
     <n v="3000000"/>
     <x v="6"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0228"/>
@@ -9049,7 +10268,7 @@
     <n v="3360000"/>
     <n v="2465000"/>
     <x v="27"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0229"/>
@@ -9069,7 +10288,7 @@
     <n v="15300000"/>
     <n v="10625000"/>
     <x v="28"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0230"/>
@@ -9089,7 +10308,7 @@
     <n v="4410000"/>
     <n v="3705000"/>
     <x v="9"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0231"/>
@@ -9109,7 +10328,7 @@
     <n v="12000000"/>
     <n v="8550000"/>
     <x v="10"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0232"/>
@@ -9129,7 +10348,7 @@
     <n v="5440000"/>
     <n v="4120000"/>
     <x v="11"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0233"/>
@@ -9149,7 +10368,7 @@
     <n v="3780000"/>
     <n v="2450000"/>
     <x v="12"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0234"/>
@@ -9169,7 +10388,7 @@
     <n v="7140000"/>
     <n v="6405000"/>
     <x v="69"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0235"/>
@@ -9189,7 +10408,7 @@
     <n v="16800000"/>
     <n v="9800000"/>
     <x v="34"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0236"/>
@@ -9209,7 +10428,7 @@
     <n v="19200000"/>
     <n v="17130000"/>
     <x v="15"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0237"/>
@@ -9229,7 +10448,7 @@
     <n v="2295000"/>
     <n v="1425000"/>
     <x v="36"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0238"/>
@@ -9249,7 +10468,7 @@
     <n v="5880000"/>
     <n v="4870000"/>
     <x v="37"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0239"/>
@@ -9269,7 +10488,7 @@
     <n v="20400000"/>
     <n v="12900000"/>
     <x v="53"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0240"/>
@@ -9289,7 +10508,7 @@
     <n v="1680000"/>
     <n v="1265000"/>
     <x v="78"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0241"/>
@@ -9309,7 +10528,7 @@
     <n v="43200000"/>
     <n v="34100000"/>
     <x v="40"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0242"/>
@@ -9329,7 +10548,7 @@
     <n v="2975000"/>
     <n v="2425000"/>
     <x v="1"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0243"/>
@@ -9349,7 +10568,7 @@
     <n v="6300000"/>
     <n v="3750000"/>
     <x v="55"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0244"/>
@@ -9369,7 +10588,7 @@
     <n v="5440000"/>
     <n v="4330000"/>
     <x v="73"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0245"/>
@@ -9389,7 +10608,7 @@
     <n v="7560000"/>
     <n v="4850000"/>
     <x v="4"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0246"/>
@@ -9409,7 +10628,7 @@
     <n v="36000000"/>
     <n v="25605000"/>
     <x v="58"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0247"/>
@@ -9429,7 +10648,7 @@
     <n v="4165000"/>
     <n v="3500000"/>
     <x v="32"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0248"/>
@@ -9449,7 +10668,7 @@
     <n v="13440000"/>
     <n v="9860000"/>
     <x v="7"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0249"/>
@@ -9469,7 +10688,7 @@
     <n v="3060000"/>
     <n v="2125000"/>
     <x v="85"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0250"/>
@@ -9489,7 +10708,7 @@
     <n v="2940000"/>
     <n v="2470000"/>
     <x v="29"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0251"/>
@@ -9509,7 +10728,7 @@
     <n v="36000000"/>
     <n v="25650000"/>
     <x v="30"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0252"/>
@@ -9529,7 +10748,7 @@
     <n v="4080000"/>
     <n v="3090000"/>
     <x v="31"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0253"/>
@@ -9549,7 +10768,7 @@
     <n v="9450000"/>
     <n v="6125000"/>
     <x v="86"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0254"/>
@@ -9569,7 +10788,7 @@
     <n v="9520000"/>
     <n v="8540000"/>
     <x v="13"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0255"/>
@@ -9589,7 +10808,7 @@
     <n v="4200000"/>
     <n v="2450000"/>
     <x v="14"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0256"/>
@@ -9609,7 +10828,7 @@
     <n v="19200000"/>
     <n v="17130000"/>
     <x v="15"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0257"/>
@@ -9629,7 +10848,7 @@
     <n v="3060000"/>
     <n v="1900000"/>
     <x v="51"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0258"/>
@@ -9649,7 +10868,7 @@
     <n v="8820000"/>
     <n v="7305000"/>
     <x v="17"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0259"/>
@@ -9669,7 +10888,7 @@
     <n v="6800000"/>
     <n v="4300000"/>
     <x v="18"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0260"/>
@@ -9689,7 +10908,7 @@
     <n v="5040000"/>
     <n v="3795000"/>
     <x v="66"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0261"/>
@@ -9709,7 +10928,7 @@
     <n v="10800000"/>
     <n v="8525000"/>
     <x v="72"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0262"/>
@@ -9729,7 +10948,7 @@
     <n v="4760000"/>
     <n v="3880000"/>
     <x v="41"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0263"/>
@@ -9749,7 +10968,7 @@
     <n v="4200000"/>
     <n v="2500000"/>
     <x v="22"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0264"/>
@@ -9769,7 +10988,7 @@
     <n v="13600000"/>
     <n v="10825000"/>
     <x v="67"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0265"/>
@@ -9789,7 +11008,7 @@
     <n v="11340000"/>
     <n v="7275000"/>
     <x v="24"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0266"/>
@@ -9809,7 +11028,7 @@
     <n v="12000000"/>
     <n v="8535000"/>
     <x v="5"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0267"/>
@@ -9829,7 +11048,7 @@
     <n v="2975000"/>
     <n v="2500000"/>
     <x v="42"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0268"/>
@@ -9849,7 +11068,7 @@
     <n v="6720000"/>
     <n v="4930000"/>
     <x v="59"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0269"/>
@@ -9869,7 +11088,7 @@
     <n v="12240000"/>
     <n v="8500000"/>
     <x v="80"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0270"/>
@@ -9889,7 +11108,7 @@
     <n v="1470000"/>
     <n v="1235000"/>
     <x v="61"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0271"/>
@@ -9909,7 +11128,7 @@
     <n v="24000000"/>
     <n v="17100000"/>
     <x v="45"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0272"/>
@@ -9929,7 +11148,7 @@
     <n v="4760000"/>
     <n v="3605000"/>
     <x v="46"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0273"/>
@@ -9949,7 +11168,7 @@
     <n v="5670000"/>
     <n v="3675000"/>
     <x v="47"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0274"/>
@@ -9969,7 +11188,7 @@
     <n v="4760000"/>
     <n v="4270000"/>
     <x v="33"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0275"/>
@@ -9989,7 +11208,7 @@
     <n v="16800000"/>
     <n v="9800000"/>
     <x v="34"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0276"/>
@@ -10009,7 +11228,7 @@
     <n v="28800000"/>
     <n v="25695000"/>
     <x v="50"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0277"/>
@@ -10029,7 +11248,7 @@
     <n v="4590000"/>
     <n v="2850000"/>
     <x v="88"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0278"/>
@@ -10049,7 +11268,7 @@
     <n v="2940000"/>
     <n v="2435000"/>
     <x v="52"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0279"/>
@@ -10069,7 +11288,7 @@
     <n v="10200000"/>
     <n v="6450000"/>
     <x v="77"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0280"/>
@@ -10089,7 +11308,7 @@
     <n v="3360000"/>
     <n v="2530000"/>
     <x v="39"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0281"/>
@@ -10109,7 +11328,7 @@
     <n v="21600000"/>
     <n v="17050000"/>
     <x v="0"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0282"/>
@@ -10129,7 +11348,7 @@
     <n v="2975000"/>
     <n v="2425000"/>
     <x v="1"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0283"/>
@@ -10149,7 +11368,7 @@
     <n v="8400000"/>
     <n v="5000000"/>
     <x v="79"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0284"/>
@@ -10169,7 +11388,7 @@
     <n v="2720000"/>
     <n v="2165000"/>
     <x v="23"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0285"/>
@@ -10189,7 +11408,7 @@
     <n v="7560000"/>
     <n v="4850000"/>
     <x v="4"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0286"/>
@@ -10209,7 +11428,7 @@
     <n v="36000000"/>
     <n v="25605000"/>
     <x v="58"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0287"/>
@@ -10229,7 +11448,7 @@
     <n v="4165000"/>
     <n v="3500000"/>
     <x v="32"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0288"/>
@@ -10249,7 +11468,7 @@
     <n v="10080000"/>
     <n v="7395000"/>
     <x v="43"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0289"/>
@@ -10269,7 +11488,7 @@
     <n v="6120000"/>
     <n v="4250000"/>
     <x v="8"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0290"/>
@@ -10289,7 +11508,7 @@
     <n v="5880000"/>
     <n v="4940000"/>
     <x v="44"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0291"/>
@@ -10309,7 +11528,7 @@
     <n v="12000000"/>
     <n v="8550000"/>
     <x v="10"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0292"/>
@@ -10329,7 +11548,7 @@
     <n v="4080000"/>
     <n v="3090000"/>
     <x v="31"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0293"/>
@@ -10349,7 +11568,7 @@
     <n v="3780000"/>
     <n v="2450000"/>
     <x v="12"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0294"/>
@@ -10369,7 +11588,7 @@
     <n v="11900000"/>
     <n v="10675000"/>
     <x v="76"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0295"/>
@@ -10389,7 +11608,7 @@
     <n v="12600000"/>
     <n v="7350000"/>
     <x v="63"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0296"/>
@@ -10409,7 +11628,7 @@
     <n v="9600000"/>
     <n v="8565000"/>
     <x v="35"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0297"/>
@@ -10429,7 +11648,7 @@
     <n v="6120000"/>
     <n v="3800000"/>
     <x v="89"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0298"/>
@@ -10449,7 +11668,7 @@
     <n v="5880000"/>
     <n v="4870000"/>
     <x v="37"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0299"/>
@@ -10469,7 +11688,7 @@
     <n v="13600000"/>
     <n v="8600000"/>
     <x v="71"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0300"/>
@@ -10489,7 +11708,7 @@
     <n v="1680000"/>
     <n v="1265000"/>
     <x v="78"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0301"/>
@@ -10509,7 +11728,7 @@
     <n v="32400000"/>
     <n v="25575000"/>
     <x v="20"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0302"/>
@@ -10529,7 +11748,7 @@
     <n v="2380000"/>
     <n v="1940000"/>
     <x v="90"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0303"/>
@@ -10549,7 +11768,7 @@
     <n v="4200000"/>
     <n v="2500000"/>
     <x v="22"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0304"/>
@@ -10569,7 +11788,7 @@
     <n v="8160000"/>
     <n v="6495000"/>
     <x v="3"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0305"/>
@@ -10589,7 +11808,7 @@
     <n v="15120000"/>
     <n v="9700000"/>
     <x v="74"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0306"/>
@@ -10609,7 +11828,7 @@
     <n v="12000000"/>
     <n v="8535000"/>
     <x v="5"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0307"/>
@@ -10629,7 +11848,7 @@
     <n v="3570000"/>
     <n v="3000000"/>
     <x v="6"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0308"/>
@@ -10649,7 +11868,7 @@
     <n v="6720000"/>
     <n v="4930000"/>
     <x v="59"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0309"/>
@@ -10669,7 +11888,7 @@
     <n v="15300000"/>
     <n v="10625000"/>
     <x v="28"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0310"/>
@@ -10689,7 +11908,7 @@
     <n v="4410000"/>
     <n v="3705000"/>
     <x v="9"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0311"/>
@@ -10709,7 +11928,7 @@
     <n v="24000000"/>
     <n v="17100000"/>
     <x v="45"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0312"/>
@@ -10729,7 +11948,7 @@
     <n v="4760000"/>
     <n v="3605000"/>
     <x v="46"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0313"/>
@@ -10749,7 +11968,7 @@
     <n v="1890000"/>
     <n v="1225000"/>
     <x v="32"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0314"/>
@@ -10769,7 +11988,7 @@
     <n v="4760000"/>
     <n v="4270000"/>
     <x v="33"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0315"/>
@@ -10789,7 +12008,7 @@
     <n v="21000000"/>
     <n v="12250000"/>
     <x v="81"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0316"/>
@@ -10809,7 +12028,7 @@
     <n v="19200000"/>
     <n v="17130000"/>
     <x v="15"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0317"/>
@@ -10829,7 +12048,7 @@
     <n v="3060000"/>
     <n v="1900000"/>
     <x v="51"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0318"/>
@@ -10849,7 +12068,7 @@
     <n v="8820000"/>
     <n v="7305000"/>
     <x v="17"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0319"/>
@@ -10869,7 +12088,7 @@
     <n v="3400000"/>
     <n v="2150000"/>
     <x v="65"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0320"/>
@@ -10889,7 +12108,7 @@
     <n v="6720000"/>
     <n v="5060000"/>
     <x v="19"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0321"/>
@@ -10909,7 +12128,7 @@
     <n v="32400000"/>
     <n v="25575000"/>
     <x v="20"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0322"/>
@@ -10929,7 +12148,7 @@
     <n v="4760000"/>
     <n v="3880000"/>
     <x v="41"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0323"/>
@@ -10949,7 +12168,7 @@
     <n v="4200000"/>
     <n v="2500000"/>
     <x v="22"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0324"/>
@@ -10969,7 +12188,7 @@
     <n v="10880000"/>
     <n v="8660000"/>
     <x v="56"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0325"/>
@@ -10989,7 +12208,7 @@
     <n v="3780000"/>
     <n v="2425000"/>
     <x v="57"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0326"/>
@@ -11009,7 +12228,7 @@
     <n v="24000000"/>
     <n v="17070000"/>
     <x v="25"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0327"/>
@@ -11029,7 +12248,7 @@
     <n v="2975000"/>
     <n v="2500000"/>
     <x v="42"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0328"/>
@@ -11049,7 +12268,7 @@
     <n v="13440000"/>
     <n v="9860000"/>
     <x v="7"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0329"/>
@@ -11069,7 +12288,7 @@
     <n v="6120000"/>
     <n v="4250000"/>
     <x v="8"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0330"/>
@@ -11089,7 +12308,7 @@
     <n v="1470000"/>
     <n v="1235000"/>
     <x v="61"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0331"/>
@@ -11109,7 +12328,7 @@
     <n v="48000000"/>
     <n v="34200000"/>
     <x v="75"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0332"/>
@@ -11129,7 +12348,7 @@
     <n v="4080000"/>
     <n v="3090000"/>
     <x v="31"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0333"/>
@@ -11149,7 +12368,7 @@
     <n v="5670000"/>
     <n v="3675000"/>
     <x v="47"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0334"/>
@@ -11169,7 +12388,7 @@
     <n v="11900000"/>
     <n v="10675000"/>
     <x v="76"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0335"/>
@@ -11189,7 +12408,7 @@
     <n v="8400000"/>
     <n v="4900000"/>
     <x v="49"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0336"/>
@@ -11209,7 +12428,7 @@
     <n v="9600000"/>
     <n v="8565000"/>
     <x v="35"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0337"/>
@@ -11229,7 +12448,7 @@
     <n v="5355000"/>
     <n v="3325000"/>
     <x v="70"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0338"/>
@@ -11249,7 +12468,7 @@
     <n v="8820000"/>
     <n v="7305000"/>
     <x v="17"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0339"/>
@@ -11269,7 +12488,7 @@
     <n v="13600000"/>
     <n v="8600000"/>
     <x v="71"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0340"/>
@@ -11289,7 +12508,7 @@
     <n v="3360000"/>
     <n v="2530000"/>
     <x v="39"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0341"/>
@@ -11309,7 +12528,7 @@
     <n v="43200000"/>
     <n v="34100000"/>
     <x v="40"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0342"/>
@@ -11329,7 +12548,7 @@
     <n v="3570000"/>
     <n v="2910000"/>
     <x v="54"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0343"/>
@@ -11349,7 +12568,7 @@
     <n v="2100000"/>
     <n v="1250000"/>
     <x v="2"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0344"/>
@@ -11369,7 +12588,7 @@
     <n v="8160000"/>
     <n v="6495000"/>
     <x v="3"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0345"/>
@@ -11389,7 +12608,7 @@
     <n v="7560000"/>
     <n v="4850000"/>
     <x v="4"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0346"/>
@@ -11409,7 +12628,7 @@
     <n v="60000000"/>
     <n v="42675000"/>
     <x v="91"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0347"/>
@@ -11429,7 +12648,7 @@
     <n v="4760000"/>
     <n v="4000000"/>
     <x v="92"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0348"/>
@@ -11449,7 +12668,7 @@
     <n v="3360000"/>
     <n v="2465000"/>
     <x v="27"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0349"/>
@@ -11469,7 +12688,7 @@
     <n v="9180000"/>
     <n v="6375000"/>
     <x v="60"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0350"/>
@@ -11489,7 +12708,7 @@
     <n v="5880000"/>
     <n v="4940000"/>
     <x v="44"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0351"/>
@@ -11509,7 +12728,7 @@
     <n v="24000000"/>
     <n v="17100000"/>
     <x v="45"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0352"/>
@@ -11529,7 +12748,7 @@
     <n v="3400000"/>
     <n v="2575000"/>
     <x v="93"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0353"/>
@@ -11549,7 +12768,7 @@
     <n v="3780000"/>
     <n v="2450000"/>
     <x v="12"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0354"/>
@@ -11569,7 +12788,7 @@
     <n v="2380000"/>
     <n v="2135000"/>
     <x v="48"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0355"/>
@@ -11589,7 +12808,7 @@
     <n v="12600000"/>
     <n v="7350000"/>
     <x v="63"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0356"/>
@@ -11609,7 +12828,7 @@
     <n v="19200000"/>
     <n v="17130000"/>
     <x v="15"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0357"/>
@@ -11629,7 +12848,7 @@
     <n v="4590000"/>
     <n v="2850000"/>
     <x v="88"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0358"/>
@@ -11649,7 +12868,7 @@
     <n v="11760000"/>
     <n v="9740000"/>
     <x v="64"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0359"/>
@@ -11669,7 +12888,7 @@
     <n v="6800000"/>
     <n v="4300000"/>
     <x v="18"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0360"/>
@@ -11689,7 +12908,7 @@
     <n v="5040000"/>
     <n v="3795000"/>
     <x v="66"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0361"/>
@@ -11709,7 +12928,7 @@
     <n v="32400000"/>
     <n v="25575000"/>
     <x v="20"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0362"/>
@@ -11729,7 +12948,7 @@
     <n v="4165000"/>
     <n v="3395000"/>
     <x v="21"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0363"/>
@@ -11749,7 +12968,7 @@
     <n v="2100000"/>
     <n v="1250000"/>
     <x v="2"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0364"/>
@@ -11769,7 +12988,7 @@
     <n v="10880000"/>
     <n v="8660000"/>
     <x v="56"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0365"/>
@@ -11789,7 +13008,7 @@
     <n v="18900000"/>
     <n v="12125000"/>
     <x v="94"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0366"/>
@@ -11809,7 +13028,7 @@
     <n v="24000000"/>
     <n v="17070000"/>
     <x v="25"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0367"/>
@@ -11829,7 +13048,7 @@
     <n v="3570000"/>
     <n v="3000000"/>
     <x v="6"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0368"/>
@@ -11849,7 +13068,7 @@
     <n v="8160000"/>
     <n v="6495000"/>
     <x v="3"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0369"/>
@@ -11869,7 +13088,7 @@
     <n v="7560000"/>
     <n v="4900000"/>
     <x v="62"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0370"/>
@@ -11889,7 +13108,7 @@
     <n v="5880000"/>
     <n v="4870000"/>
     <x v="37"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0371"/>
@@ -11909,7 +13128,7 @@
     <n v="12000000"/>
     <n v="8550000"/>
     <x v="10"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0372"/>
@@ -11929,7 +13148,7 @@
     <n v="4760000"/>
     <n v="3605000"/>
     <x v="46"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0373"/>
@@ -11949,7 +13168,7 @@
     <n v="15300000"/>
     <n v="10625000"/>
     <x v="28"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0374"/>
@@ -11969,7 +13188,7 @@
     <n v="2940000"/>
     <n v="2470000"/>
     <x v="29"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0375"/>
@@ -11989,7 +13208,7 @@
     <n v="12600000"/>
     <n v="7350000"/>
     <x v="63"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0376"/>
@@ -12009,7 +13228,7 @@
     <n v="19200000"/>
     <n v="17130000"/>
     <x v="15"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0377"/>
@@ -12029,7 +13248,7 @@
     <n v="6120000"/>
     <n v="3800000"/>
     <x v="89"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0378"/>
@@ -12049,7 +13268,7 @@
     <n v="2380000"/>
     <n v="2135000"/>
     <x v="48"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0379"/>
@@ -12069,7 +13288,7 @@
     <n v="6300000"/>
     <n v="3750000"/>
     <x v="55"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0380"/>
@@ -12089,7 +13308,7 @@
     <n v="13440000"/>
     <n v="9860000"/>
     <x v="7"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0381"/>
@@ -12109,7 +13328,7 @@
     <n v="32400000"/>
     <n v="25575000"/>
     <x v="20"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0382"/>
@@ -12129,7 +13348,7 @@
     <n v="2975000"/>
     <n v="2425000"/>
     <x v="1"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0383"/>
@@ -12149,7 +13368,7 @@
     <n v="6800000"/>
     <n v="4300000"/>
     <x v="18"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0384"/>
@@ -12169,7 +13388,7 @@
     <n v="6720000"/>
     <n v="5060000"/>
     <x v="19"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0385"/>
@@ -12189,7 +13408,7 @@
     <n v="3780000"/>
     <n v="2425000"/>
     <x v="57"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0386"/>
@@ -12209,7 +13428,7 @@
     <n v="24000000"/>
     <n v="17070000"/>
     <x v="25"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0387"/>
@@ -12229,7 +13448,7 @@
     <n v="3570000"/>
     <n v="3000000"/>
     <x v="6"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0388"/>
@@ -12249,7 +13468,7 @@
     <n v="8160000"/>
     <n v="6495000"/>
     <x v="3"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0389"/>
@@ -12269,7 +13488,7 @@
     <n v="9450000"/>
     <n v="6125000"/>
     <x v="86"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0390"/>
@@ -12289,7 +13508,7 @@
     <n v="5880000"/>
     <n v="4870000"/>
     <x v="37"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0391"/>
@@ -12309,7 +13528,7 @@
     <n v="12000000"/>
     <n v="8550000"/>
     <x v="10"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0392"/>
@@ -12329,7 +13548,7 @@
     <n v="4760000"/>
     <n v="3605000"/>
     <x v="46"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0393"/>
@@ -12349,7 +13568,7 @@
     <n v="12240000"/>
     <n v="8500000"/>
     <x v="80"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0394"/>
@@ -12369,7 +13588,7 @@
     <n v="4410000"/>
     <n v="3705000"/>
     <x v="9"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0395"/>
@@ -12389,7 +13608,7 @@
     <n v="8400000"/>
     <n v="4900000"/>
     <x v="49"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0396"/>
@@ -12409,7 +13628,7 @@
     <n v="28800000"/>
     <n v="25695000"/>
     <x v="50"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0397"/>
@@ -12429,7 +13648,7 @@
     <n v="4590000"/>
     <n v="2850000"/>
     <x v="88"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0398"/>
@@ -12449,7 +13668,7 @@
     <n v="4760000"/>
     <n v="4270000"/>
     <x v="33"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0399"/>
@@ -12469,7 +13688,7 @@
     <n v="8400000"/>
     <n v="5000000"/>
     <x v="79"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0400"/>
@@ -12489,7 +13708,7 @@
     <n v="3360000"/>
     <n v="2465000"/>
     <x v="27"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0401"/>
@@ -12509,7 +13728,7 @@
     <n v="21600000"/>
     <n v="17050000"/>
     <x v="0"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0402"/>
@@ -12529,7 +13748,7 @@
     <n v="2975000"/>
     <n v="2425000"/>
     <x v="1"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0403"/>
@@ -12549,7 +13768,7 @@
     <n v="10200000"/>
     <n v="6450000"/>
     <x v="77"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0404"/>
@@ -12569,7 +13788,7 @@
     <n v="3360000"/>
     <n v="2530000"/>
     <x v="39"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0405"/>
@@ -12589,7 +13808,7 @@
     <n v="15120000"/>
     <n v="9700000"/>
     <x v="74"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0406"/>
@@ -12609,7 +13828,7 @@
     <n v="12000000"/>
     <n v="8535000"/>
     <x v="5"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0407"/>
@@ -12629,7 +13848,7 @@
     <n v="4760000"/>
     <n v="4000000"/>
     <x v="92"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0408"/>
@@ -12649,7 +13868,7 @@
     <n v="5440000"/>
     <n v="4330000"/>
     <x v="73"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0409"/>
@@ -12669,7 +13888,7 @@
     <n v="5670000"/>
     <n v="3675000"/>
     <x v="47"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0410"/>
@@ -12689,7 +13908,7 @@
     <n v="14700000"/>
     <n v="12175000"/>
     <x v="87"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0411"/>
@@ -12709,7 +13928,7 @@
     <n v="24000000"/>
     <n v="17100000"/>
     <x v="45"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0412"/>
@@ -12729,7 +13948,7 @@
     <n v="4080000"/>
     <n v="3090000"/>
     <x v="31"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0413"/>
@@ -12749,7 +13968,7 @@
     <n v="3060000"/>
     <n v="2125000"/>
     <x v="85"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0414"/>
@@ -12769,7 +13988,7 @@
     <n v="5880000"/>
     <n v="4940000"/>
     <x v="44"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0415"/>
@@ -12789,7 +14008,7 @@
     <n v="12600000"/>
     <n v="7350000"/>
     <x v="63"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0416"/>
@@ -12809,7 +14028,7 @@
     <n v="19200000"/>
     <n v="17130000"/>
     <x v="15"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0417"/>
@@ -12829,7 +14048,7 @@
     <n v="5355000"/>
     <n v="3325000"/>
     <x v="70"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0418"/>
@@ -12849,7 +14068,7 @@
     <n v="7140000"/>
     <n v="6405000"/>
     <x v="69"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0419"/>
@@ -12869,7 +14088,7 @@
     <n v="4200000"/>
     <n v="2500000"/>
     <x v="22"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0420"/>
@@ -12889,7 +14108,7 @@
     <n v="3360000"/>
     <n v="2465000"/>
     <x v="27"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0421"/>
@@ -12909,7 +14128,7 @@
     <n v="43200000"/>
     <n v="34100000"/>
     <x v="40"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0422"/>
@@ -12929,7 +14148,7 @@
     <n v="3570000"/>
     <n v="2910000"/>
     <x v="54"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0423"/>
@@ -12949,7 +14168,7 @@
     <n v="6800000"/>
     <n v="4300000"/>
     <x v="18"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0424"/>
@@ -12969,7 +14188,7 @@
     <n v="8400000"/>
     <n v="6325000"/>
     <x v="82"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0425"/>
@@ -12989,7 +14208,7 @@
     <n v="7560000"/>
     <n v="4850000"/>
     <x v="4"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0426"/>
@@ -13009,7 +14228,7 @@
     <n v="12000000"/>
     <n v="8535000"/>
     <x v="5"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0427"/>
@@ -13029,7 +14248,7 @@
     <n v="4165000"/>
     <n v="3500000"/>
     <x v="32"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0428"/>
@@ -13049,7 +14268,7 @@
     <n v="10880000"/>
     <n v="8660000"/>
     <x v="56"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0429"/>
@@ -13069,7 +14288,7 @@
     <n v="5670000"/>
     <n v="3675000"/>
     <x v="47"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0430"/>
@@ -13089,7 +14308,7 @@
     <n v="5880000"/>
     <n v="4870000"/>
     <x v="37"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0431"/>
@@ -13109,7 +14328,7 @@
     <n v="36000000"/>
     <n v="25650000"/>
     <x v="30"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0432"/>
@@ -13129,7 +14348,7 @@
     <n v="3400000"/>
     <n v="2575000"/>
     <x v="93"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0433"/>
@@ -13149,7 +14368,7 @@
     <n v="6120000"/>
     <n v="4250000"/>
     <x v="8"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0434"/>
@@ -13169,7 +14388,7 @@
     <n v="5880000"/>
     <n v="4940000"/>
     <x v="44"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0435"/>
@@ -13189,7 +14408,7 @@
     <n v="4200000"/>
     <n v="2450000"/>
     <x v="14"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0436"/>
@@ -13209,7 +14428,7 @@
     <n v="19200000"/>
     <n v="17130000"/>
     <x v="15"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0437"/>
@@ -13229,7 +14448,7 @@
     <n v="6120000"/>
     <n v="3800000"/>
     <x v="89"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0438"/>
@@ -13249,7 +14468,7 @@
     <n v="7140000"/>
     <n v="6405000"/>
     <x v="69"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0439"/>
@@ -13269,7 +14488,7 @@
     <n v="4200000"/>
     <n v="2500000"/>
     <x v="22"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0440"/>
@@ -13289,7 +14508,7 @@
     <n v="16800000"/>
     <n v="12325000"/>
     <x v="95"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0441"/>
@@ -13309,7 +14528,7 @@
     <n v="10800000"/>
     <n v="8525000"/>
     <x v="72"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0442"/>
@@ -13329,7 +14548,7 @@
     <n v="3570000"/>
     <n v="2910000"/>
     <x v="54"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0443"/>
@@ -13349,7 +14568,7 @@
     <n v="13600000"/>
     <n v="8600000"/>
     <x v="71"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0444"/>
@@ -13369,7 +14588,7 @@
     <n v="3360000"/>
     <n v="2530000"/>
     <x v="39"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0445"/>
@@ -13389,7 +14608,7 @@
     <n v="11340000"/>
     <n v="7275000"/>
     <x v="24"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0446"/>
@@ -13409,7 +14628,7 @@
     <n v="24000000"/>
     <n v="17070000"/>
     <x v="25"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0447"/>
@@ -13429,7 +14648,7 @@
     <n v="4165000"/>
     <n v="3500000"/>
     <x v="32"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0448"/>
@@ -13449,7 +14668,7 @@
     <n v="2720000"/>
     <n v="2165000"/>
     <x v="23"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0449"/>
@@ -13469,7 +14688,7 @@
     <n v="7560000"/>
     <n v="4900000"/>
     <x v="62"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0450"/>
@@ -13489,7 +14708,7 @@
     <n v="5880000"/>
     <n v="4870000"/>
     <x v="37"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0451"/>
@@ -13509,7 +14728,7 @@
     <n v="36000000"/>
     <n v="25650000"/>
     <x v="30"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0452"/>
@@ -13529,7 +14748,7 @@
     <n v="3400000"/>
     <n v="2575000"/>
     <x v="93"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0453"/>
@@ -13549,7 +14768,7 @@
     <n v="6120000"/>
     <n v="4250000"/>
     <x v="8"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0454"/>
@@ -13569,7 +14788,7 @@
     <n v="8820000"/>
     <n v="7410000"/>
     <x v="96"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0455"/>
@@ -13589,7 +14808,7 @@
     <n v="4200000"/>
     <n v="2450000"/>
     <x v="14"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0456"/>
@@ -13609,7 +14828,7 @@
     <n v="38400000"/>
     <n v="34260000"/>
     <x v="97"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0457"/>
@@ -13629,7 +14848,7 @@
     <n v="2295000"/>
     <n v="1425000"/>
     <x v="36"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0458"/>
@@ -13649,7 +14868,7 @@
     <n v="11900000"/>
     <n v="10675000"/>
     <x v="76"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0459"/>
@@ -13669,7 +14888,7 @@
     <n v="4200000"/>
     <n v="2500000"/>
     <x v="22"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0460"/>
@@ -13689,7 +14908,7 @@
     <n v="10080000"/>
     <n v="7395000"/>
     <x v="43"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0461"/>
@@ -13709,7 +14928,7 @@
     <n v="21600000"/>
     <n v="17050000"/>
     <x v="0"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0462"/>
@@ -13729,7 +14948,7 @@
     <n v="4165000"/>
     <n v="3395000"/>
     <x v="21"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0463"/>
@@ -13749,7 +14968,7 @@
     <n v="13600000"/>
     <n v="8600000"/>
     <x v="71"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0464"/>
@@ -13769,7 +14988,7 @@
     <n v="1680000"/>
     <n v="1265000"/>
     <x v="78"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0465"/>
@@ -13789,7 +15008,7 @@
     <n v="7560000"/>
     <n v="4850000"/>
     <x v="4"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0466"/>
@@ -13809,7 +15028,7 @@
     <n v="36000000"/>
     <n v="25605000"/>
     <x v="58"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0467"/>
@@ -13829,7 +15048,7 @@
     <n v="4760000"/>
     <n v="4000000"/>
     <x v="92"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0468"/>
@@ -13849,7 +15068,7 @@
     <n v="5440000"/>
     <n v="4330000"/>
     <x v="73"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0469"/>
@@ -13869,7 +15088,7 @@
     <n v="9450000"/>
     <n v="6125000"/>
     <x v="86"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0470"/>
@@ -13889,7 +15108,7 @@
     <n v="2940000"/>
     <n v="2435000"/>
     <x v="52"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0471"/>
@@ -13909,7 +15128,7 @@
     <n v="24000000"/>
     <n v="17100000"/>
     <x v="45"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0472"/>
@@ -13929,7 +15148,7 @@
     <n v="4080000"/>
     <n v="3090000"/>
     <x v="31"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0473"/>
@@ -13949,7 +15168,7 @@
     <n v="9180000"/>
     <n v="6375000"/>
     <x v="60"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0474"/>
@@ -13969,7 +15188,7 @@
     <n v="5880000"/>
     <n v="4940000"/>
     <x v="44"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0475"/>
@@ -13989,7 +15208,7 @@
     <n v="8400000"/>
     <n v="4900000"/>
     <x v="49"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0476"/>
@@ -14009,7 +15228,7 @@
     <n v="28800000"/>
     <n v="25695000"/>
     <x v="50"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0477"/>
@@ -14029,7 +15248,7 @@
     <n v="3825000"/>
     <n v="2375000"/>
     <x v="16"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0478"/>
@@ -14049,7 +15268,7 @@
     <n v="2380000"/>
     <n v="2135000"/>
     <x v="48"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0479"/>
@@ -14069,7 +15288,7 @@
     <n v="6300000"/>
     <n v="3750000"/>
     <x v="55"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0480"/>
@@ -14089,7 +15308,7 @@
     <n v="13440000"/>
     <n v="9860000"/>
     <x v="7"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
   <r>
     <s v="TRX-0481"/>
@@ -14109,7 +15328,7 @@
     <n v="21600000"/>
     <n v="17050000"/>
     <x v="0"/>
-    <n v="0.21064814814814814"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TRX-0482"/>
@@ -14129,7 +15348,7 @@
     <n v="4165000"/>
     <n v="3395000"/>
     <x v="21"/>
-    <n v="0.18487394957983194"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TRX-0483"/>
@@ -14149,7 +15368,7 @@
     <n v="6800000"/>
     <n v="4300000"/>
     <x v="18"/>
-    <n v="0.36764705882352944"/>
+    <x v="18"/>
   </r>
   <r>
     <s v="TRX-0484"/>
@@ -14169,7 +15388,7 @@
     <n v="8400000"/>
     <n v="6325000"/>
     <x v="82"/>
-    <n v="0.24702380952380953"/>
+    <x v="19"/>
   </r>
   <r>
     <s v="TRX-0485"/>
@@ -14189,7 +15408,7 @@
     <n v="3780000"/>
     <n v="2425000"/>
     <x v="57"/>
-    <n v="0.35846560846560849"/>
+    <x v="4"/>
   </r>
   <r>
     <s v="TRX-0486"/>
@@ -14209,7 +15428,7 @@
     <n v="48000000"/>
     <n v="34140000"/>
     <x v="84"/>
-    <n v="0.28875000000000001"/>
+    <x v="5"/>
   </r>
   <r>
     <s v="TRX-0487"/>
@@ -14229,7 +15448,7 @@
     <n v="3570000"/>
     <n v="3000000"/>
     <x v="6"/>
-    <n v="0.15966386554621848"/>
+    <x v="6"/>
   </r>
   <r>
     <s v="TRX-0488"/>
@@ -14249,7 +15468,7 @@
     <n v="8160000"/>
     <n v="6495000"/>
     <x v="3"/>
-    <n v="0.20404411764705882"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="TRX-0489"/>
@@ -14269,7 +15488,7 @@
     <n v="3780000"/>
     <n v="2450000"/>
     <x v="12"/>
-    <n v="0.35185185185185186"/>
+    <x v="12"/>
   </r>
   <r>
     <s v="TRX-0490"/>
@@ -14289,7 +15508,7 @@
     <n v="8820000"/>
     <n v="7305000"/>
     <x v="17"/>
-    <n v="0.17176870748299319"/>
+    <x v="17"/>
   </r>
   <r>
     <s v="TRX-0491"/>
@@ -14309,7 +15528,7 @@
     <n v="12000000"/>
     <n v="8550000"/>
     <x v="10"/>
-    <n v="0.28749999999999998"/>
+    <x v="10"/>
   </r>
   <r>
     <s v="TRX-0492"/>
@@ -14329,7 +15548,7 @@
     <n v="5440000"/>
     <n v="4120000"/>
     <x v="11"/>
-    <n v="0.24264705882352941"/>
+    <x v="11"/>
   </r>
   <r>
     <s v="TRX-0493"/>
@@ -14349,7 +15568,7 @@
     <n v="12240000"/>
     <n v="8500000"/>
     <x v="80"/>
-    <n v="0.30555555555555558"/>
+    <x v="8"/>
   </r>
   <r>
     <s v="TRX-0494"/>
@@ -14369,7 +15588,7 @@
     <n v="2940000"/>
     <n v="2470000"/>
     <x v="29"/>
-    <n v="0.1598639455782313"/>
+    <x v="9"/>
   </r>
   <r>
     <s v="TRX-0495"/>
@@ -14389,7 +15608,7 @@
     <n v="21000000"/>
     <n v="12250000"/>
     <x v="81"/>
-    <n v="0.41666666666666669"/>
+    <x v="14"/>
   </r>
   <r>
     <s v="TRX-0496"/>
@@ -14409,7 +15628,7 @@
     <n v="28800000"/>
     <n v="25695000"/>
     <x v="50"/>
-    <n v="0.10781250000000001"/>
+    <x v="15"/>
   </r>
   <r>
     <s v="TRX-0497"/>
@@ -14429,7 +15648,7 @@
     <n v="3060000"/>
     <n v="1900000"/>
     <x v="51"/>
-    <n v="0.37908496732026142"/>
+    <x v="16"/>
   </r>
   <r>
     <s v="TRX-0498"/>
@@ -14449,7 +15668,7 @@
     <n v="4760000"/>
     <n v="4270000"/>
     <x v="33"/>
-    <n v="0.10294117647058823"/>
+    <x v="13"/>
   </r>
   <r>
     <s v="TRX-0499"/>
@@ -14469,7 +15688,7 @@
     <n v="6300000"/>
     <n v="3750000"/>
     <x v="55"/>
-    <n v="0.40476190476190477"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TRX-0500"/>
@@ -14489,14 +15708,14 @@
     <n v="6720000"/>
     <n v="4930000"/>
     <x v="59"/>
-    <n v="0.26636904761904762"/>
+    <x v="7"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{33554939-956D-4BE9-A88C-42E3B53823EE}" name="analisis" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{33554939-956D-4BE9-A88C-42E3B53823EE}" name="analisis" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" numFmtId="164" outline="0" showAll="0" defaultSubtotal="0">
@@ -14898,11 +16117,11 @@
     <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" numFmtId="166" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0">
+    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0">
       <items count="98">
         <item x="61"/>
         <item x="48"/>
@@ -15004,7 +16223,30 @@
         <item x="91"/>
       </items>
     </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="20">
+        <item x="13"/>
+        <item x="15"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="17"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="19"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="18"/>
+        <item x="16"/>
+        <item x="2"/>
+        <item x="14"/>
+      </items>
+    </pivotField>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
       <items count="368">
         <item x="0"/>
@@ -15419,12 +16661,41 @@
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
   </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Laba_Kotor" fld="16" baseField="0" baseItem="0" numFmtId="165"/>
+  <dataFields count="2">
+    <dataField name="Sum of Total_Pendapatan_Kotor" fld="12" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Sum of Margin_Keuntungan" fld="17" baseField="0" baseItem="0"/>
   </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -50199,77 +51470,96 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB7F205-A472-48BE-8BFF-99A604B10656}">
-  <dimension ref="A3:B9"/>
+  <dimension ref="A3:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="21" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>592</v>
+      </c>
+      <c r="C3" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>539</v>
       </c>
       <c r="B4" s="26">
-        <v>141715000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>567000000</v>
+      </c>
+      <c r="C4" s="49">
+        <v>29.245275888133023</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>534</v>
       </c>
       <c r="B5" s="26">
-        <v>568125000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2676000000</v>
+      </c>
+      <c r="C5" s="49">
+        <v>22.367766203703731</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>536</v>
       </c>
       <c r="B6" s="26">
-        <v>95700000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>510000000</v>
+      </c>
+      <c r="C6" s="49">
+        <v>24.156746031746</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>541</v>
       </c>
       <c r="B7" s="26">
-        <v>289005000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1071000000</v>
+      </c>
+      <c r="C7" s="49">
+        <v>30.3317507558579</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>538</v>
       </c>
       <c r="B8" s="26">
-        <v>219085000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>996200000</v>
+      </c>
+      <c r="C8" s="49">
+        <v>24.34109477124181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>590</v>
       </c>
       <c r="B9" s="26">
-        <v>1313630000</v>
+        <v>5820200000</v>
+      </c>
+      <c r="C9" s="49">
+        <v>130.44263365068247</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -50438,278 +51728,288 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="44" t="s">
         <v>587</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
+      <c r="W1" s="44"/>
+      <c r="X1" s="44"/>
+      <c r="Y1" s="44"/>
       <c r="Z1" s="42"/>
     </row>
     <row r="2" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="43"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="44"/>
       <c r="Z2" s="42"/>
     </row>
     <row r="3" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="43"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="44"/>
+      <c r="U3" s="44"/>
+      <c r="V3" s="44"/>
+      <c r="W3" s="44"/>
+      <c r="X3" s="44"/>
+      <c r="Y3" s="44"/>
       <c r="Z3" s="42"/>
     </row>
     <row r="4" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="43"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="43"/>
-      <c r="X4" s="43"/>
-      <c r="Y4" s="43"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="44"/>
+      <c r="U4" s="44"/>
+      <c r="V4" s="44"/>
+      <c r="W4" s="44"/>
+      <c r="X4" s="44"/>
+      <c r="Y4" s="44"/>
       <c r="Z4" s="42"/>
     </row>
     <row r="5" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="43"/>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
-      <c r="P5" s="43"/>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="43"/>
-      <c r="S5" s="43"/>
-      <c r="T5" s="43"/>
-      <c r="U5" s="43"/>
-      <c r="V5" s="43"/>
-      <c r="W5" s="43"/>
-      <c r="X5" s="43"/>
-      <c r="Y5" s="43"/>
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="44"/>
+      <c r="Q5" s="44"/>
+      <c r="R5" s="44"/>
+      <c r="S5" s="44"/>
+      <c r="T5" s="44"/>
+      <c r="U5" s="44"/>
+      <c r="V5" s="44"/>
+      <c r="W5" s="44"/>
+      <c r="X5" s="44"/>
+      <c r="Y5" s="44"/>
       <c r="Z5" s="42"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="48"/>
-      <c r="B6" s="46" t="s">
+      <c r="A6" s="43"/>
+      <c r="B6" s="45" t="s">
         <v>588</v>
       </c>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="46" t="s">
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="45" t="s">
         <v>589</v>
       </c>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="N6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="N6" s="45" t="s">
+        <v>591</v>
+      </c>
       <c r="O6" s="45"/>
       <c r="P6" s="45"/>
       <c r="Q6" s="45"/>
       <c r="R6" s="45"/>
-      <c r="T6" s="44"/>
-      <c r="U6" s="44"/>
-      <c r="V6" s="44"/>
-      <c r="W6" s="44"/>
-      <c r="X6" s="44"/>
+      <c r="T6" s="45" t="s">
+        <v>593</v>
+      </c>
+      <c r="U6" s="45"/>
+      <c r="V6" s="45"/>
+      <c r="W6" s="45"/>
+      <c r="X6" s="45"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="48"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
+      <c r="A7" s="43"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
       <c r="N7" s="45"/>
       <c r="O7" s="45"/>
       <c r="P7" s="45"/>
       <c r="Q7" s="45"/>
       <c r="R7" s="45"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="44"/>
-      <c r="V7" s="44"/>
-      <c r="W7" s="44"/>
-      <c r="X7" s="44"/>
+      <c r="T7" s="45"/>
+      <c r="U7" s="45"/>
+      <c r="V7" s="45"/>
+      <c r="W7" s="45"/>
+      <c r="X7" s="45"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="47">
+      <c r="B8" s="46">
         <v>5820200000</v>
       </c>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="H8" s="47">
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="H8" s="46">
         <v>1313630000</v>
       </c>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47"/>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="N8" s="45"/>
-      <c r="O8" s="45"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="45"/>
-      <c r="R8" s="45"/>
-      <c r="T8" s="44"/>
-      <c r="U8" s="44"/>
-      <c r="V8" s="44"/>
-      <c r="W8" s="44"/>
-      <c r="X8" s="44"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="46"/>
+      <c r="N8" s="47">
+        <v>0.22570000000000001</v>
+      </c>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="T8" s="48">
+        <v>1641</v>
+      </c>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="48"/>
+      <c r="X8" s="48"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="47"/>
-      <c r="N9" s="45"/>
-      <c r="O9" s="45"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="45"/>
-      <c r="R9" s="45"/>
-      <c r="T9" s="44"/>
-      <c r="U9" s="44"/>
-      <c r="V9" s="44"/>
-      <c r="W9" s="44"/>
-      <c r="X9" s="44"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="48"/>
+      <c r="R9" s="48"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="48"/>
+      <c r="V9" s="48"/>
+      <c r="W9" s="48"/>
+      <c r="X9" s="48"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47"/>
-      <c r="L10" s="47"/>
-      <c r="N10" s="45"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="45"/>
-      <c r="T10" s="44"/>
-      <c r="U10" s="44"/>
-      <c r="V10" s="44"/>
-      <c r="W10" s="44"/>
-      <c r="X10" s="44"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="46"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="48"/>
+      <c r="T10" s="48"/>
+      <c r="U10" s="48"/>
+      <c r="V10" s="48"/>
+      <c r="W10" s="48"/>
+      <c r="X10" s="48"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="N6:R10"/>
-    <mergeCell ref="T6:X10"/>
+  <mergeCells count="9">
     <mergeCell ref="A1:Y5"/>
     <mergeCell ref="B6:F7"/>
     <mergeCell ref="B8:F10"/>
     <mergeCell ref="H6:L7"/>
     <mergeCell ref="H8:L10"/>
+    <mergeCell ref="N6:R7"/>
+    <mergeCell ref="N8:R10"/>
+    <mergeCell ref="T6:X7"/>
+    <mergeCell ref="T8:X10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Analisis Retail Bisnis Omni-Channel.xlsx
+++ b/Analisis Retail Bisnis Omni-Channel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aldy\Documents\DATA ANALYST\MICROSOFT EXCEL\PORTOFOLIO\Analisis Retail Bisnis Omni-Channel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94E4536-B5C3-411B-931B-277CBB987045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC05B65-0728-4592-AB0A-D73B78627A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="1" activeTab="6" xr2:uid="{0FABD09F-C599-4D8F-AE1F-66CDC9C9D3DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="1" activeTab="4" xr2:uid="{0FABD09F-C599-4D8F-AE1F-66CDC9C9D3DB}"/>
   </bookViews>
   <sheets>
     <sheet name="penjualan" sheetId="1" r:id="rId1"/>
@@ -21,11 +21,22 @@
     <sheet name="soal" sheetId="5" r:id="rId6"/>
     <sheet name="Dashboard" sheetId="8" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="NativeTimeline_Tanggal">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}">
+      <x15:timelineCacheRefs>
+        <x15:timelineCacheRef r:id="rId9"/>
+      </x15:timelineCacheRefs>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -3573,6 +3584,55 @@
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-ID" sz="1100" b="1"/>
+              <a:t>OMNI CHANNEL SALES</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:pivotFmts>
       <c:pivotFmt>
@@ -3601,22 +3661,17 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="tx1"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -3638,7 +3693,9 @@
         <c:spPr>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
-              <a:srgbClr val="8C6047"/>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -3657,22 +3714,17 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="tx1"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -3807,7 +3859,9 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="8C6047"/>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3914,10 +3968,7 @@
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3928,6 +3979,7 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1382839439"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -3972,10 +4024,7 @@
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="85000"/>
-                    <a:lumOff val="15000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3986,7 +4035,67 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1382423807"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
+        <c:dispUnits>
+          <c:builtInUnit val="millions"/>
+          <c:dispUnitsLbl>
+            <c:layout>
+              <c:manualLayout>
+                <c:xMode val="edge"/>
+                <c:yMode val="edge"/>
+                <c:x val="2.3024594453165882E-2"/>
+                <c:y val="0.46759259259259262"/>
+              </c:manualLayout>
+            </c:layout>
+            <c:tx>
+              <c:rich>
+                <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:rPr lang="en-US" sz="800"/>
+                    <a:t>Juta</a:t>
+                  </a:r>
+                </a:p>
+              </c:rich>
+            </c:tx>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+          </c:dispUnitsLbl>
+        </c:dispUnits>
       </c:valAx>
       <c:valAx>
         <c:axId val="1382842799"/>
@@ -4011,16 +4120,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -4042,6 +4148,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1382842799"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -4056,7 +4163,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="t"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4072,10 +4179,7 @@
           <a:pPr>
             <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
               <a:ea typeface="+mn-ea"/>
@@ -4117,7 +4221,13 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+          <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -4706,15 +4816,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>9524</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>781050</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>952499</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4737,6 +4847,83 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1333500</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Tanggal">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3366D860-08CA-BAEF-5F57-FA87A974B644}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
+              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Tanggal"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1333500" y="1962150"/>
+              <a:ext cx="5581650" cy="1371600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-ID" sz="1100"/>
+                <a:t>Timeline: Works in Excel 2013 or higher. Do not move or resize.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -5702,7 +5889,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
+      <x14:pivotCacheDefinition pivotCacheId="241815905"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -15714,7 +15901,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{33554939-956D-4BE9-A88C-42E3B53823EE}" name="analisis" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{33554939-956D-4BE9-A88C-42E3B53823EE}" name="analisis" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -16676,7 +16863,7 @@
     <dataField name="Sum of Total_Pendapatan_Kotor" fld="12" baseField="0" baseItem="0" numFmtId="165"/>
     <dataField name="Sum of Margin_Keuntungan" fld="17" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="2">
+  <chartFormats count="4">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -16691,6 +16878,30 @@
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="4"/>
           </reference>
         </references>
       </pivotArea>
@@ -17105,6 +17316,23 @@
 </a:theme>
 </file>
 
+<file path=xl/timelineCaches/timelineCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<timelineCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="xr10" name="NativeTimeline_Tanggal" xr10:uid="{28F9D2A4-44D1-4593-B4E9-45FA56935458}" sourceName="Tanggal">
+  <pivotTables>
+    <pivotTable tabId="6" name="analisis"/>
+  </pivotTables>
+  <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="241815905" filterType="unknown">
+    <bounds startDate="2025-01-01T00:00:00" endDate="2027-01-01T00:00:00"/>
+  </state>
+</timelineCacheDefinition>
+</file>
+
+<file path=xl/timelines/timeline1.xml><?xml version="1.0" encoding="utf-8"?>
+<timelines xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <timeline name="Tanggal" xr10:uid="{2B7B3C0E-C565-4667-BEEF-8C2A92940EF5}" cache="NativeTimeline_Tanggal" caption="Tanggal" level="2" selectionLevel="2" scrollPosition="2025-01-01T00:00:00"/>
+</timelines>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C20CB7E-007D-4606-A73E-4B42C1284222}">
   <dimension ref="A1:R501"/>
@@ -51560,6 +51788,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
+      <x15:timelineRefs>
+        <x15:timelineRef r:id="rId3"/>
+      </x15:timelineRefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 

--- a/Analisis Retail Bisnis Omni-Channel.xlsx
+++ b/Analisis Retail Bisnis Omni-Channel.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aldy\Documents\DATA ANALYST\MICROSOFT EXCEL\PORTOFOLIO\Analisis Retail Bisnis Omni-Channel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC05B65-0728-4592-AB0A-D73B78627A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587B3DA0-A944-43DE-A322-3B7B1E89898A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="1" activeTab="4" xr2:uid="{0FABD09F-C599-4D8F-AE1F-66CDC9C9D3DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="1" activeTab="6" xr2:uid="{0FABD09F-C599-4D8F-AE1F-66CDC9C9D3DB}"/>
   </bookViews>
   <sheets>
     <sheet name="penjualan" sheetId="1" r:id="rId1"/>
@@ -23,18 +23,26 @@
   </sheets>
   <definedNames>
     <definedName name="NativeTimeline_Tanggal">#N/A</definedName>
+    <definedName name="Slicer_Kategori">#N/A</definedName>
+    <definedName name="Slicer_Kota">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId9"/>
+        <x14:slicerCache r:id="rId10"/>
+      </x14:slicerCaches>
+    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}">
       <x15:timelineCacheRefs>
-        <x15:timelineCacheRef r:id="rId9"/>
+        <x15:timelineCacheRef r:id="rId11"/>
       </x15:timelineCacheRefs>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -54,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2109" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="596">
   <si>
     <t>ID_Transaksi</t>
   </si>
@@ -1839,12 +1847,15 @@
   </si>
   <si>
     <t>Sum of Margin_Keuntungan</t>
+  </si>
+  <si>
+    <t>Sum of Laba_Kotor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* &quot;-&quot;??_-;_-@_-"/>
@@ -2187,7 +2198,67 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="54">
+  <dxfs count="58">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.24994659260841701"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Poppins"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="1" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="1" tint="-0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="1" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="1" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3546,21 +3617,700 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="blue slicer style" pivot="0" table="0" count="6" xr9:uid="{95ABF258-362B-43FB-BEAC-4E4F6D81FFFE}">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="blue template" pivot="0" table="0" count="8" xr9:uid="{714AC691-FE5F-4B9C-9A2A-B9C5A38E8463}">
+      <tableStyleElement type="wholeTable" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FFFFFFA7"/>
       <color rgb="FF8C6047"/>
       <color rgb="FFFFFF9F"/>
-      <color rgb="FFFFFFA7"/>
       <color rgb="FFFFFF5D"/>
     </mruColors>
   </colors>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{46F421CA-312F-682f-3DD2-61675219B42D}">
+      <x14:dxfs count="14">
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+          <fill>
+            <patternFill>
+              <bgColor theme="4" tint="0.59996337778862885"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="0"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+          <fill>
+            <patternFill>
+              <bgColor theme="4" tint="-0.24994659260841701"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="0"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+          <fill>
+            <patternFill>
+              <bgColor theme="4" tint="-0.24994659260841701"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="0"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+          <fill>
+            <patternFill>
+              <bgColor theme="4" tint="-0.24994659260841701"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="0"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+          <fill>
+            <patternFill>
+              <bgColor theme="4" tint="-0.24994659260841701"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="0"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+          <fill>
+            <patternFill>
+              <bgColor theme="4" tint="-0.24994659260841701"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+      </x14:dxfs>
+    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1">
+        <x14:slicerStyle name="blue slicer style">
+          <x14:slicerStyleElements>
+            <x14:slicerStyleElement type="unselectedItemWithData" dxfId="3"/>
+            <x14:slicerStyleElement type="selectedItemWithData" dxfId="2"/>
+            <x14:slicerStyleElement type="selectedItemWithNoData" dxfId="1"/>
+            <x14:slicerStyleElement type="hoveredSelectedItemWithData" dxfId="0"/>
+          </x14:slicerStyleElements>
+        </x14:slicerStyle>
+      </x14:slicerStyles>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{A0A4C193-F2C1-4fcb-8827-314CF55A85BB}">
+      <x15:dxfs count="54">
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0" tint="-0.14996795556505021"/>
+              <bgColor theme="4" tint="0.79998168889431442"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0"/>
+              <bgColor theme="4" tint="-0.24994659260841701"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="9"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0" tint="-0.14999847407452621"/>
+              <bgColor theme="0" tint="-0.14999847407452621"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0"/>
+              <bgColor theme="4" tint="-0.24994659260841701"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="9"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0" tint="-0.14999847407452621"/>
+              <bgColor theme="0" tint="-0.14999847407452621"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0"/>
+              <bgColor theme="4" tint="-0.24994659260841701"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="9"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b val="0"/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0" tint="-0.14999847407452621"/>
+              <bgColor theme="0" tint="-0.14999847407452621"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0"/>
+              <bgColor theme="0"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="9"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b val="0"/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0" tint="-0.14999847407452621"/>
+              <bgColor theme="0" tint="-0.14999847407452621"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0"/>
+              <bgColor theme="0"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="9"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="9"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b val="0"/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0" tint="-0.14999847407452621"/>
+              <bgColor theme="0" tint="-0.14999847407452621"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0"/>
+              <bgColor theme="0"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <sz val="9"/>
+            <color theme="1" tint="0.499984740745262"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="9"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b val="0"/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0" tint="-0.14999847407452621"/>
+              <bgColor theme="0" tint="-0.14999847407452621"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0"/>
+              <bgColor theme="0"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <sz val="9"/>
+            <color theme="1" tint="0.499984740745262"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <sz val="9"/>
+            <color theme="1" tint="0.499984740745262"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b val="0"/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0" tint="-0.14999847407452621"/>
+              <bgColor theme="0" tint="-0.14999847407452621"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0"/>
+              <bgColor theme="0"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <sz val="9"/>
+            <color theme="1" tint="0.499984740745262"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <sz val="9"/>
+            <color theme="1" tint="0.499984740745262"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="11"/>
+            <color auto="1"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b val="0"/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0" tint="-0.14999847407452621"/>
+              <bgColor theme="0" tint="-0.14999847407452621"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0"/>
+              <bgColor theme="0"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <sz val="9"/>
+            <color theme="1" tint="0.499984740745262"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <sz val="9"/>
+            <color theme="1" tint="0.499984740745262"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <sz val="9"/>
+            <color theme="1" tint="0.499984740745262"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <b val="0"/>
+            <i val="0"/>
+            <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+        </dxf>
+      </x15:dxfs>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1">
+        <x15:timelineStyle name="blue template">
+          <x15:timelineStyleElements>
+            <x15:timelineStyleElement type="selectionLabel" dxfId="5"/>
+            <x15:timelineStyleElement type="timeLevel" dxfId="4"/>
+            <x15:timelineStyleElement type="periodLabel1" dxfId="3"/>
+            <x15:timelineStyleElement type="periodLabel2" dxfId="2"/>
+            <x15:timelineStyleElement type="selectedTimeBlock" dxfId="1"/>
+            <x15:timelineStyleElement type="unselectedTimeBlock" dxfId="0"/>
+          </x15:timelineStyleElements>
+        </x15:timelineStyle>
+      </x15:timelineStyles>
     </ext>
   </extLst>
 </styleSheet>
@@ -3581,7 +4331,7 @@
   </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[Analisis Retail Bisnis Omni-Channel.xlsx]analisis!analisis</c:name>
-    <c:fmtId val="0"/>
+    <c:fmtId val="11"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -3661,7 +4411,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -3691,10 +4443,13 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent2">
-                <a:lumMod val="50000"/>
+                <a:lumMod val="75000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -3714,7 +4469,232 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -3804,26 +4784,26 @@
                 <c:formatCode>_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>567000000</c:v>
+                  <c:v>289800000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2676000000</c:v>
+                  <c:v>1260000000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>510000000</c:v>
+                  <c:v>261800000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1071000000</c:v>
+                  <c:v>512400000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>996200000</c:v>
+                  <c:v>489600000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-63F6-46B0-9AFF-3C647A8F7E08}"/>
+              <c16:uniqueId val="{00000000-1CD5-4064-BF41-FF9DC864A1DB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3860,7 +4840,7 @@
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2">
-                  <a:lumMod val="50000"/>
+                  <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -3900,19 +4880,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>29.245275888133023</c:v>
+                  <c:v>14.017054043839757</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22.367766203703731</c:v>
+                  <c:v>10.844340277777777</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24.156746031746</c:v>
+                  <c:v>12.644491129785242</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>30.3317507558579</c:v>
+                  <c:v>14.975907029478458</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>24.34109477124181</c:v>
+                  <c:v>12.231413398692801</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3920,7 +4900,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-63F6-46B0-9AFF-3C647A8F7E08}"/>
+              <c16:uniqueId val="{00000001-1CD5-4064-BF41-FF9DC864A1DB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4255,7 +5235,822 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Analisis Retail Bisnis Omni-Channel.xlsx]analisis!PivotTable1</c:name>
+    <c:fmtId val="14"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>Kontribusi</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t> Laba  Per Kota</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="bg1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="bg1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="bg1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>analisis!$G$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-39AD-4074-A2BD-0AD721C29F98}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-39AD-4074-A2BD-0AD721C29F98}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-39AD-4074-A2BD-0AD721C29F98}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-39AD-4074-A2BD-0AD721C29F98}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>analisis!$F$4:$F$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Jakarta</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Makassar</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Medan</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Surabaya</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>analisis!$G$4:$G$8</c:f>
+              <c:numCache>
+                <c:formatCode>_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>167845000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>111475000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>234065000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>120440000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-39AD-4074-A2BD-0AD721C29F98}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Poppins" panose="00000500000000000000" pitchFamily="2" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -4811,31 +6606,552 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>781050</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>127907</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>49306</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>146957</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0580262D-F0D7-6767-4290-2A419F72E9FE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C090A6E6-249C-44AC-9A37-C7F4CD99B2A3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4851,25 +7167,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1333500</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>13607</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>10294</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>140922</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="3" name="Tanggal">
+            <xdr:cNvPr id="5" name="Tanggal">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3366D860-08CA-BAEF-5F57-FA87A974B644}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8ADB4C4-D361-43E5-9AE8-93E003C4D02A}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4896,8 +7212,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1333500" y="1962150"/>
-              <a:ext cx="5581650" cy="1371600"/>
+              <a:off x="92048" y="2722118"/>
+              <a:ext cx="6116011" cy="1363275"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4918,6 +7234,200 @@
               <a:r>
                 <a:rPr lang="en-ID" sz="1100"/>
                 <a:t>Timeline: Works in Excel 2013 or higher. Do not move or resize.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>502425</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>178253</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>454800</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>197303</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED53858A-7BA1-4F93-B9C3-7160E6394346}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>210911</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>89809</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>399089</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>51707</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="7" name="Kota">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64B326E5-1A96-4AEE-A94F-D468B5FD1846}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Kota"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="894470" y="7732221"/>
+              <a:ext cx="2687090" cy="948015"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-ID" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>264378</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>62594</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>50107</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>21772</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="8" name="Kategori">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29F731CD-373D-4D7A-A5C0-58845854EEDE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Kategori"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4051966" y="7705006"/>
+              <a:ext cx="2206200" cy="1191825"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-ID" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -15901,7 +18411,1217 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{33554939-956D-4BE9-A88C-42E3B53823EE}" name="analisis" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{240C8AC7-0F61-4DDD-9013-EAC85AE6134F}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="15">
+  <location ref="F3:G8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" numFmtId="164" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="364">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="3"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="98">
+        <item x="61"/>
+        <item x="48"/>
+        <item x="26"/>
+        <item x="78"/>
+        <item x="90"/>
+        <item x="29"/>
+        <item x="42"/>
+        <item x="33"/>
+        <item x="52"/>
+        <item x="1"/>
+        <item x="23"/>
+        <item x="6"/>
+        <item x="54"/>
+        <item x="32"/>
+        <item x="9"/>
+        <item x="69"/>
+        <item x="92"/>
+        <item x="21"/>
+        <item x="93"/>
+        <item x="39"/>
+        <item x="2"/>
+        <item x="36"/>
+        <item x="41"/>
+        <item x="27"/>
+        <item x="85"/>
+        <item x="44"/>
+        <item x="13"/>
+        <item x="31"/>
+        <item x="37"/>
+        <item x="35"/>
+        <item x="73"/>
+        <item x="46"/>
+        <item x="51"/>
+        <item x="68"/>
+        <item x="76"/>
+        <item x="66"/>
+        <item x="65"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="57"/>
+        <item x="96"/>
+        <item x="16"/>
+        <item x="83"/>
+        <item x="17"/>
+        <item x="19"/>
+        <item x="3"/>
+        <item x="22"/>
+        <item x="88"/>
+        <item x="14"/>
+        <item x="59"/>
+        <item x="8"/>
+        <item x="47"/>
+        <item x="64"/>
+        <item x="70"/>
+        <item x="15"/>
+        <item x="82"/>
+        <item x="56"/>
+        <item x="72"/>
+        <item x="89"/>
+        <item x="18"/>
+        <item x="87"/>
+        <item x="55"/>
+        <item x="62"/>
+        <item x="43"/>
+        <item x="4"/>
+        <item x="67"/>
+        <item x="60"/>
+        <item x="50"/>
+        <item x="86"/>
+        <item x="79"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="49"/>
+        <item x="7"/>
+        <item x="80"/>
+        <item x="77"/>
+        <item x="24"/>
+        <item x="97"/>
+        <item x="95"/>
+        <item x="0"/>
+        <item x="28"/>
+        <item x="71"/>
+        <item x="63"/>
+        <item x="74"/>
+        <item x="38"/>
+        <item x="94"/>
+        <item x="20"/>
+        <item x="45"/>
+        <item x="25"/>
+        <item x="34"/>
+        <item x="53"/>
+        <item x="81"/>
+        <item x="40"/>
+        <item x="30"/>
+        <item x="58"/>
+        <item x="75"/>
+        <item x="84"/>
+        <item x="91"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="20">
+        <item x="13"/>
+        <item x="15"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="17"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="19"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="18"/>
+        <item x="16"/>
+        <item x="2"/>
+        <item x="14"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
+      <items count="368">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Laba_Kotor" fld="16" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <chartFormats count="20">
+    <chartFormat chart="9" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="13">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="14">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="13">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="14">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="21" name="Tanggal">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="45689"/>
+            <customFilter operator="lessThanOrEqual" val="45869"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{33554939-956D-4BE9-A88C-42E3B53823EE}" name="analisis" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="12">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -16863,7 +20583,7 @@
     <dataField name="Sum of Total_Pendapatan_Kotor" fld="12" baseField="0" baseItem="0" numFmtId="165"/>
     <dataField name="Sum of Margin_Keuntungan" fld="17" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="4">
+  <chartFormats count="12">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -16882,32 +20602,115 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="0" format="2">
+    <chartFormat chart="4" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
+        <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="4"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="0" format="3">
+    <chartFormat chart="4" format="3" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
+        <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="1"/>
           </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="4"/>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="11" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="11" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="21" name="Tanggal">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="45689"/>
+            <customFilter operator="lessThanOrEqual" val="45869"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -16919,50 +20722,92 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Kota" xr10:uid="{778F3C14-16CE-40F3-B5D6-56003E13C63D}" sourceName="Kota">
+  <pivotTables>
+    <pivotTable tabId="6" name="analisis"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="241815905">
+      <items count="4">
+        <i x="0" s="1"/>
+        <i x="3" s="1"/>
+        <i x="2" s="1"/>
+        <i x="1" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Kategori" xr10:uid="{3A4EE724-4778-4E2C-98B6-A2758514889C}" sourceName="Kategori">
+  <pivotTables>
+    <pivotTable tabId="6" name="analisis"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="241815905">
+      <items count="3">
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
+        <i x="2" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Kota" xr10:uid="{2F14FB20-EA99-479D-BF43-71C5B0CBE7C0}" cache="Slicer_Kota" caption="Kota" columnCount="2" style="blue slicer style" rowHeight="241300"/>
+  <slicer name="Kategori" xr10:uid="{0AD13CFD-B6F7-43DC-A11D-7BC70C551F06}" cache="Slicer_Kategori" caption="Kategori" style="blue slicer style" rowHeight="241300"/>
+</slicers>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91C63E51-A52D-46AB-91EB-CF63578A5333}" name="Table1" displayName="Table1" ref="A1:R501" totalsRowShown="0" headerRowDxfId="53" dataDxfId="51" headerRowBorderDxfId="52" tableBorderDxfId="50" totalsRowBorderDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91C63E51-A52D-46AB-91EB-CF63578A5333}" name="Table1" displayName="Table1" ref="A1:R501" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56" tableBorderDxfId="54" totalsRowBorderDxfId="53">
   <autoFilter ref="A1:R501" xr:uid="{91C63E51-A52D-46AB-91EB-CF63578A5333}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{535352A0-284A-4EC3-BEA5-FCAC4589AD45}" name="ID_Transaksi" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{60F5C6B6-2EE4-4C37-834D-803292CD8C49}" name="Tanggal" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{E56A6511-4721-46F1-A464-627EE6ED25E5}" name="Kota" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{D6C78C85-4803-494C-B4E3-8459D877E28E}" name="SKU" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{0C6A6903-F5CE-4107-9FDE-CC53F5F04204}" name="Jumlah_Unit" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{048E2C98-E916-4C7C-AA4A-3150159A27E8}" name="Kode_Promo" dataDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{3B8F5B69-10F0-4AEE-8CCF-65814EF6B3D8}" name="Nama_Produk" dataDxfId="42">
+    <tableColumn id="1" xr3:uid="{535352A0-284A-4EC3-BEA5-FCAC4589AD45}" name="ID_Transaksi" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{60F5C6B6-2EE4-4C37-834D-803292CD8C49}" name="Tanggal" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{E56A6511-4721-46F1-A464-627EE6ED25E5}" name="Kota" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{D6C78C85-4803-494C-B4E3-8459D877E28E}" name="SKU" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{0C6A6903-F5CE-4107-9FDE-CC53F5F04204}" name="Jumlah_Unit" dataDxfId="48"/>
+    <tableColumn id="6" xr3:uid="{048E2C98-E916-4C7C-AA4A-3150159A27E8}" name="Kode_Promo" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{3B8F5B69-10F0-4AEE-8CCF-65814EF6B3D8}" name="Nama_Produk" dataDxfId="46">
       <calculatedColumnFormula>INDEX(Table2[Nama Produk],MATCH(Table1[[#This Row],[SKU]],Table2[SKU],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{735DE14D-F3A8-4241-B953-035F6E26A6A0}" name="Kategori" dataDxfId="41">
+    <tableColumn id="8" xr3:uid="{735DE14D-F3A8-4241-B953-035F6E26A6A0}" name="Kategori" dataDxfId="45">
       <calculatedColumnFormula>VLOOKUP(Table1[[#This Row],[SKU]],Table2[],3,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{ECD5AF4E-B3F4-41BB-B37B-443DEE5B7141}" name="Harga_Satuan" dataDxfId="40">
+    <tableColumn id="9" xr3:uid="{ECD5AF4E-B3F4-41BB-B37B-443DEE5B7141}" name="Harga_Satuan" dataDxfId="44">
       <calculatedColumnFormula>INDEX(Table2[Harga Jual],MATCH(Table1[[#This Row],[SKU]],Table2[SKU],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C465DBB9-4C64-4E93-9532-CB6D42B2E695}" name="HPP_Satuan" dataDxfId="39">
+    <tableColumn id="10" xr3:uid="{C465DBB9-4C64-4E93-9532-CB6D42B2E695}" name="HPP_Satuan" dataDxfId="43">
       <calculatedColumnFormula>VLOOKUP(Table1[[#This Row],[SKU]],Table2[],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FBA65091-B8F3-4737-AD43-21E2351C753A}" name="Biaya_Kirim_Satuan" dataDxfId="38">
+    <tableColumn id="11" xr3:uid="{FBA65091-B8F3-4737-AD43-21E2351C753A}" name="Biaya_Kirim_Satuan" dataDxfId="42">
       <calculatedColumnFormula>INDEX(Table3[Biaya Kirim per Unit],MATCH(Table1[[#This Row],[Kota]],Table3[Kota],))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{236D1E61-E310-4595-8E7E-18D3E9DD1768}" name="Persentase_Diskon" dataDxfId="37" dataCellStyle="Percent">
+    <tableColumn id="12" xr3:uid="{236D1E61-E310-4595-8E7E-18D3E9DD1768}" name="Persentase_Diskon" dataDxfId="41" dataCellStyle="Percent">
       <calculatedColumnFormula>VLOOKUP(Table1[[#This Row],[Kode_Promo]],Table4[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{CA31B10C-74E5-409B-A9BB-69CF31F44850}" name="Total_Pendapatan_Kotor" dataDxfId="36">
+    <tableColumn id="13" xr3:uid="{CA31B10C-74E5-409B-A9BB-69CF31F44850}" name="Total_Pendapatan_Kotor" dataDxfId="40">
       <calculatedColumnFormula>Table1[[#This Row],[Jumlah_Unit]]*Table1[[#This Row],[Harga_Satuan]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3AE5F5BA-9CCD-4247-B4FB-CBB68DB0342F}" name="Potongan_Diskon" dataDxfId="35">
+    <tableColumn id="14" xr3:uid="{3AE5F5BA-9CCD-4247-B4FB-CBB68DB0342F}" name="Potongan_Diskon" dataDxfId="39">
       <calculatedColumnFormula>Table1[[#This Row],[Total_Pendapatan_Kotor]]*Table1[[#This Row],[Persentase_Diskon]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{83ED65EB-9A6F-4F9C-A403-5E4DEC52A650}" name="Total_Pendapatan_Bersih" dataDxfId="34">
+    <tableColumn id="15" xr3:uid="{83ED65EB-9A6F-4F9C-A403-5E4DEC52A650}" name="Total_Pendapatan_Bersih" dataDxfId="38">
       <calculatedColumnFormula>Table1[[#This Row],[Total_Pendapatan_Kotor]]-Table1[[#This Row],[Potongan_Diskon]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C66B6AE0-9825-4E7F-9199-125CC56ED9A7}" name="Total_Biaya" dataDxfId="33">
+    <tableColumn id="16" xr3:uid="{C66B6AE0-9825-4E7F-9199-125CC56ED9A7}" name="Total_Biaya" dataDxfId="37">
       <calculatedColumnFormula>(Table1[[#This Row],[Jumlah_Unit]]*Table1[[#This Row],[HPP_Satuan]])+(Table1[[#This Row],[Jumlah_Unit]]*Table1[[#This Row],[Biaya_Kirim_Satuan]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{8448139B-E35F-403D-88B7-2B81687ED76E}" name="Laba_Kotor" dataDxfId="32">
+    <tableColumn id="17" xr3:uid="{8448139B-E35F-403D-88B7-2B81687ED76E}" name="Laba_Kotor" dataDxfId="36">
       <calculatedColumnFormula>Table1[[#This Row],[Total_Pendapatan_Bersih]]-Table1[[#This Row],[Total_Biaya]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{19F6E599-1DA2-4A17-B20A-85FAA9CAA88F}" name="Margin_Keuntungan" dataDxfId="31">
+    <tableColumn id="18" xr3:uid="{19F6E599-1DA2-4A17-B20A-85FAA9CAA88F}" name="Margin_Keuntungan" dataDxfId="35">
       <calculatedColumnFormula>Table1[[#This Row],[Laba_Kotor]]/Table1[[#This Row],[Total_Pendapatan_Bersih]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16971,51 +20816,51 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FDD45560-B6D3-41C6-AE2A-F8AD6BBACE68}" name="Table2" displayName="Table2" ref="A1:E6" totalsRowShown="0" headerRowDxfId="30" headerRowBorderDxfId="29" tableBorderDxfId="28" totalsRowBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FDD45560-B6D3-41C6-AE2A-F8AD6BBACE68}" name="Table2" displayName="Table2" ref="A1:E6" totalsRowShown="0" headerRowDxfId="34" headerRowBorderDxfId="33" tableBorderDxfId="32" totalsRowBorderDxfId="31">
   <autoFilter ref="A1:E6" xr:uid="{FDD45560-B6D3-41C6-AE2A-F8AD6BBACE68}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8EB14854-7AF6-49A4-88AA-B3FDDCC42382}" name="SKU" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{5D2A612D-0698-4443-8219-30640E779857}" name="Nama Produk" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{A6103524-5795-4C97-B3D5-365566612506}" name="Kategori" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{E99EBFAC-0288-49E8-A2CE-BA8095F96A66}" name="HPP" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{3D2D3651-2CAB-4DFC-ABF1-674CCD068115}" name="Harga Jual" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{8EB14854-7AF6-49A4-88AA-B3FDDCC42382}" name="SKU" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{5D2A612D-0698-4443-8219-30640E779857}" name="Nama Produk" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{A6103524-5795-4C97-B3D5-365566612506}" name="Kategori" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{E99EBFAC-0288-49E8-A2CE-BA8095F96A66}" name="HPP" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{3D2D3651-2CAB-4DFC-ABF1-674CCD068115}" name="Harga Jual" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{10F71EA0-F0EC-4DFE-A2AB-43A6531E908A}" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{10F71EA0-F0EC-4DFE-A2AB-43A6531E908A}" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0" headerRowBorderDxfId="25" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="A1:C5" xr:uid="{10F71EA0-F0EC-4DFE-A2AB-43A6531E908A}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0A45B6A5-0536-4D20-A5E2-7E4BD4BDCE05}" name="Kota" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{636D6F2C-8691-45F9-87EF-3C4669C8D4FE}" name="Wilayah" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{873955BF-A08E-404A-897B-9A4966E646E3}" name="Biaya Kirim per Unit" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{0A45B6A5-0536-4D20-A5E2-7E4BD4BDCE05}" name="Kota" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{636D6F2C-8691-45F9-87EF-3C4669C8D4FE}" name="Wilayah" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{873955BF-A08E-404A-897B-9A4966E646E3}" name="Biaya Kirim per Unit" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DA8C010A-5D31-4A19-AF5C-380C4883E588}" name="Table4" displayName="Table4" ref="A1:C5" totalsRowShown="0" headerRowBorderDxfId="15" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DA8C010A-5D31-4A19-AF5C-380C4883E588}" name="Table4" displayName="Table4" ref="A1:C5" totalsRowShown="0" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
   <autoFilter ref="A1:C5" xr:uid="{DA8C010A-5D31-4A19-AF5C-380C4883E588}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0FEAB7C0-9975-4BB3-97C0-65272C933D59}" name="Kode Promo" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{7268390E-5820-4F31-AA85-AF2D35552741}" name="Besaran Diskon" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{95D74BC3-E24F-46CD-A305-3DE4BBBB44D9}" name="Keterangan Syarat" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{0FEAB7C0-9975-4BB3-97C0-65272C933D59}" name="Kode Promo" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{7268390E-5820-4F31-AA85-AF2D35552741}" name="Besaran Diskon" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{95D74BC3-E24F-46CD-A305-3DE4BBBB44D9}" name="Keterangan Syarat" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2D8BD81D-9F01-414B-A4EE-0F3E3758FAD8}" name="Table5" displayName="Table5" ref="A5:D12" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5" dataCellStyle="Percent">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2D8BD81D-9F01-414B-A4EE-0F3E3758FAD8}" name="Table5" displayName="Table5" ref="A5:D12" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9" dataCellStyle="Percent">
   <autoFilter ref="A5:D12" xr:uid="{2D8BD81D-9F01-414B-A4EE-0F3E3758FAD8}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C0DB13C7-69BD-4B04-AD37-A903E9718342}" name="Nomor Soal" dataDxfId="4" dataCellStyle="Percent"/>
-    <tableColumn id="2" xr3:uid="{0024CB6F-4755-4E2C-8351-AEB7946C3495}" name="Kategori Keterampilan" dataDxfId="3" dataCellStyle="Percent"/>
-    <tableColumn id="3" xr3:uid="{E54C8867-FE29-4C25-A0EC-89B409159D7E}" name="Instruksi Pengerjaan" dataDxfId="2" dataCellStyle="Percent"/>
-    <tableColumn id="4" xr3:uid="{2E3FF913-4ABB-4AED-AD44-A625313457B5}" name="Output yang Diharapkan" dataDxfId="1" dataCellStyle="Percent"/>
+    <tableColumn id="1" xr3:uid="{C0DB13C7-69BD-4B04-AD37-A903E9718342}" name="Nomor Soal" dataDxfId="8" dataCellStyle="Percent"/>
+    <tableColumn id="2" xr3:uid="{0024CB6F-4755-4E2C-8351-AEB7946C3495}" name="Kategori Keterampilan" dataDxfId="7" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{E54C8867-FE29-4C25-A0EC-89B409159D7E}" name="Instruksi Pengerjaan" dataDxfId="6" dataCellStyle="Percent"/>
+    <tableColumn id="4" xr3:uid="{2E3FF913-4ABB-4AED-AD44-A625313457B5}" name="Output yang Diharapkan" dataDxfId="5" dataCellStyle="Percent"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17317,11 +21162,13 @@
 </file>
 
 <file path=xl/timelineCaches/timelineCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<timelineCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="xr10" name="NativeTimeline_Tanggal" xr10:uid="{28F9D2A4-44D1-4593-B4E9-45FA56935458}" sourceName="Tanggal">
+<timelineCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="xr10" name="NativeTimeline_Tanggal" xr10:uid="{AD52D45B-92ED-4481-B367-3B377E209546}" sourceName="Tanggal">
   <pivotTables>
     <pivotTable tabId="6" name="analisis"/>
+    <pivotTable tabId="6" name="PivotTable1"/>
   </pivotTables>
-  <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="241815905" filterType="unknown">
+  <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="241815905" filterType="dateBetween">
+    <selection startDate="2025-02-01T00:00:00" endDate="2025-07-31T00:00:00"/>
     <bounds startDate="2025-01-01T00:00:00" endDate="2027-01-01T00:00:00"/>
   </state>
 </timelineCacheDefinition>
@@ -17329,7 +21176,7 @@
 
 <file path=xl/timelines/timeline1.xml><?xml version="1.0" encoding="utf-8"?>
 <timelines xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <timeline name="Tanggal" xr10:uid="{2B7B3C0E-C565-4667-BEEF-8C2A92940EF5}" cache="NativeTimeline_Tanggal" caption="Tanggal" level="2" selectionLevel="2" scrollPosition="2025-01-01T00:00:00"/>
+  <timeline name="Tanggal" xr10:uid="{9DA8BBED-2023-4092-AEF7-60DAB179E2FA}" cache="NativeTimeline_Tanggal" caption="Tanggal" level="2" selectionLevel="2" scrollPosition="2025-01-01T00:00:00" style="blue template"/>
 </timelines>
 </file>
 
@@ -51416,7 +55263,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:R501">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>$E2 &gt; 5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -51698,17 +55545,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB7F205-A472-48BE-8BFF-99A604B10656}">
-  <dimension ref="A3:C9"/>
+  <dimension ref="A3:G9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="21" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="21" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
         <v>6</v>
       </c>
@@ -51718,83 +55569,111 @@
       <c r="C3" t="s">
         <v>594</v>
       </c>
+      <c r="F3" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>595</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>539</v>
       </c>
       <c r="B4" s="26">
-        <v>567000000</v>
+        <v>289800000</v>
       </c>
       <c r="C4" s="49">
-        <v>29.245275888133023</v>
+        <v>14.017054043839757</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="26">
+        <v>167845000</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>534</v>
       </c>
       <c r="B5" s="26">
-        <v>2676000000</v>
+        <v>1260000000</v>
       </c>
       <c r="C5" s="49">
-        <v>22.367766203703731</v>
+        <v>10.844340277777777</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="26">
+        <v>111475000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>536</v>
       </c>
       <c r="B6" s="26">
-        <v>510000000</v>
+        <v>261800000</v>
       </c>
       <c r="C6" s="49">
-        <v>24.156746031746</v>
+        <v>12.644491129785242</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="26">
+        <v>234065000</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>541</v>
       </c>
       <c r="B7" s="26">
-        <v>1071000000</v>
+        <v>512400000</v>
       </c>
       <c r="C7" s="49">
-        <v>30.3317507558579</v>
+        <v>14.975907029478458</v>
+      </c>
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="26">
+        <v>120440000</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>538</v>
       </c>
       <c r="B8" s="26">
-        <v>996200000</v>
+        <v>489600000</v>
       </c>
       <c r="C8" s="49">
-        <v>24.34109477124181</v>
+        <v>12.231413398692801</v>
+      </c>
+      <c r="F8" t="s">
+        <v>590</v>
+      </c>
+      <c r="G8" s="26">
+        <v>633825000</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>590</v>
       </c>
       <c r="B9" s="26">
-        <v>5820200000</v>
+        <v>2813600000</v>
       </c>
       <c r="C9" s="49">
-        <v>130.44263365068247</v>
+        <v>64.713205879574033</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
-      <x15:timelineRefs>
-        <x15:timelineRef r:id="rId3"/>
-      </x15:timelineRefs>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -52247,5 +56126,18 @@
     <mergeCell ref="T8:X10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId2"/>
+      </x14:slicerList>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
+      <x15:timelineRefs>
+        <x15:timelineRef r:id="rId3"/>
+      </x15:timelineRefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/Analisis Retail Bisnis Omni-Channel.xlsx
+++ b/Analisis Retail Bisnis Omni-Channel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aldy\Documents\DATA ANALYST\MICROSOFT EXCEL\PORTOFOLIO\Analisis Retail Bisnis Omni-Channel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587B3DA0-A944-43DE-A322-3B7B1E89898A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142355CE-9E95-47A4-91AC-8BEFC8D05393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="1" activeTab="6" xr2:uid="{0FABD09F-C599-4D8F-AE1F-66CDC9C9D3DB}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2110" uniqueCount="596">
   <si>
     <t>ID_Transaksi</t>
   </si>
@@ -2218,6 +2218,20 @@
         <name val="Poppins"/>
         <scheme val="none"/>
       </font>
+      <border>
+        <left style="thin">
+          <color theme="4" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="-0.24994659260841701"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="-0.24994659260841701"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2246,16 +2260,16 @@
       </fill>
       <border>
         <left style="thin">
-          <color theme="1" tint="-0.499984740745262"/>
+          <color theme="4" tint="-0.24994659260841701"/>
         </left>
         <right style="thin">
-          <color theme="1" tint="-0.499984740745262"/>
+          <color theme="4" tint="-0.24994659260841701"/>
         </right>
         <top style="thin">
-          <color theme="1" tint="-0.499984740745262"/>
+          <color theme="4" tint="-0.24994659260841701"/>
         </top>
         <bottom style="thin">
-          <color theme="1" tint="-0.499984740745262"/>
+          <color theme="4" tint="-0.24994659260841701"/>
         </bottom>
       </border>
     </dxf>
@@ -3637,7 +3651,7 @@
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{46F421CA-312F-682f-3DD2-61675219B42D}">
-      <x14:dxfs count="14">
+      <x14:dxfs count="8">
         <dxf>
           <font>
             <b/>
@@ -3698,6 +3712,21 @@
             <b/>
             <i val="0"/>
             <sz val="8"/>
+            <color theme="4" tint="-0.24994659260841701"/>
+            <name val="Poppins"/>
+            <scheme val="none"/>
+          </font>
+          <fill>
+            <patternFill>
+              <bgColor theme="4" tint="0.59996337778862885"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="8"/>
             <color auto="1"/>
             <name val="Poppins"/>
             <scheme val="none"/>
@@ -3733,81 +3762,6 @@
             </patternFill>
           </fill>
         </dxf>
-        <dxf>
-          <font>
-            <b/>
-            <i val="0"/>
-            <sz val="8"/>
-            <color theme="0"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-          <fill>
-            <patternFill>
-              <bgColor theme="4" tint="-0.24994659260841701"/>
-            </patternFill>
-          </fill>
-        </dxf>
-        <dxf>
-          <font>
-            <b/>
-            <i val="0"/>
-            <sz val="8"/>
-            <color auto="1"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b/>
-            <i val="0"/>
-            <sz val="8"/>
-            <color theme="4" tint="-0.24994659260841701"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b/>
-            <i val="0"/>
-            <sz val="8"/>
-            <color auto="1"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b/>
-            <i val="0"/>
-            <sz val="8"/>
-            <color theme="4" tint="-0.24994659260841701"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b/>
-            <i val="0"/>
-            <sz val="8"/>
-            <color auto="1"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b/>
-            <i val="0"/>
-            <sz val="8"/>
-            <color theme="4" tint="-0.24994659260841701"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
       </x14:dxfs>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3823,7 +3777,7 @@
       </x14:slicerStyles>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{A0A4C193-F2C1-4fcb-8827-314CF55A85BB}">
-      <x15:dxfs count="54">
+      <x15:dxfs count="24">
         <dxf>
           <fill>
             <patternFill patternType="solid">
@@ -3883,8 +3837,8 @@
         <dxf>
           <fill>
             <patternFill patternType="solid">
-              <fgColor theme="0" tint="-0.14999847407452621"/>
-              <bgColor theme="0" tint="-0.14999847407452621"/>
+              <fgColor theme="0" tint="-0.14996795556505021"/>
+              <bgColor theme="4" tint="0.79998168889431442"/>
             </patternFill>
           </fill>
         </dxf>
@@ -3939,8 +3893,8 @@
         <dxf>
           <fill>
             <patternFill patternType="solid">
-              <fgColor theme="0" tint="-0.14999847407452621"/>
-              <bgColor theme="0" tint="-0.14999847407452621"/>
+              <fgColor theme="0" tint="-0.14996795556505021"/>
+              <bgColor theme="4" tint="0.79998168889431442"/>
             </patternFill>
           </fill>
         </dxf>
@@ -3984,7 +3938,7 @@
         </dxf>
         <dxf>
           <font>
-            <b val="0"/>
+            <b/>
             <i val="0"/>
             <sz val="8"/>
             <color theme="4" tint="-0.24994659260841701"/>
@@ -3995,8 +3949,8 @@
         <dxf>
           <fill>
             <patternFill patternType="solid">
-              <fgColor theme="0" tint="-0.14999847407452621"/>
-              <bgColor theme="0" tint="-0.14999847407452621"/>
+              <fgColor theme="0" tint="-0.14996795556505021"/>
+              <bgColor theme="4" tint="0.79998168889431442"/>
             </patternFill>
           </fill>
         </dxf>
@@ -4004,7 +3958,7 @@
           <fill>
             <patternFill patternType="solid">
               <fgColor theme="0"/>
-              <bgColor theme="0"/>
+              <bgColor theme="4" tint="-0.24994659260841701"/>
             </patternFill>
           </fill>
         </dxf>
@@ -4040,255 +3994,7 @@
         </dxf>
         <dxf>
           <font>
-            <b val="0"/>
-            <i val="0"/>
-            <sz val="8"/>
-            <color theme="4" tint="-0.24994659260841701"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <fill>
-            <patternFill patternType="solid">
-              <fgColor theme="0" tint="-0.14999847407452621"/>
-              <bgColor theme="0" tint="-0.14999847407452621"/>
-            </patternFill>
-          </fill>
-        </dxf>
-        <dxf>
-          <fill>
-            <patternFill patternType="solid">
-              <fgColor theme="0"/>
-              <bgColor theme="0"/>
-            </patternFill>
-          </fill>
-        </dxf>
-        <dxf>
-          <font>
             <b/>
-            <i val="0"/>
-            <sz val="9"/>
-            <color auto="1"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b/>
-            <i val="0"/>
-            <sz val="9"/>
-            <color auto="1"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b/>
-            <i val="0"/>
-            <sz val="8"/>
-            <color auto="1"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b val="0"/>
-            <i val="0"/>
-            <sz val="8"/>
-            <color theme="4" tint="-0.24994659260841701"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <fill>
-            <patternFill patternType="solid">
-              <fgColor theme="0" tint="-0.14999847407452621"/>
-              <bgColor theme="0" tint="-0.14999847407452621"/>
-            </patternFill>
-          </fill>
-        </dxf>
-        <dxf>
-          <fill>
-            <patternFill patternType="solid">
-              <fgColor theme="0"/>
-              <bgColor theme="0"/>
-            </patternFill>
-          </fill>
-        </dxf>
-        <dxf>
-          <font>
-            <sz val="9"/>
-            <color theme="1" tint="0.499984740745262"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b/>
-            <i val="0"/>
-            <sz val="9"/>
-            <color auto="1"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b/>
-            <i val="0"/>
-            <sz val="8"/>
-            <color auto="1"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b val="0"/>
-            <i val="0"/>
-            <sz val="8"/>
-            <color theme="4" tint="-0.24994659260841701"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <fill>
-            <patternFill patternType="solid">
-              <fgColor theme="0" tint="-0.14999847407452621"/>
-              <bgColor theme="0" tint="-0.14999847407452621"/>
-            </patternFill>
-          </fill>
-        </dxf>
-        <dxf>
-          <fill>
-            <patternFill patternType="solid">
-              <fgColor theme="0"/>
-              <bgColor theme="0"/>
-            </patternFill>
-          </fill>
-        </dxf>
-        <dxf>
-          <font>
-            <sz val="9"/>
-            <color theme="1" tint="0.499984740745262"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <sz val="9"/>
-            <color theme="1" tint="0.499984740745262"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b/>
-            <i val="0"/>
-            <sz val="8"/>
-            <color auto="1"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b val="0"/>
-            <i val="0"/>
-            <sz val="8"/>
-            <color theme="4" tint="-0.24994659260841701"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <fill>
-            <patternFill patternType="solid">
-              <fgColor theme="0" tint="-0.14999847407452621"/>
-              <bgColor theme="0" tint="-0.14999847407452621"/>
-            </patternFill>
-          </fill>
-        </dxf>
-        <dxf>
-          <fill>
-            <patternFill patternType="solid">
-              <fgColor theme="0"/>
-              <bgColor theme="0"/>
-            </patternFill>
-          </fill>
-        </dxf>
-        <dxf>
-          <font>
-            <sz val="9"/>
-            <color theme="1" tint="0.499984740745262"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <sz val="9"/>
-            <color theme="1" tint="0.499984740745262"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b/>
-            <i val="0"/>
-            <sz val="11"/>
-            <color auto="1"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b val="0"/>
-            <i val="0"/>
-            <sz val="8"/>
-            <color theme="4" tint="-0.24994659260841701"/>
-            <name val="Poppins"/>
-            <scheme val="none"/>
-          </font>
-        </dxf>
-        <dxf>
-          <fill>
-            <patternFill patternType="solid">
-              <fgColor theme="0" tint="-0.14999847407452621"/>
-              <bgColor theme="0" tint="-0.14999847407452621"/>
-            </patternFill>
-          </fill>
-        </dxf>
-        <dxf>
-          <fill>
-            <patternFill patternType="solid">
-              <fgColor theme="0"/>
-              <bgColor theme="0"/>
-            </patternFill>
-          </fill>
-        </dxf>
-        <dxf>
-          <font>
-            <sz val="9"/>
-            <color theme="1" tint="0.499984740745262"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <sz val="9"/>
-            <color theme="1" tint="0.499984740745262"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <sz val="9"/>
-            <color theme="1" tint="0.499984740745262"/>
-          </font>
-        </dxf>
-        <dxf>
-          <font>
-            <b val="0"/>
             <i val="0"/>
             <sz val="8"/>
             <color theme="4" tint="-0.24994659260841701"/>
@@ -4756,22 +4462,13 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>analisis!$A$4:$A$9</c:f>
+              <c:f>analisis!$A$4:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Kursi Kerja Ergonomis</c:v>
+                  <c:v>Laptop Pro 14</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Laptop Pro 14</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Mechanical Keyboard</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Meja Adjustable</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>Monitor Ergonomis 27</c:v>
                 </c:pt>
               </c:strCache>
@@ -4779,24 +4476,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>analisis!$B$4:$B$9</c:f>
+              <c:f>analisis!$B$4:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* "-"??_-;_-@_-</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>289800000</c:v>
+                  <c:v>180000000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1260000000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>261800000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>512400000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>489600000</c:v>
+                  <c:v>54400000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4852,22 +4540,13 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>analisis!$A$4:$A$9</c:f>
+              <c:f>analisis!$A$4:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Kursi Kerja Ergonomis</c:v>
+                  <c:v>Laptop Pro 14</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Laptop Pro 14</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Mechanical Keyboard</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Meja Adjustable</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>Monitor Ergonomis 27</c:v>
                 </c:pt>
               </c:strCache>
@@ -4875,24 +4554,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>analisis!$C$4:$C$9</c:f>
+              <c:f>analisis!$C$4:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>14.017054043839757</c:v>
+                  <c:v>1.474537037037037</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.844340277777777</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>12.644491129785242</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>14.975907029478458</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>12.231413398692801</c:v>
+                  <c:v>1.8333333333333335</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5742,10 +5412,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -5765,10 +5432,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent3"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -5788,9 +5452,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent4"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -5859,41 +5521,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>analisis!$F$4:$F$8</c:f>
+              <c:f>analisis!$F$4:$F$5</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Jakarta</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Makassar</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Medan</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Surabaya</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>analisis!$G$4:$G$8</c:f>
+              <c:f>analisis!$G$4:$G$5</c:f>
               <c:numCache>
                 <c:formatCode>_-[$Rp-3809]* #,##0_-;\-[$Rp-3809]* #,##0_-;_-[$Rp-3809]* "-"??_-;_-@_-</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>167845000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>111475000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>234065000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>120440000</c:v>
+                  <c:v>49085000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7129,16 +6773,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>127907</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>239966</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>49306</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>146957</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>12486</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7175,11 +6819,11 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>140922</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
+      <mc:Choice Requires="tsle">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="5" name="Tanggal">
@@ -7197,12 +6841,12 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
-              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Tanggal"/>
+              <tsle:timeslicer name="Tanggal"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -7245,15 +6889,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>502425</xdr:colOff>
+      <xdr:colOff>4980</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>178253</xdr:rowOff>
+      <xdr:rowOff>244514</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>454800</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>197303</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>15085</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7282,16 +6926,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>210911</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>89809</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>6621</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>4040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>399089</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>51707</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>227135</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -7327,8 +6971,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="894470" y="7732221"/>
-              <a:ext cx="2687090" cy="948015"/>
+              <a:off x="6293121" y="2525364"/>
+              <a:ext cx="2492292" cy="1455742"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7360,16 +7004,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>264378</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>62594</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>14657</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>6687</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>50107</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>21772</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>231913</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -7405,8 +7049,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4051966" y="7705006"/>
-              <a:ext cx="2206200" cy="1191825"/>
+              <a:off x="8878510" y="2528011"/>
+              <a:ext cx="3010932" cy="1457873"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -18412,7 +18056,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{240C8AC7-0F61-4DDD-9013-EAC85AE6134F}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="15">
-  <location ref="F3:G8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="F3:G5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" numFmtId="164" outline="0" showAll="0" defaultSubtotal="0">
@@ -18786,9 +18430,9 @@
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
       <items count="4">
         <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
       </items>
     </pivotField>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -18805,9 +18449,9 @@
     </pivotField>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
       <items count="3">
-        <item x="1"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="2"/>
+        <item h="1" x="2"/>
       </items>
     </pivotField>
     <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -19338,18 +18982,9 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="5">
+  <rowItems count="2">
     <i>
       <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -19593,11 +19228,11 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="21" name="Tanggal">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="27" name="Tanggal">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
-            <customFilter operator="greaterThanOrEqual" val="45689"/>
+            <customFilter operator="greaterThanOrEqual" val="45778"/>
             <customFilter operator="lessThanOrEqual" val="45869"/>
           </customFilters>
         </filterColumn>
@@ -19622,7 +19257,7 @@
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{33554939-956D-4BE9-A88C-42E3B53823EE}" name="analisis" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="12">
-  <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A3:C6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" numFmtId="164" outline="0" showAll="0" defaultSubtotal="0">
@@ -19996,9 +19631,9 @@
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
       <items count="4">
         <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
       </items>
     </pivotField>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -20015,9 +19650,9 @@
     </pivotField>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
       <items count="3">
-        <item x="1"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="2"/>
+        <item h="1" x="2"/>
       </items>
     </pivotField>
     <pivotField compact="0" numFmtId="165" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -20548,18 +20183,9 @@
   <rowFields count="1">
     <field x="6"/>
   </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
+  <rowItems count="3">
     <i>
       <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i>
       <x v="4"/>
@@ -20695,11 +20321,11 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="21" name="Tanggal">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="27" name="Tanggal">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
-            <customFilter operator="greaterThanOrEqual" val="45689"/>
+            <customFilter operator="greaterThanOrEqual" val="45778"/>
             <customFilter operator="lessThanOrEqual" val="45869"/>
           </customFilters>
         </filterColumn>
@@ -20726,14 +20352,15 @@
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Kota" xr10:uid="{778F3C14-16CE-40F3-B5D6-56003E13C63D}" sourceName="Kota">
   <pivotTables>
     <pivotTable tabId="6" name="analisis"/>
+    <pivotTable tabId="6" name="PivotTable1"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="241815905">
       <items count="4">
         <i x="0" s="1"/>
-        <i x="3" s="1"/>
-        <i x="2" s="1"/>
-        <i x="1" s="1"/>
+        <i x="3"/>
+        <i x="2"/>
+        <i x="1"/>
       </items>
     </tabular>
   </data>
@@ -20744,13 +20371,14 @@
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Kategori" xr10:uid="{3A4EE724-4778-4E2C-98B6-A2758514889C}" sourceName="Kategori">
   <pivotTables>
     <pivotTable tabId="6" name="analisis"/>
+    <pivotTable tabId="6" name="PivotTable1"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="241815905">
       <items count="3">
-        <i x="1" s="1"/>
+        <i x="1"/>
         <i x="0" s="1"/>
-        <i x="2" s="1"/>
+        <i x="2"/>
       </items>
     </tabular>
   </data>
@@ -21168,7 +20796,7 @@
     <pivotTable tabId="6" name="PivotTable1"/>
   </pivotTables>
   <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="241815905" filterType="dateBetween">
-    <selection startDate="2025-02-01T00:00:00" endDate="2025-07-31T00:00:00"/>
+    <selection startDate="2025-05-01T00:00:00" endDate="2025-07-31T00:00:00"/>
     <bounds startDate="2025-01-01T00:00:00" endDate="2027-01-01T00:00:00"/>
   </state>
 </timelineCacheDefinition>
@@ -55545,7 +55173,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB7F205-A472-48BE-8BFF-99A604B10656}">
-  <dimension ref="A3:G9"/>
+  <dimension ref="A3:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.28515625" bestFit="1" customWidth="1"/>
@@ -55578,98 +55206,47 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B4" s="26">
-        <v>289800000</v>
+        <v>180000000</v>
       </c>
       <c r="C4" s="49">
-        <v>14.017054043839757</v>
+        <v>1.474537037037037</v>
       </c>
       <c r="F4" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="26">
-        <v>167845000</v>
+        <v>49085000</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B5" s="26">
-        <v>1260000000</v>
+        <v>54400000</v>
       </c>
       <c r="C5" s="49">
-        <v>10.844340277777777</v>
+        <v>1.8333333333333335</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>590</v>
       </c>
       <c r="G5" s="26">
-        <v>111475000</v>
+        <v>49085000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>536</v>
+        <v>590</v>
       </c>
       <c r="B6" s="26">
-        <v>261800000</v>
+        <v>234400000</v>
       </c>
       <c r="C6" s="49">
-        <v>12.644491129785242</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="26">
-        <v>234065000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>541</v>
-      </c>
-      <c r="B7" s="26">
-        <v>512400000</v>
-      </c>
-      <c r="C7" s="49">
-        <v>14.975907029478458</v>
-      </c>
-      <c r="F7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="26">
-        <v>120440000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>538</v>
-      </c>
-      <c r="B8" s="26">
-        <v>489600000</v>
-      </c>
-      <c r="C8" s="49">
-        <v>12.231413398692801</v>
-      </c>
-      <c r="F8" t="s">
-        <v>590</v>
-      </c>
-      <c r="G8" s="26">
-        <v>633825000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>590</v>
-      </c>
-      <c r="B9" s="26">
-        <v>2813600000</v>
-      </c>
-      <c r="C9" s="49">
-        <v>64.713205879574033</v>
+        <v>3.3078703703703702</v>
       </c>
     </row>
   </sheetData>
@@ -55826,7 +55403,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD4BEB8-677A-470D-90C9-6F3AB7B3C0BA}">
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="1.140625" style="14" customWidth="1"/>
@@ -55834,7 +55411,9 @@
     <col min="7" max="7" width="1.140625" style="14" customWidth="1"/>
     <col min="8" max="12" width="9.140625" style="14"/>
     <col min="13" max="13" width="1.140625" style="14" customWidth="1"/>
-    <col min="14" max="18" width="9.140625" style="14"/>
+    <col min="14" max="15" width="9.140625" style="14"/>
+    <col min="16" max="16" width="1.140625" style="14" customWidth="1"/>
+    <col min="17" max="18" width="9.140625" style="14"/>
     <col min="19" max="19" width="1.140625" style="14" customWidth="1"/>
     <col min="20" max="24" width="9.140625" style="14"/>
     <col min="25" max="25" width="1.140625" style="14" customWidth="1"/>
@@ -56113,6 +55692,8 @@
       <c r="W10" s="48"/>
       <c r="X10" s="48"/>
     </row>
+    <row r="11" spans="1:26" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="18" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:Y5"/>
